--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -64,17 +64,18 @@
     <definedName name="TrenchFt">Intake!$B$40</definedName>
     <definedName name="LaborDays">Intake!$B$41</definedName>
     <definedName name="WireTotal">Intake!$H$54</definedName>
-    <definedName name="IncHardware">Intake!$B$57</definedName>
-    <definedName name="IncSitePlan">Intake!$B$58</definedName>
-    <definedName name="IncSLD">Intake!$B$59</definedName>
-    <definedName name="IncCpm">Intake!$B$60</definedName>
-    <definedName name="IncPermits">Intake!$B$61</definedName>
-    <definedName name="IncGpr">Intake!$B$62</definedName>
-    <definedName name="HardwareFactor">Intake!$B$65</definedName>
-    <definedName name="RebateAmt">Intake!$B$66</definedName>
-    <definedName name="NetworkFeeMo">Intake!$B$67</definedName>
-    <definedName name="ContractYears">Intake!$B$68</definedName>
-    <definedName name="ServicePlanYr">Intake!$B$69</definedName>
+    <definedName name="LaborBase">Intake!$D$61</definedName>
+    <definedName name="IncHardware">Intake!$B$64</definedName>
+    <definedName name="IncSitePlan">Intake!$B$65</definedName>
+    <definedName name="IncSLD">Intake!$B$66</definedName>
+    <definedName name="IncCpm">Intake!$B$67</definedName>
+    <definedName name="IncPermits">Intake!$B$68</definedName>
+    <definedName name="IncGpr">Intake!$B$69</definedName>
+    <definedName name="HardwareFactor">Intake!$B$72</definedName>
+    <definedName name="RebateAmt">Intake!$B$73</definedName>
+    <definedName name="NetworkFeeMo">Intake!$B$74</definedName>
+    <definedName name="ContractYears">Intake!$B$75</definedName>
+    <definedName name="ServicePlanYr">Intake!$B$76</definedName>
     <definedName name="SgSuggested">Panel!$F$15</definedName>
     <definedName name="TxKvaConnected">Panel!$F$33</definedName>
     <definedName name="TxKvaSuggested">Panel!$F$35</definedName>
@@ -94,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="388">
   <si>
     <t>RFC INTAKE — EV Charging Project</t>
   </si>
@@ -264,6 +265,27 @@
     <t>Wire total</t>
   </si>
   <si>
+    <t>LABOR BREAKDOWN — add roles/phases; the total feeds the estimate</t>
+  </si>
+  <si>
+    <t>Role / phase</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>$ / day</t>
+  </si>
+  <si>
+    <t>Labor $</t>
+  </si>
+  <si>
+    <t>Electrical crew</t>
+  </si>
+  <si>
+    <t>Labor total (before contingency)</t>
+  </si>
+  <si>
     <t>INCLUDED SERVICES (Yes / No)</t>
   </si>
   <si>
@@ -585,7 +607,7 @@
     <t>Construction total (loaded)</t>
   </si>
   <si>
-    <t>Labor (days × rate, contingency-loaded)</t>
+    <t>Labor (breakdown total, contingency-loaded)</t>
   </si>
   <si>
     <t>Sales tax on construction</t>
@@ -1170,10 +1192,16 @@
     <t xml:space="preserve">   labor days, services, commercial terms. Totals show at the bottom of the Intake.</t>
   </si>
   <si>
-    <t>2. WIRE RUNS &amp; FEEDERS: every run's wire size, material (Cu/Al) and one-way ft is editable — like the V18 workbooks. Defaults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   auto-fill from the model and site distances; overtyping a yellow cell replaces its default formula (re-enter it to restore).</t>
+    <t>2. WIRE RUNS &amp; FEEDERS: every run's wire size, material (Cu/Al), runs and one-way ft is editable — like the V18 workbooks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Defaults auto-fill from the model and site distances; overtyping a yellow cell replaces its default formula. On long DCFC or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   feeder runs, extra parallel runs split the amps so each set can use smaller wire — often cheaper than one fat conductor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   LABOR BREAKDOWN: itemize by role/phase (foreman, crew, flagger…); the total feeds the estimate, contingency-loaded.</t>
   </si>
   <si>
     <t>3. Every price lives on the RateCard (yellow) — hardware, install allowance, gear catalog, wire $/ft (incl. 450 kcmil Cu &amp; Al),</t>
@@ -1464,8 +1492,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1896,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2285,7 +2313,7 @@
       <c r="C45" s="5">
         <f>IFERROR(VLOOKUP($A$23,ModelTable,15,FALSE),"Cu")</f>
       </c>
-      <c r="D45">
+      <c r="D45" s="5">
         <f>IFERROR($B$23*VLOOKUP($A$23,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E45">
@@ -2311,7 +2339,7 @@
       <c r="C46" s="5">
         <f>IFERROR(VLOOKUP($A$24,ModelTable,15,FALSE),"Cu")</f>
       </c>
-      <c r="D46">
+      <c r="D46" s="5">
         <f>IFERROR($B$24*VLOOKUP($A$24,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E46">
@@ -2337,7 +2365,7 @@
       <c r="C47" s="5">
         <f>IFERROR(VLOOKUP($A$25,ModelTable,15,FALSE),"Cu")</f>
       </c>
-      <c r="D47">
+      <c r="D47" s="5">
         <f>IFERROR($B$25*VLOOKUP($A$25,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E47">
@@ -2363,7 +2391,7 @@
       <c r="C48" s="5">
         <f>IFERROR(VLOOKUP($A$26,ModelTable,15,FALSE),"Cu")</f>
       </c>
-      <c r="D48">
+      <c r="D48" s="5">
         <f>IFERROR($B$26*VLOOKUP($A$26,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E48">
@@ -2389,7 +2417,7 @@
       <c r="C49" s="5">
         <f>IFERROR(VLOOKUP($A$27,ModelTable,15,FALSE),"Cu")</f>
       </c>
-      <c r="D49">
+      <c r="D49" s="5">
         <f>IFERROR($B$27*VLOOKUP($A$27,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E49">
@@ -2415,7 +2443,7 @@
       <c r="C50" s="5">
         <f>IFERROR(VLOOKUP($A$28,ModelTable,15,FALSE),"Cu")</f>
       </c>
-      <c r="D50">
+      <c r="D50" s="5">
         <f>IFERROR($B$28*VLOOKUP($A$28,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E50">
@@ -2522,131 +2550,196 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="7" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
+      <c r="C57" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
+      <c r="D57" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
+      <c r="B58" s="5">
+        <f>LaborDays</f>
+      </c>
+      <c r="C58" s="11">
+        <f>LaborDayRate</f>
+      </c>
+      <c r="D58" s="9">
+        <f>$B$58*$C$58</f>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5">
+        <v>0</v>
+      </c>
+      <c r="C59" s="11">
+        <v>0</v>
+      </c>
+      <c r="D59" s="9">
+        <f>$B$59*$C$59</f>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5">
+        <v>0</v>
+      </c>
+      <c r="C60" s="11">
+        <v>0</v>
+      </c>
+      <c r="D60" s="9">
+        <f>$B$60*$C$60</f>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+      <c r="D61" s="10">
+        <f>SUM(D58:D60)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B65" s="5">
-        <v>1</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B66" s="12">
-        <v>0</v>
+      <c r="B66" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="12">
-        <v>39.99</v>
+      <c r="B67" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="5">
-        <v>5</v>
+      <c r="B68" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B71">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="5">
+        <v>1</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="11">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78">
         <f>AdaVan&amp;" van + "&amp;AdaStd&amp;" standard + "&amp;AdaAmb&amp;" ambulatory"</f>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79">
         <f>IF(NDcfc&gt;0,SgSuggested&amp;"A switchgear @ 480V","208V service")&amp;IF(TxKvaSuggested&gt;0," + "&amp;TxKvaSuggested&amp;" kVA step-down TX","")</f>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B73" s="14">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="14">
         <f>TotalCost</f>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B74" s="10">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="10">
         <f>CustomerTotal</f>
       </c>
     </row>
@@ -2661,7 +2754,7 @@
     <dataValidation type="list" allowBlank="1" sqref="B45:B53">
       <formula1>RateCard!$A$129:$A$153</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B57:B62">
+    <dataValidation type="list" sqref="B64:B69">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C45:C53">
@@ -2675,7 +2768,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="114" customWidth="1"/>
@@ -2683,142 +2776,152 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="63" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="63" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="63" t="s">
-        <v>238</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>364</v>
+      <c r="A12" s="63" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="63" t="s">
-        <v>365</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="63" t="s">
-        <v>366</v>
+      <c r="A14" s="16" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="63" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="63" t="s">
-        <v>238</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>368</v>
+      <c r="A17" s="63" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="63" t="s">
-        <v>369</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="63" t="s">
-        <v>370</v>
+      <c r="A19" s="16" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="63" t="s">
-        <v>238</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>371</v>
+      <c r="A21" s="63" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="63" t="s">
-        <v>372</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="s">
-        <v>373</v>
+      <c r="A23" s="16" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="63" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="63" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="63" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="63" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="63" t="s">
-        <v>378</v>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="63" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="63" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -2839,12 +2942,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2855,16 +2958,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2989,7 +3092,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F11">
         <f>SUM(F5:F10)</f>
@@ -2997,7 +3100,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F12">
         <f>IF(AND(NDcfc&gt;0,NumL2&gt;0),TxKvaConnected*1000/(480*SQRT(3)),0)</f>
@@ -3005,7 +3108,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F13">
         <f>F11+F12</f>
@@ -3013,7 +3116,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F14">
         <f>F13*1.25</f>
@@ -3021,7 +3124,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F15">
         <f>IF(NDcfc&gt;0,INDEX(SgSizes,MIN(ROWS(SgSizes),COUNTIF(SgSizes,"&lt;"&amp;F14)+1)),0)</f>
@@ -3029,7 +3132,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F16" s="9">
         <f>IF(NDcfc&gt;0,VLOOKUP(SgSuggested,SgTable,2,FALSE),0)</f>
@@ -3037,7 +3140,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3048,16 +3151,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3182,7 +3285,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F26">
         <f>SUM(F20:F25)</f>
@@ -3190,7 +3293,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F27">
         <f>F26*1.25</f>
@@ -3198,7 +3301,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F28">
         <f>IF(NumL2&gt;0,INDEX(PnlSizes,MIN(ROWS(PnlSizes),COUNTIF(PnlSizes,"&lt;"&amp;F27)+1)),0)</f>
@@ -3206,7 +3309,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F29">
         <f>IF(NumL2=0,"—",IF(F28&gt;=1000,"Distribution panel","Sub-panel"))</f>
@@ -3214,7 +3317,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F30" s="9">
         <f>IF(NumL2&gt;0,VLOOKUP(F28,PnlTable,2,FALSE),0)</f>
@@ -3222,12 +3325,12 @@
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F33">
         <f>IF(AND(NDcfc&gt;0,NumL2&gt;0),F26*208*SQRT(3)/1000,0)</f>
@@ -3235,7 +3338,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F34">
         <f>F33*1.25</f>
@@ -3243,7 +3346,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F35">
         <f>IF(F33&gt;0,INDEX(TxSizes,MIN(ROWS(TxSizes),COUNTIF(TxSizes,"&lt;"&amp;F34)+1)),0)</f>
@@ -3251,7 +3354,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F36" s="9">
         <f>IF(F35&gt;0,VLOOKUP(F35,TxTable,2,FALSE),0)</f>
@@ -3259,7 +3362,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F37">
         <f>IF(F35&gt;0,F35*1000/(480*SQRT(3)),0)</f>
@@ -3267,7 +3370,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F38">
         <f>IF(F35&gt;0,INDEX(StdBrk,MIN(ROWS(StdBrk),COUNTIF(StdBrk,"&lt;"&amp;F37*1.25)+1)),0)</f>
@@ -3275,7 +3378,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F39" s="9">
         <f>IF(F38&gt;0,IFERROR(VLOOKUP(F38,BrkTbl480,2,FALSE),0),0)</f>
@@ -3283,7 +3386,7 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3291,19 +3394,19 @@
         <v>18</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3428,7 +3531,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F49" s="9">
         <f>SUM(F43:F48)+F39</f>
@@ -3436,7 +3539,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F51" s="17">
         <f>F16+F30+F36+F49</f>
@@ -3444,7 +3547,7 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3481,7 +3584,7 @@
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -3499,30 +3602,30 @@
     </row>
     <row r="2" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R2" s="20" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="N3">
         <f>SgSuggested&amp;" A 3P"</f>
@@ -3536,19 +3639,19 @@
     </row>
     <row r="4" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D4" s="21" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E4">
         <f>"UTILITY"</f>
       </c>
       <c r="H4" s="21" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N4">
         <f>SgSuggested&amp;" A"</f>
@@ -3562,22 +3665,22 @@
     </row>
     <row r="5" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D5" s="21" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="S5">
         <f>IF(Intake!$D$25="DCFC",Intake!$B$25*IFERROR(VLOOKUP(Intake!$A$25,ModelTable,7,FALSE),0),0)</f>
@@ -3596,40 +3699,40 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="S7">
         <f>IF(Intake!$D$27="DCFC",Intake!$B$27*IFERROR(VLOOKUP(Intake!$A$27,ModelTable,7,FALSE),0),0)</f>
@@ -3640,7 +3743,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B8" s="23">
         <v>1</v>
@@ -3677,7 +3780,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S8">
         <f>IF(Intake!$D$28="DCFC",Intake!$B$28*IFERROR(VLOOKUP(Intake!$A$28,ModelTable,7,FALSE),0),0)</f>
@@ -3688,7 +3791,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B9" s="23">
         <v>3</v>
@@ -3717,10 +3820,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="S9">
         <f>SUM(S3:S8)</f>
@@ -3728,7 +3831,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B10" s="23">
         <v>5</v>
@@ -3757,12 +3860,12 @@
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B11" s="23">
         <v>7</v>
@@ -3799,12 +3902,12 @@
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B12" s="23">
         <v>9</v>
@@ -3833,7 +3936,7 @@
         <v>10</v>
       </c>
       <c r="P12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -3865,7 +3968,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B13" s="23">
         <v>11</v>
@@ -3894,7 +3997,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S13">
         <v>2</v>
@@ -3926,7 +4029,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B14" s="23">
         <v>13</v>
@@ -3963,7 +4066,7 @@
         <v>14</v>
       </c>
       <c r="P14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S14">
         <v>3</v>
@@ -3995,7 +4098,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B15" s="23">
         <v>15</v>
@@ -4024,7 +4127,7 @@
         <v>16</v>
       </c>
       <c r="P15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S15">
         <v>4</v>
@@ -4056,7 +4159,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B16" s="23">
         <v>17</v>
@@ -4085,7 +4188,7 @@
         <v>18</v>
       </c>
       <c r="P16" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -4117,7 +4220,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B17" s="23">
         <v>19</v>
@@ -4154,7 +4257,7 @@
         <v>20</v>
       </c>
       <c r="P17" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -4186,7 +4289,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B18" s="23">
         <v>21</v>
@@ -4215,7 +4318,7 @@
         <v>22</v>
       </c>
       <c r="P18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -4247,7 +4350,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B19" s="23">
         <v>23</v>
@@ -4276,7 +4379,7 @@
         <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -4308,7 +4411,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B20" s="23">
         <v>25</v>
@@ -4345,7 +4448,7 @@
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -4377,7 +4480,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B21" s="23">
         <v>27</v>
@@ -4406,7 +4509,7 @@
         <v>28</v>
       </c>
       <c r="P21" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -4438,7 +4541,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B22" s="23">
         <v>29</v>
@@ -4467,7 +4570,7 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S22">
         <v>11</v>
@@ -4499,7 +4602,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B23" s="23">
         <v>31</v>
@@ -4536,7 +4639,7 @@
         <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S23">
         <v>12</v>
@@ -4568,7 +4671,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B24" s="23">
         <v>33</v>
@@ -4597,7 +4700,7 @@
         <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S24">
         <v>13</v>
@@ -4629,7 +4732,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B25" s="23">
         <v>35</v>
@@ -4658,7 +4761,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S25">
         <v>14</v>
@@ -4690,7 +4793,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B26" s="23">
         <v>37</v>
@@ -4727,7 +4830,7 @@
         <v>38</v>
       </c>
       <c r="P26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S26">
         <v>15</v>
@@ -4759,7 +4862,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B27" s="23">
         <v>39</v>
@@ -4788,7 +4891,7 @@
         <v>40</v>
       </c>
       <c r="P27" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S27">
         <v>16</v>
@@ -4820,7 +4923,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B28" s="23">
         <v>41</v>
@@ -4849,12 +4952,12 @@
         <v>42</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B29" s="23">
         <v>43</v>
@@ -4891,12 +4994,12 @@
         <v>44</v>
       </c>
       <c r="P29" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B30" s="23">
         <v>45</v>
@@ -4925,12 +5028,12 @@
         <v>46</v>
       </c>
       <c r="P30" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B31" s="23">
         <v>47</v>
@@ -4959,12 +5062,12 @@
         <v>48</v>
       </c>
       <c r="P31" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F33" s="25">
         <f>SUM(F8:G31)</f>
@@ -4979,7 +5082,7 @@
       </c>
       <c r="K33" s="25"/>
       <c r="L33" s="21" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="M33" s="21"/>
       <c r="N33" s="25">
@@ -4988,7 +5091,7 @@
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F34" s="25">
         <f>F33*1.25</f>
@@ -5003,7 +5106,7 @@
       </c>
       <c r="K34" s="25"/>
       <c r="L34" s="21" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="M34" s="21"/>
       <c r="N34" s="25">
@@ -5012,7 +5115,7 @@
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F35" s="25">
         <f>MAX($F$34,$H$34,$J$34)</f>
@@ -5027,7 +5130,7 @@
       </c>
       <c r="K35" s="25"/>
       <c r="L35" s="21" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M35" s="21"/>
       <c r="N35" s="26">
@@ -5036,7 +5139,7 @@
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F36" s="26">
         <f>F35/(480/SQRT(3))</f>
@@ -5051,7 +5154,7 @@
       </c>
       <c r="K36" s="26"/>
       <c r="L36" s="21" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M36" s="21"/>
       <c r="N36">
@@ -5119,7 +5222,7 @@
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -5137,30 +5240,30 @@
     </row>
     <row r="2" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R2" s="20" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="N3">
         <f>Panel!$F$28&amp;" A 3P"</f>
@@ -5174,19 +5277,19 @@
     </row>
     <row r="4" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D4" s="21" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E4">
         <f>IF(TxKvaSuggested&gt;0,"EV_MAIN VIA "&amp;TxKvaSuggested&amp;" KVA XFMR","UTILITY")</f>
       </c>
       <c r="H4" s="21" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N4">
         <f>Panel!$F$28&amp;" A"</f>
@@ -5200,22 +5303,22 @@
     </row>
     <row r="5" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D5" s="21" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="S5">
         <f>IF(Intake!$D$25="L2",Intake!$B$25*IFERROR(VLOOKUP(Intake!$A$25,ModelTable,7,FALSE),0),0)</f>
@@ -5234,40 +5337,40 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="S7">
         <f>IF(Intake!$D$27="L2",Intake!$B$27*IFERROR(VLOOKUP(Intake!$A$27,ModelTable,7,FALSE),0),0)</f>
@@ -5278,7 +5381,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B8" s="23">
         <v>1</v>
@@ -5315,7 +5418,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S8">
         <f>IF(Intake!$D$28="L2",Intake!$B$28*IFERROR(VLOOKUP(Intake!$A$28,ModelTable,7,FALSE),0),0)</f>
@@ -5326,7 +5429,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B9" s="23">
         <v>3</v>
@@ -5355,10 +5458,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="S9">
         <f>SUM(S3:S8)</f>
@@ -5366,7 +5469,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B10" s="23">
         <v>5</v>
@@ -5403,12 +5506,12 @@
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B11" s="23">
         <v>7</v>
@@ -5437,12 +5540,12 @@
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B12" s="23">
         <v>9</v>
@@ -5479,7 +5582,7 @@
         <v>10</v>
       </c>
       <c r="P12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -5511,7 +5614,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B13" s="23">
         <v>11</v>
@@ -5540,7 +5643,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S13">
         <v>2</v>
@@ -5572,7 +5675,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B14" s="23">
         <v>13</v>
@@ -5609,7 +5712,7 @@
         <v>14</v>
       </c>
       <c r="P14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S14">
         <v>3</v>
@@ -5641,7 +5744,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B15" s="23">
         <v>15</v>
@@ -5670,7 +5773,7 @@
         <v>16</v>
       </c>
       <c r="P15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S15">
         <v>4</v>
@@ -5702,7 +5805,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B16" s="23">
         <v>17</v>
@@ -5739,7 +5842,7 @@
         <v>18</v>
       </c>
       <c r="P16" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -5771,7 +5874,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B17" s="23">
         <v>19</v>
@@ -5800,7 +5903,7 @@
         <v>20</v>
       </c>
       <c r="P17" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -5832,7 +5935,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B18" s="23">
         <v>21</v>
@@ -5869,7 +5972,7 @@
         <v>22</v>
       </c>
       <c r="P18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -5901,7 +6004,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B19" s="23">
         <v>23</v>
@@ -5930,7 +6033,7 @@
         <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -5962,7 +6065,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B20" s="23">
         <v>25</v>
@@ -5999,7 +6102,7 @@
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -6031,7 +6134,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B21" s="23">
         <v>27</v>
@@ -6060,7 +6163,7 @@
         <v>28</v>
       </c>
       <c r="P21" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -6092,7 +6195,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B22" s="23">
         <v>29</v>
@@ -6129,7 +6232,7 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S22">
         <v>11</v>
@@ -6161,7 +6264,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B23" s="23">
         <v>31</v>
@@ -6190,7 +6293,7 @@
         <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S23">
         <v>12</v>
@@ -6222,7 +6325,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B24" s="23">
         <v>33</v>
@@ -6259,7 +6362,7 @@
         <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S24">
         <v>13</v>
@@ -6291,7 +6394,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B25" s="23">
         <v>35</v>
@@ -6320,7 +6423,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S25">
         <v>14</v>
@@ -6352,7 +6455,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B26" s="23">
         <v>37</v>
@@ -6389,7 +6492,7 @@
         <v>38</v>
       </c>
       <c r="P26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S26">
         <v>15</v>
@@ -6421,7 +6524,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B27" s="23">
         <v>39</v>
@@ -6450,7 +6553,7 @@
         <v>40</v>
       </c>
       <c r="P27" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S27">
         <v>16</v>
@@ -6482,7 +6585,7 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B28" s="23">
         <v>41</v>
@@ -6519,7 +6622,7 @@
         <v>42</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S28">
         <v>17</v>
@@ -6551,7 +6654,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B29" s="23">
         <v>43</v>
@@ -6580,7 +6683,7 @@
         <v>44</v>
       </c>
       <c r="P29" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="S29">
         <v>18</v>
@@ -6612,7 +6715,7 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B30" s="23">
         <v>45</v>
@@ -6649,7 +6752,7 @@
         <v>46</v>
       </c>
       <c r="P30" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="S30">
         <v>19</v>
@@ -6681,7 +6784,7 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B31" s="23">
         <v>47</v>
@@ -6710,7 +6813,7 @@
         <v>48</v>
       </c>
       <c r="P31" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="S31">
         <v>20</v>
@@ -6771,7 +6874,7 @@
     </row>
     <row r="33" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F33" s="25">
         <f>SUM(F8:G31)</f>
@@ -6786,7 +6889,7 @@
       </c>
       <c r="K33" s="25"/>
       <c r="L33" s="21" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="M33" s="21"/>
       <c r="N33" s="25">
@@ -6822,7 +6925,7 @@
     </row>
     <row r="34" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F34" s="25">
         <f>F33*1.25</f>
@@ -6837,7 +6940,7 @@
       </c>
       <c r="K34" s="25"/>
       <c r="L34" s="21" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="M34" s="21"/>
       <c r="N34" s="25">
@@ -6873,7 +6976,7 @@
     </row>
     <row r="35" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F35" s="25">
         <f>MAX($F$34,$H$34,$J$34)</f>
@@ -6888,7 +6991,7 @@
       </c>
       <c r="K35" s="25"/>
       <c r="L35" s="21" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M35" s="21"/>
       <c r="N35" s="26">
@@ -6924,7 +7027,7 @@
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F36" s="26">
         <f>F35/120</f>
@@ -6939,7 +7042,7 @@
       </c>
       <c r="K36" s="26"/>
       <c r="L36" s="21" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="M36" s="21"/>
       <c r="N36">
@@ -6991,17 +7094,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B4">
         <f>LaborDays</f>
@@ -7009,13 +7112,13 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B6" s="29"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B7" s="9">
         <f>WireTotal+SUM(Intake!E23:E28)</f>
@@ -7023,7 +7126,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B8" s="9">
         <f>GearTotal</f>
@@ -7031,7 +7134,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B9" s="9">
         <f>TrenchFt*TrenchRate*VLOOKUP(Terrain,TerrainTable,2,FALSE)</f>
@@ -7039,7 +7142,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B10" s="9">
         <f>IF(NTotal&gt;0,CivilBase,0)+NDcfc*CivilDcfc+NumL2*CivilL2</f>
@@ -7047,7 +7150,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B11" s="9">
         <f>NDcfc*SignageDcfc+NumL2*SignageL2</f>
@@ -7055,7 +7158,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B12" s="9">
         <f>AdaCost</f>
@@ -7063,7 +7166,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B13" s="9">
         <f>TrenchFt*VLOOKUP(Terrain,TerrainTable,5,FALSE)</f>
@@ -7071,7 +7174,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B14" s="9">
         <f>IF(IncGpr="Yes",MAX(1,ROUNDUP(TrenchFt/GprFtPerDay,0))*GprDayRate,0)</f>
@@ -7079,7 +7182,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B15" s="9">
         <f>IF(NTotal&gt;0,EquipBase+EquipPerDay*LaborDays,0)</f>
@@ -7087,7 +7190,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B16" s="9">
         <f>IF(IncPermits="Yes",200+60*NTotal,0)</f>
@@ -7095,7 +7198,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B17" s="9">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,2500+TransformerPad,800),0)</f>
@@ -7103,7 +7206,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B18" s="9">
         <f>SUM(B7:B17)</f>
@@ -7111,7 +7214,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B19" s="9">
         <f>B18*ContingencyPct</f>
@@ -7119,7 +7222,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B20" s="10">
         <f>B18+B19</f>
@@ -7127,15 +7230,15 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B22" s="9">
-        <f>LaborDays*LaborDayRate*(1+ContingencyPct)</f>
+        <f>LaborBase*(1+ContingencyPct)</f>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B23" s="9">
         <f>ConstructionTotal*TaxPct</f>
@@ -7143,7 +7246,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B24" s="9">
         <f>ConstructionTotal+LaborCost</f>
@@ -7151,13 +7254,13 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B26" s="29"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B27" s="9">
         <f>IF(IncHardware="Yes",SUM(Intake!F23:F28)*HardwareFactor,0)</f>
@@ -7165,7 +7268,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B28" s="9">
         <f>IF(IncHardware="Yes",CommDcfc*NDcfc+CommL2*NumL2,0)</f>
@@ -7173,7 +7276,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B29" s="9">
         <f>IF(IncHardware="Yes",NPorts*NetworkFeeMo*12*ContractYears,0)</f>
@@ -7181,7 +7284,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B30" s="9">
         <f>IF(IncHardware="Yes",ServicePlanYr*ContractYears,0)</f>
@@ -7189,7 +7292,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B31" s="9">
         <f>B27*TaxPct</f>
@@ -7197,13 +7300,13 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B33" s="29"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B34" s="9">
         <f>IF(IncSitePlan="Yes",2500+150*NTotal+IF(NDcfc&gt;0,1000,0),0)</f>
@@ -7211,7 +7314,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B35" s="9">
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,6000+900*NDcfc+150*NumL2,2500+150*NumL2),0)</f>
@@ -7219,7 +7322,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B36" s="9">
         <f>C36*PmRate</f>
@@ -7230,7 +7333,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B37" s="9">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,500+0.02*Valuation,300),0)</f>
@@ -7238,7 +7341,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B38" s="9">
         <f>SUM(B34:B37)</f>
@@ -7246,7 +7349,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B40" s="14">
         <f>ConstructionTotal+LaborCost+B23+B27+B28+B29+B30+B31+B38</f>
@@ -7254,7 +7357,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B41" s="9">
         <f>-RebateAmt</f>
@@ -7262,7 +7365,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B42" s="32">
         <f>TotalCost-RebateAmt</f>
@@ -7297,27 +7400,27 @@
   <sheetData>
     <row r="2" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="33" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="38" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C3" s="39">
         <v>1</v>
@@ -7335,13 +7438,13 @@
         <f>F3*C3</f>
       </c>
       <c r="J3" s="43" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K3" s="44"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="38" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C4" s="39">
         <v>1</v>
@@ -7359,15 +7462,15 @@
         <f>F4*C4</f>
       </c>
       <c r="J4" s="45" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="K4" s="46">
-        <f>LaborDayRate</f>
+        <f>IF(LaborDays&gt;0,LaborBase/LaborDays,0)</f>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C5" s="39">
         <v>1</v>
@@ -7385,7 +7488,7 @@
         <f>F5*C5</f>
       </c>
       <c r="J5" s="45" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K5" s="47">
         <f>LaborDays</f>
@@ -7393,7 +7496,7 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C6" s="39">
         <v>1</v>
@@ -7411,7 +7514,7 @@
         <f>F6*C6</f>
       </c>
       <c r="J6" s="45" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K6" s="47">
         <f>K5/30</f>
@@ -7419,7 +7522,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C7" s="39">
         <v>1</v>
@@ -7437,7 +7540,7 @@
         <f>F7*C7</f>
       </c>
       <c r="J7" s="48" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K7" s="49">
         <f>K5*K4</f>
@@ -7445,7 +7548,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="38" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C8" s="39">
         <v>1</v>
@@ -7465,7 +7568,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="38" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C9" s="39">
         <v>1</v>
@@ -7485,7 +7588,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="38" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C10" s="39">
         <v>1</v>
@@ -7505,7 +7608,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="38" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C11" s="39">
         <v>1</v>
@@ -7545,7 +7648,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C13" s="39">
         <v>1</v>
@@ -7565,7 +7668,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="38" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C14" s="39">
         <v>1</v>
@@ -7596,7 +7699,7 @@
     <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="55" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C17" s="55"/>
       <c r="D17" s="55"/>
@@ -7606,7 +7709,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="38" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C18" s="39">
         <f>K5</f>
@@ -7637,7 +7740,7 @@
     <row r="20" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="48"/>
       <c r="C20" s="56" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
@@ -7668,12 +7771,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B3">
         <f>NTotal</f>
@@ -7681,7 +7784,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B4">
         <f>IF(NTotal&lt;=0,0,IF(NTotal&lt;=100,1,1+ROUNDUP((NTotal-100)/300,0)))</f>
@@ -7689,7 +7792,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B5">
         <f>IF(NTotal&lt;=4,0,IF(NTotal&lt;=50,1,IF(NTotal&lt;=75,2,IF(NTotal&lt;=100,3,3+ROUNDUP((NTotal-100)/60,0)))))</f>
@@ -7697,7 +7800,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B6">
         <f>IF(NTotal&lt;=25,0,IF(NTotal&lt;=50,1,IF(NTotal&lt;=75,2,IF(NTotal&lt;=100,3,3+ROUNDUP((NTotal-100)/50,0)))))</f>
@@ -7705,7 +7808,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B7">
         <f>AdaVan+AdaStd+AdaAmb</f>
@@ -7713,7 +7816,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B9">
         <f>VLOOKUP(Terrain,TerrainTable,4,FALSE)</f>
@@ -7721,7 +7824,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B10" s="9">
         <f>(AdaVan*AdaVanCost+AdaStd*AdaStdCost+AdaAmb*AdaAmbCost)*VLOOKUP(Terrain,TerrainTable,4,FALSE)+IF(NTotal&gt;0,AdaRampCost,0)</f>
@@ -7729,130 +7832,130 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D15" s="59" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="59" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="59" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C19" s="59" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D19" s="59" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="60" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="60" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="60" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -7873,26 +7976,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B4">
         <f>2</f>
@@ -7901,12 +8004,12 @@
         <f>4</f>
       </c>
       <c r="D4" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <f>IF(IncSitePlan="Yes",5+ROUNDUP(NTotal/4,0),0)</f>
@@ -7915,12 +8018,12 @@
         <f>IF(IncSitePlan="Yes",10+ROUNDUP(NTotal/4,0),0)</f>
       </c>
       <c r="D5" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B6">
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,10+ROUNDUP(NDcfc/2,0),7),0)</f>
@@ -7929,12 +8032,12 @@
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,17+ROUNDUP(NDcfc/2,0),14),0)</f>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B7">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,20,5),0)</f>
@@ -7943,12 +8046,12 @@
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,60,15),0)</f>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B8">
         <f>IF(NDcfc&gt;0,85,20)</f>
@@ -7957,12 +8060,12 @@
         <f>IF(NDcfc&gt;0,250,60)</f>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B9">
         <f>LaborDays</f>
@@ -7971,12 +8074,12 @@
         <f>LaborDays+7</f>
       </c>
       <c r="D9" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B10">
         <f>5</f>
@@ -7985,12 +8088,12 @@
         <f>10</f>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B12">
         <f>MAX(B4+B5+B6+B7+B9+B10,B8)</f>
@@ -8001,7 +8104,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B13">
         <f>ROUND(B12/21,1)</f>
@@ -8039,7 +8142,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -8050,40 +8153,40 @@
         <v>20</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>42</v>
@@ -8092,21 +8195,21 @@
         <v>35</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B4" s="61">
         <v>3000</v>
@@ -8115,7 +8218,7 @@
         <v>538</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E4">
         <v>208</v>
@@ -8145,10 +8248,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -8168,7 +8271,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B5" s="61">
         <v>3500</v>
@@ -8177,7 +8280,7 @@
         <v>532</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E5">
         <v>208</v>
@@ -8207,13 +8310,13 @@
         <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O5" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q5" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="R5" s="8">
         <v>1.2</v>
@@ -8239,7 +8342,7 @@
         <v>542</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E6">
         <v>208</v>
@@ -8269,13 +8372,13 @@
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O6" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q6" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="R6" s="8">
         <v>1.5</v>
@@ -8292,7 +8395,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B7" s="61">
         <v>5000</v>
@@ -8301,7 +8404,7 @@
         <v>611</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E7">
         <v>208</v>
@@ -8331,13 +8434,13 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O7" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q7" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="R7" s="8">
         <v>2.5</v>
@@ -8354,7 +8457,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B8" s="61">
         <v>7500</v>
@@ -8363,7 +8466,7 @@
         <v>943</v>
       </c>
       <c r="D8" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E8">
         <v>208</v>
@@ -8393,15 +8496,15 @@
         <v>2</v>
       </c>
       <c r="N8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="O8" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B9" s="61">
         <v>5500</v>
@@ -8410,7 +8513,7 @@
         <v>693</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E9">
         <v>208</v>
@@ -8440,15 +8543,15 @@
         <v>2</v>
       </c>
       <c r="N9" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O9" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B10" s="61">
         <v>6500</v>
@@ -8457,7 +8560,7 @@
         <v>710</v>
       </c>
       <c r="D10" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E10">
         <v>208</v>
@@ -8487,13 +8590,13 @@
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O10" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="R10" s="61">
         <v>40.81</v>
@@ -8501,7 +8604,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B11" s="61">
         <v>8500</v>
@@ -8510,7 +8613,7 @@
         <v>862</v>
       </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E11">
         <v>208</v>
@@ -8540,13 +8643,13 @@
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O11" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q11" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="R11" s="62">
         <v>0.1</v>
@@ -8554,7 +8657,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B12" s="61">
         <v>32000</v>
@@ -8563,7 +8666,7 @@
         <v>654</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E12">
         <v>480</v>
@@ -8593,13 +8696,13 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O12" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q12" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="R12" s="62">
         <v>0.0725</v>
@@ -8607,7 +8710,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B13" s="61">
         <v>35000</v>
@@ -8616,7 +8719,7 @@
         <v>654</v>
       </c>
       <c r="D13" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E13">
         <v>480</v>
@@ -8646,13 +8749,13 @@
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O13" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q13" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="R13" s="61">
         <v>2250</v>
@@ -8660,7 +8763,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B14" s="61">
         <v>38000</v>
@@ -8669,7 +8772,7 @@
         <v>657</v>
       </c>
       <c r="D14" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E14">
         <v>480</v>
@@ -8699,13 +8802,13 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O14" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q14" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="R14" s="61">
         <v>358</v>
@@ -8713,7 +8816,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B15" s="61">
         <v>42000</v>
@@ -8722,7 +8825,7 @@
         <v>657</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E15">
         <v>480</v>
@@ -8752,13 +8855,13 @@
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="O15" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q15" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="R15" s="62">
         <v>0.05</v>
@@ -8766,7 +8869,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B16" s="61">
         <v>52000</v>
@@ -8775,7 +8878,7 @@
         <v>768</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E16">
         <v>480</v>
@@ -8805,13 +8908,13 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O16" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q16" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="R16" s="61">
         <v>1500</v>
@@ -8819,7 +8922,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B17" s="61">
         <v>57000</v>
@@ -8828,7 +8931,7 @@
         <v>768</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E17">
         <v>480</v>
@@ -8858,13 +8961,13 @@
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O17" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q17" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="R17" s="8">
         <v>2000</v>
@@ -8872,7 +8975,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B18" s="61">
         <v>60000</v>
@@ -8881,7 +8984,7 @@
         <v>808</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E18">
         <v>480</v>
@@ -8911,13 +9014,13 @@
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O18" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q18" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="R18" s="61">
         <v>6500</v>
@@ -8925,7 +9028,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B19" s="61">
         <v>66000</v>
@@ -8934,7 +9037,7 @@
         <v>808</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E19">
         <v>480</v>
@@ -8964,13 +9067,13 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O19" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q19" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="R19" s="61">
         <v>4900</v>
@@ -8978,7 +9081,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B20" s="61">
         <v>72000</v>
@@ -8987,7 +9090,7 @@
         <v>1003</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E20">
         <v>480</v>
@@ -9017,13 +9120,13 @@
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="O20" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q20" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="R20" s="61">
         <v>3500</v>
@@ -9031,7 +9134,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B21" s="61">
         <v>79000</v>
@@ -9040,7 +9143,7 @@
         <v>1003</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E21">
         <v>480</v>
@@ -9070,13 +9173,13 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="O21" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q21" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="R21" s="61">
         <v>5200</v>
@@ -9084,7 +9187,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B22" s="61">
         <v>80000</v>
@@ -9093,7 +9196,7 @@
         <v>1086</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E22">
         <v>480</v>
@@ -9123,13 +9226,13 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="O22" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q22" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="R22" s="61">
         <v>2903</v>
@@ -9137,7 +9240,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B23" s="61">
         <v>88000</v>
@@ -9146,7 +9249,7 @@
         <v>1086</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E23">
         <v>480</v>
@@ -9176,13 +9279,13 @@
         <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="O23" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q23" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="R23" s="61">
         <v>758</v>
@@ -9199,7 +9302,7 @@
         <v>1182</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E24">
         <v>480</v>
@@ -9229,13 +9332,13 @@
         <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="O24" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q24" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="R24" s="61">
         <v>302</v>
@@ -9243,7 +9346,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B25" s="61">
         <v>100000</v>
@@ -9252,7 +9355,7 @@
         <v>1182</v>
       </c>
       <c r="D25" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E25">
         <v>480</v>
@@ -9282,13 +9385,13 @@
         <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="O25" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q25" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="R25" s="61">
         <v>658</v>
@@ -9296,7 +9399,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B26" s="61">
         <v>105000</v>
@@ -9305,7 +9408,7 @@
         <v>1518</v>
       </c>
       <c r="D26" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E26">
         <v>480</v>
@@ -9335,13 +9438,13 @@
         <v>3</v>
       </c>
       <c r="N26" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O26" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q26" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="R26" s="61">
         <v>396</v>
@@ -9349,7 +9452,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B27" s="61">
         <v>115000</v>
@@ -9358,7 +9461,7 @@
         <v>1518</v>
       </c>
       <c r="D27" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E27">
         <v>480</v>
@@ -9388,13 +9491,13 @@
         <v>3</v>
       </c>
       <c r="N27" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O27" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q27" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="R27" s="61">
         <v>5000</v>
@@ -9402,7 +9505,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B28" s="61">
         <v>120000</v>
@@ -9411,7 +9514,7 @@
         <v>1816</v>
       </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E28">
         <v>480</v>
@@ -9441,13 +9544,13 @@
         <v>3</v>
       </c>
       <c r="N28" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O28" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q28" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="R28" s="61">
         <v>1500</v>
@@ -9455,7 +9558,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B29" s="61">
         <v>130000</v>
@@ -9464,7 +9567,7 @@
         <v>1816</v>
       </c>
       <c r="D29" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E29">
         <v>480</v>
@@ -9494,13 +9597,13 @@
         <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q29" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="R29" s="61">
         <v>250</v>
@@ -9508,7 +9611,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B30" s="61">
         <v>135000</v>
@@ -9517,7 +9620,7 @@
         <v>1816</v>
       </c>
       <c r="D30" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E30">
         <v>480</v>
@@ -9547,13 +9650,13 @@
         <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O30" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q30" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="R30" s="61">
         <v>3519</v>
@@ -9561,7 +9664,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B31" s="61">
         <v>147000</v>
@@ -9570,7 +9673,7 @@
         <v>1816</v>
       </c>
       <c r="D31" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E31">
         <v>480</v>
@@ -9600,13 +9703,13 @@
         <v>3</v>
       </c>
       <c r="N31" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O31" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Q31" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="R31" s="61">
         <v>261</v>
@@ -9614,7 +9717,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B32" s="61">
         <v>155000</v>
@@ -9623,7 +9726,7 @@
         <v>2007</v>
       </c>
       <c r="D32" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E32">
         <v>480</v>
@@ -9656,12 +9759,12 @@
         <v>54</v>
       </c>
       <c r="O32" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B33" s="61">
         <v>168000</v>
@@ -9670,7 +9773,7 @@
         <v>2007</v>
       </c>
       <c r="D33" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E33">
         <v>480</v>
@@ -9703,25 +9806,25 @@
         <v>54</v>
       </c>
       <c r="O33" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -9806,15 +9909,15 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -9867,15 +9970,15 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -9936,15 +10039,15 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -10045,15 +10148,15 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -10082,7 +10185,7 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
@@ -10267,29 +10370,29 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B129" s="61">
         <v>0</v>
@@ -10306,7 +10409,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B130" s="61">
         <v>0</v>
@@ -10323,7 +10426,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B131" s="61">
         <v>0.30329</v>
@@ -10340,7 +10443,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B132" s="61">
         <v>0.56613</v>
@@ -10357,7 +10460,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B133" s="61">
         <v>0.87104</v>
@@ -10374,7 +10477,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B134" s="61">
         <v>1.33293</v>
@@ -10391,7 +10494,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B135" s="61">
         <v>1.68126</v>
@@ -10408,7 +10511,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B136" s="61">
         <v>2.1044</v>
@@ -10425,7 +10528,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B137" s="61">
         <v>2.39833</v>
@@ -10442,7 +10545,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B138" s="61">
         <v>2.95304</v>
@@ -10459,7 +10562,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B139" s="61">
         <v>3.63758</v>
@@ -10476,7 +10579,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B140" s="61">
         <v>4.5658</v>
@@ -10510,7 +10613,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B142" s="61">
         <v>6.64016</v>
@@ -10527,7 +10630,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B143" s="61">
         <v>7.9632</v>
@@ -10561,7 +10664,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B145" s="61">
         <v>10.60671</v>
@@ -10578,7 +10681,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B146" s="61">
         <v>11.334</v>
@@ -10595,7 +10698,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B147" s="61">
         <v>13.30059</v>
@@ -10629,7 +10732,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B149" s="61">
         <v>0</v>
@@ -10646,7 +10749,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B150" s="61">
         <v>25.921</v>
@@ -10663,7 +10766,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B151" s="61">
         <v>0</v>
@@ -10680,7 +10783,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B152" s="61">
         <v>0</v>
@@ -10697,7 +10800,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B153" s="61">
         <v>34.398</v>
@@ -10714,7 +10817,7 @@
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -16,7 +16,7 @@
     <sheet sheetId="10" name="Instructions" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="ModelTable">RateCard!$A$4:$O$33</definedName>
+    <definedName name="ModelTable">RateCard!$A$4:$P$33</definedName>
     <definedName name="SgSizes">RateCard!$A$38:$A$47</definedName>
     <definedName name="SgTable">RateCard!$A$38:$B$47</definedName>
     <definedName name="PnlSizes">RateCard!$A$51:$A$56</definedName>
@@ -53,6 +53,11 @@
     <definedName name="CommL2">RateCard!$R$29</definedName>
     <definedName name="EquipBase">RateCard!$R$30</definedName>
     <definedName name="EquipPerDay">RateCard!$R$31</definedName>
+    <definedName name="EquipBaseEmt">RateCard!$R$32</definedName>
+    <definedName name="EquipPerDayEmt">RateCard!$R$33</definedName>
+    <definedName name="EmtRackCost">RateCard!$R$34</definedName>
+    <definedName name="EmtStrapCost">RateCard!$R$35</definedName>
+    <definedName name="EmtFtPerDay">RateCard!$R$36</definedName>
     <definedName name="NTotal">Intake!$B$30</definedName>
     <definedName name="NDcfc">Intake!$B$31</definedName>
     <definedName name="NumL2">Intake!$B$32</definedName>
@@ -61,33 +66,35 @@
     <definedName name="RunFtL2">Intake!$B$37</definedName>
     <definedName name="StepFt">Intake!$B$38</definedName>
     <definedName name="Terrain">Intake!$B$39</definedName>
-    <definedName name="TrenchFt">Intake!$B$40</definedName>
-    <definedName name="LaborDays">Intake!$B$41</definedName>
-    <definedName name="WireTotal">Intake!$H$54</definedName>
-    <definedName name="LaborBase">Intake!$D$61</definedName>
-    <definedName name="IncHardware">Intake!$B$64</definedName>
-    <definedName name="IncSitePlan">Intake!$B$65</definedName>
-    <definedName name="IncSLD">Intake!$B$66</definedName>
-    <definedName name="IncCpm">Intake!$B$67</definedName>
-    <definedName name="IncPermits">Intake!$B$68</definedName>
-    <definedName name="IncGpr">Intake!$B$69</definedName>
-    <definedName name="HardwareFactor">Intake!$B$72</definedName>
-    <definedName name="RebateAmt">Intake!$B$73</definedName>
-    <definedName name="NetworkFeeMo">Intake!$B$74</definedName>
-    <definedName name="ContractYears">Intake!$B$75</definedName>
-    <definedName name="ServicePlanYr">Intake!$B$76</definedName>
+    <definedName name="InstallMethod">Intake!$B$40</definedName>
+    <definedName name="RouteFt">Intake!$B$41</definedName>
+    <definedName name="TrenchFt">Intake!$B$42</definedName>
+    <definedName name="LaborDays">Intake!$B$43</definedName>
+    <definedName name="WireTotal">Intake!$H$56</definedName>
+    <definedName name="LaborBase">Intake!$D$63</definedName>
+    <definedName name="IncHardware">Intake!$B$66</definedName>
+    <definedName name="IncSitePlan">Intake!$B$67</definedName>
+    <definedName name="IncSLD">Intake!$B$68</definedName>
+    <definedName name="IncCpm">Intake!$B$69</definedName>
+    <definedName name="IncPermits">Intake!$B$70</definedName>
+    <definedName name="IncGpr">Intake!$B$71</definedName>
+    <definedName name="HardwareFactor">Intake!$B$74</definedName>
+    <definedName name="RebateAmt">Intake!$B$75</definedName>
+    <definedName name="NetworkFeeMo">Intake!$B$76</definedName>
+    <definedName name="ContractYears">Intake!$B$77</definedName>
+    <definedName name="ServicePlanYr">Intake!$B$78</definedName>
     <definedName name="SgSuggested">Panel!$F$15</definedName>
     <definedName name="TxKvaConnected">Panel!$F$33</definedName>
     <definedName name="TxKvaSuggested">Panel!$F$35</definedName>
     <definedName name="GearTotal">Panel!$F$51</definedName>
-    <definedName name="ConstructionTotal">Estimate!$B$20</definedName>
-    <definedName name="LaborCost">Estimate!$B$22</definedName>
-    <definedName name="Valuation">Estimate!$B$24</definedName>
-    <definedName name="TotalCost">Estimate!$B$40</definedName>
-    <definedName name="CustomerTotal">Estimate!$B$42</definedName>
-    <definedName name="AdaVan">ADA!$B$4</definedName>
-    <definedName name="AdaStd">ADA!$B$5</definedName>
-    <definedName name="AdaAmb">ADA!$B$6</definedName>
+    <definedName name="ConstructionTotal">Estimate!$B$21</definedName>
+    <definedName name="LaborCost">Estimate!$B$23</definedName>
+    <definedName name="Valuation">Estimate!$B$25</definedName>
+    <definedName name="TotalCost">Estimate!$B$41</definedName>
+    <definedName name="CustomerTotal">Estimate!$B$43</definedName>
+    <definedName name="AdaVan">ADA!$C$6</definedName>
+    <definedName name="AdaStd">ADA!$D$6</definedName>
+    <definedName name="AdaAmb">ADA!$E$6</definedName>
     <definedName name="AdaCost">ADA!$B$10</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -95,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="412">
   <si>
     <t>RFC INTAKE — EV Charging Project</t>
   </si>
@@ -208,7 +215,19 @@
     <t>flat</t>
   </si>
   <si>
-    <t>Trench length (ft) — overtype if surveyed</t>
+    <t>Install method (Trenched / Surface EMT / Hybrid)</t>
+  </si>
+  <si>
+    <t>Trenched</t>
+  </si>
+  <si>
+    <t>Surface EMT = garage ceiling racks, no digging. Hybrid = EMT inside, trench only the utility→switchgear section.</t>
+  </si>
+  <si>
+    <t>Conduit route (ft) — the path the runs follow; overtype if surveyed</t>
+  </si>
+  <si>
+    <t>Trench length (ft) — auto from the method; overtype if surveyed</t>
   </si>
   <si>
     <t>Construction labor days — overtype if known</t>
@@ -331,7 +350,7 @@
     <t>Service plan $/year (post-warranty)</t>
   </si>
   <si>
-    <t>CBC 11B-812 accessible stalls required</t>
+    <t>Accessible stalls (CBC 11B-228.3: L2 and DCFC counted separately)</t>
   </si>
   <si>
     <t>Main gear (auto — Panel sheet)</t>
@@ -373,7 +392,10 @@
     <t>480V bus demand amps (×125%)</t>
   </si>
   <si>
-    <t>Suggested main switchgear (A)</t>
+    <t>Main switchgear (A) — auto, or type an override in D15</t>
+  </si>
+  <si>
+    <t>← override</t>
   </si>
   <si>
     <t>Switchgear price (website catalog)</t>
@@ -388,7 +410,7 @@
     <t>208V bus demand amps (×125%)</t>
   </si>
   <si>
-    <t>Suggested 208V panel (A)</t>
+    <t>208V panel (A) — auto, or type an override in D28</t>
   </si>
   <si>
     <t>Panel type</t>
@@ -406,7 +428,7 @@
     <t>Demand kVA (×125%)</t>
   </si>
   <si>
-    <t>Suggested transformer (kVA)</t>
+    <t>Transformer (kVA) — auto, or type an override in D35</t>
   </si>
   <si>
     <t>Transformer price</t>
@@ -442,6 +464,9 @@
     <t>A $0 unit price means no catalog price for that size — add it on the RateCard before quoting.</t>
   </si>
   <si>
+    <t>Yellow D-column cells override the auto gear size (D15 switchgear, D28 panel, D35 transformer) — the primary breaker, feeder runs on the Intake, and prices all re-derive. Clear the cell to go back to auto.</t>
+  </si>
+  <si>
     <t>PANEL SCHEDULE</t>
   </si>
   <si>
@@ -577,6 +602,9 @@
     <t>Trenching / asphalt cut (terrain-adjusted)</t>
   </si>
   <si>
+    <t>Surface EMT supports — strut racks @ 10 ft + straps (NEC 358.30)</t>
+  </si>
+  <si>
     <t>Civil (concrete, rebar, wheel stops)</t>
   </si>
   <si>
@@ -721,22 +749,34 @@
     <t>ZERO IMPACT BUILDERS COSTS</t>
   </si>
   <si>
-    <t>Accessible EVCS — CBC 11B-812 (auto from Intake)</t>
-  </si>
-  <si>
-    <t>Total chargers (from Intake)</t>
-  </si>
-  <si>
-    <t>Van accessible (12 ft + 5 ft aisle)</t>
-  </si>
-  <si>
-    <t>Standard accessible (9 ft + 5 ft aisle)</t>
-  </si>
-  <si>
-    <t>Ambulatory (10 ft, no aisle)</t>
-  </si>
-  <si>
-    <t>Total accessible stalls</t>
+    <t>Accessible EVCS — CBC 11B-228.3 / 11B-812 (auto from Intake)</t>
+  </si>
+  <si>
+    <t>Each charging level (L2, DCFC) counts as its own facility per 11B-228.3.2 — the table below runs once per level, then sums.</t>
+  </si>
+  <si>
+    <t>Facility (charging level)</t>
+  </si>
+  <si>
+    <t>Chargers</t>
+  </si>
+  <si>
+    <t>Van</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Ambulatory</t>
+  </si>
+  <si>
+    <t>Level 2 (208/240V AC)</t>
+  </si>
+  <si>
+    <t>Level 3 / DCFC</t>
+  </si>
+  <si>
+    <t>SITE TOTAL (sum of facilities)</t>
   </si>
   <si>
     <t>Terrain regrade factor (2% slope rule)</t>
@@ -745,19 +785,10 @@
     <t>ADA construction cost</t>
   </si>
   <si>
-    <t>CBC Table 11B-228.3.2.1 (2022 CBC — van divisor is 300; verify with your AHJ):</t>
-  </si>
-  <si>
-    <t>Total EVCS</t>
-  </si>
-  <si>
-    <t>Van</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>Ambulatory</t>
+    <t>CBC Table 11B-228.3.2.1 — applied PER FACILITY (per charging level), not to the combined count (van divisor 300 per 2022/2025 CBC; verify with your AHJ):</t>
+  </si>
+  <si>
+    <t>EVCS per facility</t>
   </si>
   <si>
     <t>1 – 4</t>
@@ -799,13 +830,16 @@
     <t>3 + 1/50 over 100</t>
   </si>
   <si>
+    <t>• 11B-228.3.2: each charging level AND connector type is a separate facility — mixing CCS + NACS on one power level can add facilities; verify with the AHJ.</t>
+  </si>
+  <si>
     <t>• Slope ≤ 2% in every direction under stalls and aisles — regrading is the big cost on sloped lots.</t>
   </si>
   <si>
     <t>• EVCS markings must NOT be blue (11B-812.9); stencil 'EV CHARGING ONLY' in 12-in letters.</t>
   </si>
   <si>
-    <t>• ISA signs: none if ≤4 EVCS; van space only for 5-25; all van + standard for 26+. Never on ambulatory.</t>
+    <t>• ISA signs (per facility): none if ≤4 EVCS; van space only for 5-25; all van + standard for 26+. Never on ambulatory.</t>
   </si>
   <si>
     <t>• Accessible EVCS do NOT count toward regular ADA parking minimums (11B-208.1).</t>
@@ -889,6 +923,9 @@
     <t>Default wire</t>
   </si>
   <si>
+    <t>Install EMT $/u</t>
+  </si>
+  <si>
     <t>Trench ×</t>
   </si>
   <si>
@@ -1090,15 +1127,30 @@
     <t>DCFC 360kW</t>
   </si>
   <si>
+    <t>Equipment base $ (surface EMT — lift, no dig gear)</t>
+  </si>
+  <si>
     <t>DCFC 360kW Dual</t>
   </si>
   <si>
-    <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
+    <t>Equipment $/labor-day (surface EMT)</t>
+  </si>
+  <si>
+    <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. 'Install EMT $/u' is the same allowance with surface EMT conduit (garage installs; strut racks are a separate Estimate line). Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
+  </si>
+  <si>
+    <t>Strut trapeze rack $ (strut+rod+anchors, NEC 358.30)</t>
+  </si>
+  <si>
+    <t>Strut conduit strap $ (per pipe per rack)</t>
   </si>
   <si>
     <t>Main switchgear 480V (website catalog)</t>
   </si>
   <si>
+    <t>Surface EMT route-ft per crew-day</t>
+  </si>
+  <si>
     <t>Size</t>
   </si>
   <si>
@@ -1204,6 +1256,24 @@
     <t xml:space="preserve">   LABOR BREAKDOWN: itemize by role/phase (foreman, crew, flagger…); the total feeds the estimate, contingency-loaded.</t>
   </si>
   <si>
+    <t xml:space="preserve">   INSTALL METHOD (Intake B40): 'Trenched' = underground PVC (the classic outdoor lot). 'Surface EMT' = garage install on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   strut trapeze racks every 10 ft (NEC 358.30) — zero trenching, racks/straps priced on the Estimate, install allowance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   switches to the EMT column, dig-gear rentals swap for a scissor lift. 'Hybrid' = chargers in EMT inside the structure,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   trench only the utility → switchgear service section (feeder lengths, rows 53-55).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   PANEL SHEET OVERRIDES: type a size in the yellow D-cells (D15 switchgear, D28 panel, D35 transformer) to force gear one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   frame up/down — the primary breaker, Intake feeder runs and prices all re-derive. Clear the cell to go back to auto.</t>
+  </si>
+  <si>
     <t>3. Every price lives on the RateCard (yellow) — hardware, install allowance, gear catalog, wire $/ft (incl. 450 kcmil Cu &amp; Al),</t>
   </si>
   <si>
@@ -1246,7 +1316,16 @@
     <t>• Terrain multipliers: trenching ×1.2 sloped / ×1.5 hilly / ×2.5 rocky; ADA regrade ×1.4/×1.7/×1.8 (2% slope rule). Solid rock: quote.</t>
   </si>
   <si>
-    <t>• ADA per CBC 11B-812: van $6.5k, standard $4.9k (shop bid rate), ambulatory $3.5k flat-lot, ramp $5.2k. Markings must NOT be blue.</t>
+    <t>• ADA per CBC 11B-228.3: L2 and DCFC count as SEPARATE facilities — the stall table runs once per level, then sums (see ADA sheet).</t>
+  </si>
+  <si>
+    <t>• ADA stall rates: van $6.5k, standard $4.9k (shop bid rate), ambulatory $3.5k flat-lot, ramp $5.2k. Markings must NOT be blue.</t>
+  </si>
+  <si>
+    <t>• Surface EMT: strut trapeze $28 + $3.25/strap per pipe per rack (every 10 ft, NEC 358.30); EMT hangs ~100 route-ft/crew-day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Open-air decks are damp/wet locations — swap set-screw fittings for listed raintight compression (≈2-3× price) per 358.42.</t>
   </si>
   <si>
     <t>• Permits: L2-only = streamlined flat fees (AB 1236); DCFC = plan check ≈ 2% of construction valuation + issuance + utility fees.</t>
@@ -1491,9 +1570,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1924,7 +2003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2079,7 +2158,7 @@
         <f>IFERROR(VLOOKUP($A23,ModelTable,4,FALSE),"")</f>
       </c>
       <c r="E23" s="9">
-        <f>IFERROR($B23*VLOOKUP($A23,ModelTable,3,FALSE),0)</f>
+        <f>IFERROR($B23*VLOOKUP($A23,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
       </c>
       <c r="F23" s="9">
         <f>IFERROR($B23*VLOOKUP($A23,ModelTable,2,FALSE),0)</f>
@@ -2102,7 +2181,7 @@
         <f>IFERROR(VLOOKUP($A24,ModelTable,4,FALSE),"")</f>
       </c>
       <c r="E24" s="9">
-        <f>IFERROR($B24*VLOOKUP($A24,ModelTable,3,FALSE),0)</f>
+        <f>IFERROR($B24*VLOOKUP($A24,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
       </c>
       <c r="F24" s="9">
         <f>IFERROR($B24*VLOOKUP($A24,ModelTable,2,FALSE),0)</f>
@@ -2121,7 +2200,7 @@
         <f>IFERROR(VLOOKUP($A25,ModelTable,4,FALSE),"")</f>
       </c>
       <c r="E25" s="9">
-        <f>IFERROR($B25*VLOOKUP($A25,ModelTable,3,FALSE),0)</f>
+        <f>IFERROR($B25*VLOOKUP($A25,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
       </c>
       <c r="F25" s="9">
         <f>IFERROR($B25*VLOOKUP($A25,ModelTable,2,FALSE),0)</f>
@@ -2140,7 +2219,7 @@
         <f>IFERROR(VLOOKUP($A26,ModelTable,4,FALSE),"")</f>
       </c>
       <c r="E26" s="9">
-        <f>IFERROR($B26*VLOOKUP($A26,ModelTable,3,FALSE),0)</f>
+        <f>IFERROR($B26*VLOOKUP($A26,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
       </c>
       <c r="F26" s="9">
         <f>IFERROR($B26*VLOOKUP($A26,ModelTable,2,FALSE),0)</f>
@@ -2159,7 +2238,7 @@
         <f>IFERROR(VLOOKUP($A27,ModelTable,4,FALSE),"")</f>
       </c>
       <c r="E27" s="9">
-        <f>IFERROR($B27*VLOOKUP($A27,ModelTable,3,FALSE),0)</f>
+        <f>IFERROR($B27*VLOOKUP($A27,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
       </c>
       <c r="F27" s="9">
         <f>IFERROR($B27*VLOOKUP($A27,ModelTable,2,FALSE),0)</f>
@@ -2178,7 +2257,7 @@
         <f>IFERROR(VLOOKUP($A28,ModelTable,4,FALSE),"")</f>
       </c>
       <c r="E28" s="9">
-        <f>IFERROR($B28*VLOOKUP($A28,ModelTable,3,FALSE),0)</f>
+        <f>IFERROR($B28*VLOOKUP($A28,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
       </c>
       <c r="F28" s="9">
         <f>IFERROR($B28*VLOOKUP($A28,ModelTable,2,FALSE),0)</f>
@@ -2256,123 +2335,90 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="5">
-        <f>IF(NDcfc&gt;0,RunFtDcfc+StepFt*(NDcfc-1),0)+IF(NumL2&gt;0,RunFtL2+StepFt*(NumL2-1),0)</f>
+      <c r="B40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5">
-        <f>IF(NTotal&lt;=0,0,ROUNDUP((8+2.5*NDcfc+1*NumL2+TrenchFt/40)*VLOOKUP(Terrain,TerrainTable,3,FALSE),0))</f>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="7" t="s">
+        <f>IF(NDcfc&gt;0,RunFtDcfc+StepFt*(NDcfc-1),0)+IF(NumL2&gt;0,RunFtL2+StepFt*(NumL2-1),0)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="B42" s="5">
+        <f>IF(InstallMethod="Surface EMT",0,IF(InstallMethod="Hybrid",SUMPRODUCT(($D$53:$D$55&gt;0)*$F$53:$F$55),RouteFt))</f>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="B43" s="5">
+        <f>IF(NTotal&lt;=0,0,ROUNDUP((8+2.5*NDcfc+1*NumL2+TrenchFt/40)*VLOOKUP(Terrain,TerrainTable,3,FALSE)+IF(InstallMethod="Trenched",0,RouteFt/EmtFtPerDay),0))</f>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="7" t="s">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="B46" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="D46" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <f>IF($A$23&lt;&gt;"",$A$23,"")</f>
-      </c>
-      <c r="B45" s="5">
-        <f>IFERROR(VLOOKUP($A$23,ModelTable,14,FALSE),"")</f>
-      </c>
-      <c r="C45" s="5">
-        <f>IFERROR(VLOOKUP($A$23,ModelTable,15,FALSE),"Cu")</f>
-      </c>
-      <c r="D45" s="5">
-        <f>IFERROR($B$23*VLOOKUP($A$23,ModelTable,12,FALSE),0)</f>
-      </c>
-      <c r="E45">
-        <f>IFERROR(VLOOKUP($A$23,ModelTable,13,FALSE),0)</f>
-      </c>
-      <c r="F45" s="5">
-        <f>IF($B$23&gt;0,IF($D$23="DCFC",RunFtDcfc,RunFtL2)+StepFt*(0+($B$23-1)/2),0)</f>
-      </c>
-      <c r="G45" s="9">
-        <f>IF(OR($B$45="",$D$45=0),0,IF($C$45="Cu",VLOOKUP($B$45,WireTable,2,FALSE),VLOOKUP($B$45,WireTable,3,FALSE)))</f>
-      </c>
-      <c r="H45" s="9">
-        <f>$D$45*$E$45*$F$45*$G$45</f>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <f>IF($A$24&lt;&gt;"",$A$24,"")</f>
-      </c>
-      <c r="B46" s="5">
-        <f>IFERROR(VLOOKUP($A$24,ModelTable,14,FALSE),"")</f>
-      </c>
-      <c r="C46" s="5">
-        <f>IFERROR(VLOOKUP($A$24,ModelTable,15,FALSE),"Cu")</f>
-      </c>
-      <c r="D46" s="5">
-        <f>IFERROR($B$24*VLOOKUP($A$24,ModelTable,12,FALSE),0)</f>
-      </c>
-      <c r="E46">
-        <f>IFERROR(VLOOKUP($A$24,ModelTable,13,FALSE),0)</f>
-      </c>
-      <c r="F46" s="5">
-        <f>IF($B$24&gt;0,IF($D$24="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$23=$D$24)*$B$23:$B$23)+($B$24-1)/2),0)</f>
-      </c>
-      <c r="G46" s="9">
-        <f>IF(OR($B$46="",$D$46=0),0,IF($C$46="Cu",VLOOKUP($B$46,WireTable,2,FALSE),VLOOKUP($B$46,WireTable,3,FALSE)))</f>
-      </c>
-      <c r="H46" s="9">
-        <f>$D$46*$E$46*$F$46*$G$46</f>
+      <c r="E46" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
-        <f>IF($A$25&lt;&gt;"",$A$25,"")</f>
+        <f>IF($A$23&lt;&gt;"",$A$23,"")</f>
       </c>
       <c r="B47" s="5">
-        <f>IFERROR(VLOOKUP($A$25,ModelTable,14,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($A$23,ModelTable,14,FALSE),"")</f>
       </c>
       <c r="C47" s="5">
-        <f>IFERROR(VLOOKUP($A$25,ModelTable,15,FALSE),"Cu")</f>
+        <f>IFERROR(VLOOKUP($A$23,ModelTable,15,FALSE),"Cu")</f>
       </c>
       <c r="D47" s="5">
-        <f>IFERROR($B$25*VLOOKUP($A$25,ModelTable,12,FALSE),0)</f>
+        <f>IFERROR($B$23*VLOOKUP($A$23,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E47">
-        <f>IFERROR(VLOOKUP($A$25,ModelTable,13,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($A$23,ModelTable,13,FALSE),0)</f>
       </c>
       <c r="F47" s="5">
-        <f>IF($B$25&gt;0,IF($D$25="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$24=$D$25)*$B$23:$B$24)+($B$25-1)/2),0)</f>
+        <f>IF($B$23&gt;0,IF($D$23="DCFC",RunFtDcfc,RunFtL2)+StepFt*(0+($B$23-1)/2),0)</f>
       </c>
       <c r="G47" s="9">
         <f>IF(OR($B$47="",$D$47=0),0,IF($C$47="Cu",VLOOKUP($B$47,WireTable,2,FALSE),VLOOKUP($B$47,WireTable,3,FALSE)))</f>
@@ -2383,22 +2429,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
-        <f>IF($A$26&lt;&gt;"",$A$26,"")</f>
+        <f>IF($A$24&lt;&gt;"",$A$24,"")</f>
       </c>
       <c r="B48" s="5">
-        <f>IFERROR(VLOOKUP($A$26,ModelTable,14,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($A$24,ModelTable,14,FALSE),"")</f>
       </c>
       <c r="C48" s="5">
-        <f>IFERROR(VLOOKUP($A$26,ModelTable,15,FALSE),"Cu")</f>
+        <f>IFERROR(VLOOKUP($A$24,ModelTable,15,FALSE),"Cu")</f>
       </c>
       <c r="D48" s="5">
-        <f>IFERROR($B$26*VLOOKUP($A$26,ModelTable,12,FALSE),0)</f>
+        <f>IFERROR($B$24*VLOOKUP($A$24,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E48">
-        <f>IFERROR(VLOOKUP($A$26,ModelTable,13,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($A$24,ModelTable,13,FALSE),0)</f>
       </c>
       <c r="F48" s="5">
-        <f>IF($B$26&gt;0,IF($D$26="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$25=$D$26)*$B$23:$B$25)+($B$26-1)/2),0)</f>
+        <f>IF($B$24&gt;0,IF($D$24="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$23=$D$24)*$B$23:$B$23)+($B$24-1)/2),0)</f>
       </c>
       <c r="G48" s="9">
         <f>IF(OR($B$48="",$D$48=0),0,IF($C$48="Cu",VLOOKUP($B$48,WireTable,2,FALSE),VLOOKUP($B$48,WireTable,3,FALSE)))</f>
@@ -2409,22 +2455,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
-        <f>IF($A$27&lt;&gt;"",$A$27,"")</f>
+        <f>IF($A$25&lt;&gt;"",$A$25,"")</f>
       </c>
       <c r="B49" s="5">
-        <f>IFERROR(VLOOKUP($A$27,ModelTable,14,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($A$25,ModelTable,14,FALSE),"")</f>
       </c>
       <c r="C49" s="5">
-        <f>IFERROR(VLOOKUP($A$27,ModelTable,15,FALSE),"Cu")</f>
+        <f>IFERROR(VLOOKUP($A$25,ModelTable,15,FALSE),"Cu")</f>
       </c>
       <c r="D49" s="5">
-        <f>IFERROR($B$27*VLOOKUP($A$27,ModelTable,12,FALSE),0)</f>
+        <f>IFERROR($B$25*VLOOKUP($A$25,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E49">
-        <f>IFERROR(VLOOKUP($A$27,ModelTable,13,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($A$25,ModelTable,13,FALSE),0)</f>
       </c>
       <c r="F49" s="5">
-        <f>IF($B$27&gt;0,IF($D$27="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$26=$D$27)*$B$23:$B$26)+($B$27-1)/2),0)</f>
+        <f>IF($B$25&gt;0,IF($D$25="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$24=$D$25)*$B$23:$B$24)+($B$25-1)/2),0)</f>
       </c>
       <c r="G49" s="9">
         <f>IF(OR($B$49="",$D$49=0),0,IF($C$49="Cu",VLOOKUP($B$49,WireTable,2,FALSE),VLOOKUP($B$49,WireTable,3,FALSE)))</f>
@@ -2435,22 +2481,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
-        <f>IF($A$28&lt;&gt;"",$A$28,"")</f>
+        <f>IF($A$26&lt;&gt;"",$A$26,"")</f>
       </c>
       <c r="B50" s="5">
-        <f>IFERROR(VLOOKUP($A$28,ModelTable,14,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP($A$26,ModelTable,14,FALSE),"")</f>
       </c>
       <c r="C50" s="5">
-        <f>IFERROR(VLOOKUP($A$28,ModelTable,15,FALSE),"Cu")</f>
+        <f>IFERROR(VLOOKUP($A$26,ModelTable,15,FALSE),"Cu")</f>
       </c>
       <c r="D50" s="5">
-        <f>IFERROR($B$28*VLOOKUP($A$28,ModelTable,12,FALSE),0)</f>
+        <f>IFERROR($B$26*VLOOKUP($A$26,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E50">
-        <f>IFERROR(VLOOKUP($A$28,ModelTable,13,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP($A$26,ModelTable,13,FALSE),0)</f>
       </c>
       <c r="F50" s="5">
-        <f>IF($B$28&gt;0,IF($D$28="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$27=$D$28)*$B$23:$B$27)+($B$28-1)/2),0)</f>
+        <f>IF($B$26&gt;0,IF($D$26="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$25=$D$26)*$B$23:$B$25)+($B$26-1)/2),0)</f>
       </c>
       <c r="G50" s="9">
         <f>IF(OR($B$50="",$D$50=0),0,IF($C$50="Cu",VLOOKUP($B$50,WireTable,2,FALSE),VLOOKUP($B$50,WireTable,3,FALSE)))</f>
@@ -2460,23 +2506,23 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>50</v>
+      <c r="A51">
+        <f>IF($A$27&lt;&gt;"",$A$27,"")</f>
+      </c>
+      <c r="B51" s="5">
+        <f>IFERROR(VLOOKUP($A$27,ModelTable,14,FALSE),"")</f>
+      </c>
+      <c r="C51" s="5">
+        <f>IFERROR(VLOOKUP($A$27,ModelTable,15,FALSE),"Cu")</f>
       </c>
       <c r="D51" s="5">
-        <f>IF(NDcfc&gt;0,MAX(1,ROUNDUP(Panel!$F$13*1.25/VLOOKUP($B$51,WireTable,IF($C$51="Cu",4,5),FALSE),0)),0)</f>
+        <f>IFERROR($B$27*VLOOKUP($A$27,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E51">
-        <v>4</v>
+        <f>IFERROR(VLOOKUP($A$27,ModelTable,13,FALSE),0)</f>
       </c>
       <c r="F51" s="5">
-        <v>25</v>
+        <f>IF($B$27&gt;0,IF($D$27="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$26=$D$27)*$B$23:$B$26)+($B$27-1)/2),0)</f>
       </c>
       <c r="G51" s="9">
         <f>IF(OR($B$51="",$D$51=0),0,IF($C$51="Cu",VLOOKUP($B$51,WireTable,2,FALSE),VLOOKUP($B$51,WireTable,3,FALSE)))</f>
@@ -2486,23 +2532,23 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>50</v>
+      <c r="A52">
+        <f>IF($A$28&lt;&gt;"",$A$28,"")</f>
+      </c>
+      <c r="B52" s="5">
+        <f>IFERROR(VLOOKUP($A$28,ModelTable,14,FALSE),"")</f>
+      </c>
+      <c r="C52" s="5">
+        <f>IFERROR(VLOOKUP($A$28,ModelTable,15,FALSE),"Cu")</f>
       </c>
       <c r="D52" s="5">
-        <f>IF(TxKvaSuggested&gt;0,MAX(1,ROUNDUP(Panel!$F$37*1.25/VLOOKUP($B$52,WireTable,IF($C$52="Cu",4,5),FALSE),0)),0)</f>
+        <f>IFERROR($B$28*VLOOKUP($A$28,ModelTable,12,FALSE),0)</f>
       </c>
       <c r="E52">
-        <v>4</v>
+        <f>IFERROR(VLOOKUP($A$28,ModelTable,13,FALSE),0)</f>
       </c>
       <c r="F52" s="5">
-        <v>15</v>
+        <f>IF($B$28&gt;0,IF($D$28="DCFC",RunFtDcfc,RunFtL2)+StepFt*(SUMPRODUCT(($D$23:$D$27=$D$28)*$B$23:$B$27)+($B$28-1)/2),0)</f>
       </c>
       <c r="G52" s="9">
         <f>IF(OR($B$52="",$D$52=0),0,IF($C$52="Cu",VLOOKUP($B$52,WireTable,2,FALSE),VLOOKUP($B$52,WireTable,3,FALSE)))</f>
@@ -2513,22 +2559,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D53" s="5">
-        <f>IF(NumL2&gt;0,MAX(1,ROUNDUP(IF(TxKvaSuggested&gt;0,TxKvaSuggested*1000/(208*SQRT(3)),Panel!$F$26)*1.25/VLOOKUP($B$53,WireTable,IF($C$53="Cu",4,5),FALSE),0)),0)</f>
+        <f>IF(NDcfc&gt;0,MAX(1,ROUNDUP(Panel!$F$13*1.25/VLOOKUP($B$53,WireTable,IF($C$53="Cu",4,5),FALSE),0)),0)</f>
       </c>
       <c r="E53">
         <v>4</v>
       </c>
       <c r="F53" s="5">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G53" s="9">
         <f>IF(OR($B$53="",$D$53=0),0,IF($C$53="Cu",VLOOKUP($B$53,WireTable,2,FALSE),VLOOKUP($B$53,WireTable,3,FALSE)))</f>
@@ -2538,226 +2584,281 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="A54" t="s">
         <v>55</v>
       </c>
-      <c r="H54" s="10">
-        <f>SUM(H45:H53)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="5">
+        <f>IF(TxKvaSuggested&gt;0,MAX(1,ROUNDUP(Panel!$F$37*1.25/VLOOKUP($B$54,WireTable,IF($C$54="Cu",4,5),FALSE),0)),0)</f>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+      <c r="F54" s="5">
+        <v>15</v>
+      </c>
+      <c r="G54" s="9">
+        <f>IF(OR($B$54="",$D$54=0),0,IF($C$54="Cu",VLOOKUP($B$54,WireTable,2,FALSE),VLOOKUP($B$54,WireTable,3,FALSE)))</f>
+      </c>
+      <c r="H54" s="9">
+        <f>$D$54*$E$54*$F$54*$G$54</f>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="5">
+        <f>IF(NumL2&gt;0,MAX(1,ROUNDUP(IF(TxKvaSuggested&gt;0,TxKvaSuggested*1000/(208*SQRT(3)),Panel!$F$26)*1.25/VLOOKUP($B$55,WireTable,IF($C$55="Cu",4,5),FALSE),0)),0)</f>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55" s="5">
+        <v>15</v>
+      </c>
+      <c r="G55" s="9">
+        <f>IF(OR($B$55="",$D$55=0),0,IF($C$55="Cu",VLOOKUP($B$55,WireTable,2,FALSE),VLOOKUP($B$55,WireTable,3,FALSE)))</f>
+      </c>
+      <c r="H55" s="9">
+        <f>$D$55*$E$55*$F$55*$G$55</f>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="H56" s="11">
+        <f>SUM(H47:H55)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B59" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="5">
         <f>LaborDays</f>
       </c>
-      <c r="C58" s="11">
+      <c r="C60" s="12">
         <f>LaborDayRate</f>
-      </c>
-      <c r="D58" s="9">
-        <f>$B$58*$C$58</f>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5">
-        <v>0</v>
-      </c>
-      <c r="C59" s="11">
-        <v>0</v>
-      </c>
-      <c r="D59" s="9">
-        <f>$B$59*$C$59</f>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5">
-        <v>0</v>
-      </c>
-      <c r="C60" s="11">
-        <v>0</v>
       </c>
       <c r="D60" s="9">
         <f>$B$60*$C$60</f>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D61" s="10">
-        <f>SUM(D58:D60)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5">
+        <v>0</v>
+      </c>
+      <c r="C61" s="12">
+        <v>0</v>
+      </c>
+      <c r="D61" s="9">
+        <f>$B$61*$C$61</f>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5">
+        <v>0</v>
+      </c>
+      <c r="C62" s="12">
+        <v>0</v>
+      </c>
+      <c r="D62" s="9">
+        <f>$B$62*$C$62</f>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>65</v>
+      <c r="D63" s="11">
+        <f>SUM(D60:D62)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B74" s="5">
         <v>1</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B73" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" s="11">
-        <v>39.99</v>
+      <c r="C74" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B75" s="5">
-        <v>5</v>
+        <v>78</v>
+      </c>
+      <c r="B75" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B76" s="11">
+        <v>79</v>
+      </c>
+      <c r="B76" s="12">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B78">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80">
         <f>AdaVan&amp;" van + "&amp;AdaStd&amp;" standard + "&amp;AdaAmb&amp;" ambulatory"</f>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79">
-        <f>IF(NDcfc&gt;0,SgSuggested&amp;"A switchgear @ 480V","208V service")&amp;IF(TxKvaSuggested&gt;0," + "&amp;TxKvaSuggested&amp;" kVA step-down TX","")</f>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B80" s="14">
-        <f>TotalCost</f>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" s="10">
+        <v>83</v>
+      </c>
+      <c r="B81">
+        <f>IF(NDcfc&gt;0,SgSuggested&amp;"A switchgear @ 480V","208V service")&amp;IF(TxKvaSuggested&gt;0," + "&amp;TxKvaSuggested&amp;" kVA step-down TX","")</f>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="14">
+        <f>TotalCost</f>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83" s="11">
         <f>CustomerTotal</f>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" sqref="A23:A28">
       <formula1>RateCard!$A$4:$A$33</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="B39">
       <formula1>"flat,sloped,hilly,rocky"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B45:B53">
+    <dataValidation type="list" sqref="B40">
+      <formula1>"Trenched,Surface EMT,Hybrid"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B47:B55">
       <formula1>RateCard!$A$129:$A$153</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B64:B69">
+    <dataValidation type="list" sqref="B66:B71">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C45:C53">
+    <dataValidation type="list" allowBlank="1" sqref="C47:C55">
       <formula1>"Cu,Al"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2768,7 +2869,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="114" customWidth="1"/>
@@ -2776,152 +2877,197 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="63" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="63" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="63" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="63" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="63" t="s">
-        <v>245</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>373</v>
+      <c r="A14" s="63" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="63" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="63" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="63" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="63" t="s">
-        <v>245</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>377</v>
+      <c r="A19" s="63" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="63" t="s">
-        <v>378</v>
+      <c r="A20" s="16" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="63" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="63" t="s">
-        <v>245</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>380</v>
+      <c r="A23" s="63" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="63" t="s">
-        <v>381</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="63" t="s">
-        <v>382</v>
+      <c r="A25" s="16" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="63" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="63" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="63" t="s">
-        <v>385</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="63" t="s">
-        <v>386</v>
+      <c r="A29" s="16" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="63" t="s">
-        <v>387</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="63" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="63" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="63" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="63" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="63" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="63" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="63" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +3078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2942,12 +3088,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2958,16 +3104,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3092,7 +3238,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F11">
         <f>SUM(F5:F10)</f>
@@ -3100,7 +3246,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F12">
         <f>IF(AND(NDcfc&gt;0,NumL2&gt;0),TxKvaConnected*1000/(480*SQRT(3)),0)</f>
@@ -3108,7 +3254,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F13">
         <f>F11+F12</f>
@@ -3116,7 +3262,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F14">
         <f>F13*1.25</f>
@@ -3124,23 +3270,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="F15">
-        <f>IF(NDcfc&gt;0,INDEX(SgSizes,MIN(ROWS(SgSizes),COUNTIF(SgSizes,"&lt;"&amp;F14)+1)),0)</f>
+        <f>IF(NDcfc&gt;0,IF(ISNUMBER($D$15),$D$15,INDEX(SgSizes,MIN(ROWS(SgSizes),COUNTIF(SgSizes,"&lt;"&amp;F14)+1))),0)</f>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F16" s="9">
-        <f>IF(NDcfc&gt;0,VLOOKUP(SgSuggested,SgTable,2,FALSE),0)</f>
+        <f>IF(NDcfc&gt;0,IFERROR(VLOOKUP(SgSuggested,SgTable,2,FALSE),0),0)</f>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3151,16 +3301,16 @@
         <v>19</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3285,7 +3435,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <f>SUM(F20:F25)</f>
@@ -3293,7 +3443,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F27">
         <f>F26*1.25</f>
@@ -3301,15 +3451,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="10" t="s">
         <v>97</v>
       </c>
       <c r="F28">
-        <f>IF(NumL2&gt;0,INDEX(PnlSizes,MIN(ROWS(PnlSizes),COUNTIF(PnlSizes,"&lt;"&amp;F27)+1)),0)</f>
+        <f>IF(NumL2&gt;0,IF(ISNUMBER($D$28),$D$28,INDEX(PnlSizes,MIN(ROWS(PnlSizes),COUNTIF(PnlSizes,"&lt;"&amp;F27)+1))),0)</f>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F29">
         <f>IF(NumL2=0,"—",IF(F28&gt;=1000,"Distribution panel","Sub-panel"))</f>
@@ -3317,20 +3471,20 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F30" s="9">
-        <f>IF(NumL2&gt;0,VLOOKUP(F28,PnlTable,2,FALSE),0)</f>
+        <f>IF(NumL2&gt;0,IFERROR(VLOOKUP(F28,PnlTable,2,FALSE),0),0)</f>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F33">
         <f>IF(AND(NDcfc&gt;0,NumL2&gt;0),F26*208*SQRT(3)/1000,0)</f>
@@ -3338,7 +3492,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F34">
         <f>F33*1.25</f>
@@ -3346,23 +3500,27 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="F35">
-        <f>IF(F33&gt;0,INDEX(TxSizes,MIN(ROWS(TxSizes),COUNTIF(TxSizes,"&lt;"&amp;F34)+1)),0)</f>
+        <f>IF(F33&gt;0,IF(ISNUMBER($D$35),$D$35,INDEX(TxSizes,MIN(ROWS(TxSizes),COUNTIF(TxSizes,"&lt;"&amp;F34)+1))),0)</f>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F36" s="9">
-        <f>IF(F35&gt;0,VLOOKUP(F35,TxTable,2,FALSE),0)</f>
+        <f>IF(F35&gt;0,IFERROR(VLOOKUP(F35,TxTable,2,FALSE),0),0)</f>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F37">
         <f>IF(F35&gt;0,F35*1000/(480*SQRT(3)),0)</f>
@@ -3370,7 +3528,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F38">
         <f>IF(F35&gt;0,INDEX(StdBrk,MIN(ROWS(StdBrk),COUNTIF(StdBrk,"&lt;"&amp;F37*1.25)+1)),0)</f>
@@ -3378,7 +3536,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F39" s="9">
         <f>IF(F38&gt;0,IFERROR(VLOOKUP(F38,BrkTbl480,2,FALSE),0),0)</f>
@@ -3386,7 +3544,7 @@
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3394,19 +3552,19 @@
         <v>18</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3531,7 +3689,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F49" s="9">
         <f>SUM(F43:F48)+F39</f>
@@ -3539,7 +3697,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F51" s="17">
         <f>F16+F30+F36+F49</f>
@@ -3547,10 +3705,26 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>114</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="D15">
+      <formula1>SgSizes</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D28">
+      <formula1>PnlSizes</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D35">
+      <formula1>TxSizes</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3584,7 +3758,7 @@
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -3602,30 +3776,30 @@
     </row>
     <row r="2" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R2" s="20" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N3">
         <f>SgSuggested&amp;" A 3P"</f>
@@ -3639,19 +3813,19 @@
     </row>
     <row r="4" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D4" s="21" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E4">
         <f>"UTILITY"</f>
       </c>
       <c r="H4" s="21" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="N4">
         <f>SgSuggested&amp;" A"</f>
@@ -3665,22 +3839,22 @@
     </row>
     <row r="5" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D5" s="21" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="S5">
         <f>IF(Intake!$D$25="DCFC",Intake!$B$25*IFERROR(VLOOKUP(Intake!$A$25,ModelTable,7,FALSE),0),0)</f>
@@ -3699,40 +3873,40 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="S7">
         <f>IF(Intake!$D$27="DCFC",Intake!$B$27*IFERROR(VLOOKUP(Intake!$A$27,ModelTable,7,FALSE),0),0)</f>
@@ -3743,7 +3917,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B8" s="23">
         <v>1</v>
@@ -3780,7 +3954,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S8">
         <f>IF(Intake!$D$28="DCFC",Intake!$B$28*IFERROR(VLOOKUP(Intake!$A$28,ModelTable,7,FALSE),0),0)</f>
@@ -3791,7 +3965,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B9" s="23">
         <v>3</v>
@@ -3820,10 +3994,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="S9">
         <f>SUM(S3:S8)</f>
@@ -3831,7 +4005,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B10" s="23">
         <v>5</v>
@@ -3860,12 +4034,12 @@
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B11" s="23">
         <v>7</v>
@@ -3902,12 +4076,12 @@
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B12" s="23">
         <v>9</v>
@@ -3936,7 +4110,7 @@
         <v>10</v>
       </c>
       <c r="P12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -3968,7 +4142,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B13" s="23">
         <v>11</v>
@@ -3997,7 +4171,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S13">
         <v>2</v>
@@ -4029,7 +4203,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B14" s="23">
         <v>13</v>
@@ -4066,7 +4240,7 @@
         <v>14</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S14">
         <v>3</v>
@@ -4098,7 +4272,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B15" s="23">
         <v>15</v>
@@ -4127,7 +4301,7 @@
         <v>16</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S15">
         <v>4</v>
@@ -4159,7 +4333,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B16" s="23">
         <v>17</v>
@@ -4188,7 +4362,7 @@
         <v>18</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -4220,7 +4394,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B17" s="23">
         <v>19</v>
@@ -4257,7 +4431,7 @@
         <v>20</v>
       </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -4289,7 +4463,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B18" s="23">
         <v>21</v>
@@ -4318,7 +4492,7 @@
         <v>22</v>
       </c>
       <c r="P18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -4350,7 +4524,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B19" s="23">
         <v>23</v>
@@ -4379,7 +4553,7 @@
         <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -4411,7 +4585,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B20" s="23">
         <v>25</v>
@@ -4448,7 +4622,7 @@
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -4480,7 +4654,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B21" s="23">
         <v>27</v>
@@ -4509,7 +4683,7 @@
         <v>28</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -4541,7 +4715,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B22" s="23">
         <v>29</v>
@@ -4570,7 +4744,7 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S22">
         <v>11</v>
@@ -4602,7 +4776,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B23" s="23">
         <v>31</v>
@@ -4639,7 +4813,7 @@
         <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S23">
         <v>12</v>
@@ -4671,7 +4845,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B24" s="23">
         <v>33</v>
@@ -4700,7 +4874,7 @@
         <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S24">
         <v>13</v>
@@ -4732,7 +4906,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B25" s="23">
         <v>35</v>
@@ -4761,7 +4935,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S25">
         <v>14</v>
@@ -4793,7 +4967,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B26" s="23">
         <v>37</v>
@@ -4830,7 +5004,7 @@
         <v>38</v>
       </c>
       <c r="P26" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S26">
         <v>15</v>
@@ -4862,7 +5036,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B27" s="23">
         <v>39</v>
@@ -4891,7 +5065,7 @@
         <v>40</v>
       </c>
       <c r="P27" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S27">
         <v>16</v>
@@ -4923,7 +5097,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B28" s="23">
         <v>41</v>
@@ -4952,12 +5126,12 @@
         <v>42</v>
       </c>
       <c r="P28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B29" s="23">
         <v>43</v>
@@ -4994,12 +5168,12 @@
         <v>44</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B30" s="23">
         <v>45</v>
@@ -5028,12 +5202,12 @@
         <v>46</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B31" s="23">
         <v>47</v>
@@ -5062,12 +5236,12 @@
         <v>48</v>
       </c>
       <c r="P31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F33" s="25">
         <f>SUM(F8:G31)</f>
@@ -5082,7 +5256,7 @@
       </c>
       <c r="K33" s="25"/>
       <c r="L33" s="21" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M33" s="21"/>
       <c r="N33" s="25">
@@ -5091,7 +5265,7 @@
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F34" s="25">
         <f>F33*1.25</f>
@@ -5106,7 +5280,7 @@
       </c>
       <c r="K34" s="25"/>
       <c r="L34" s="21" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M34" s="21"/>
       <c r="N34" s="25">
@@ -5115,7 +5289,7 @@
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F35" s="25">
         <f>MAX($F$34,$H$34,$J$34)</f>
@@ -5130,7 +5304,7 @@
       </c>
       <c r="K35" s="25"/>
       <c r="L35" s="21" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="M35" s="21"/>
       <c r="N35" s="26">
@@ -5139,7 +5313,7 @@
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F36" s="26">
         <f>F35/(480/SQRT(3))</f>
@@ -5154,7 +5328,7 @@
       </c>
       <c r="K36" s="26"/>
       <c r="L36" s="21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="M36" s="21"/>
       <c r="N36">
@@ -5222,7 +5396,7 @@
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -5240,30 +5414,30 @@
     </row>
     <row r="2" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R2" s="20" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N3">
         <f>Panel!$F$28&amp;" A 3P"</f>
@@ -5277,19 +5451,19 @@
     </row>
     <row r="4" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D4" s="21" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E4">
         <f>IF(TxKvaSuggested&gt;0,"EV_MAIN VIA "&amp;TxKvaSuggested&amp;" KVA XFMR","UTILITY")</f>
       </c>
       <c r="H4" s="21" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="N4">
         <f>Panel!$F$28&amp;" A"</f>
@@ -5303,22 +5477,22 @@
     </row>
     <row r="5" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D5" s="21" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="S5">
         <f>IF(Intake!$D$25="L2",Intake!$B$25*IFERROR(VLOOKUP(Intake!$A$25,ModelTable,7,FALSE),0),0)</f>
@@ -5337,40 +5511,40 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="N7" s="22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O7" s="22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="S7">
         <f>IF(Intake!$D$27="L2",Intake!$B$27*IFERROR(VLOOKUP(Intake!$A$27,ModelTable,7,FALSE),0),0)</f>
@@ -5381,7 +5555,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B8" s="23">
         <v>1</v>
@@ -5418,7 +5592,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S8">
         <f>IF(Intake!$D$28="L2",Intake!$B$28*IFERROR(VLOOKUP(Intake!$A$28,ModelTable,7,FALSE),0),0)</f>
@@ -5429,7 +5603,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B9" s="23">
         <v>3</v>
@@ -5458,10 +5632,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="S9">
         <f>SUM(S3:S8)</f>
@@ -5469,7 +5643,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B10" s="23">
         <v>5</v>
@@ -5506,12 +5680,12 @@
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B11" s="23">
         <v>7</v>
@@ -5540,12 +5714,12 @@
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B12" s="23">
         <v>9</v>
@@ -5582,7 +5756,7 @@
         <v>10</v>
       </c>
       <c r="P12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -5614,7 +5788,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B13" s="23">
         <v>11</v>
@@ -5643,7 +5817,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S13">
         <v>2</v>
@@ -5675,7 +5849,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B14" s="23">
         <v>13</v>
@@ -5712,7 +5886,7 @@
         <v>14</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S14">
         <v>3</v>
@@ -5744,7 +5918,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B15" s="23">
         <v>15</v>
@@ -5773,7 +5947,7 @@
         <v>16</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S15">
         <v>4</v>
@@ -5805,7 +5979,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B16" s="23">
         <v>17</v>
@@ -5842,7 +6016,7 @@
         <v>18</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -5874,7 +6048,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B17" s="23">
         <v>19</v>
@@ -5903,7 +6077,7 @@
         <v>20</v>
       </c>
       <c r="P17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -5935,7 +6109,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B18" s="23">
         <v>21</v>
@@ -5972,7 +6146,7 @@
         <v>22</v>
       </c>
       <c r="P18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S18">
         <v>7</v>
@@ -6004,7 +6178,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B19" s="23">
         <v>23</v>
@@ -6033,7 +6207,7 @@
         <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -6065,7 +6239,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B20" s="23">
         <v>25</v>
@@ -6102,7 +6276,7 @@
         <v>26</v>
       </c>
       <c r="P20" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -6134,7 +6308,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B21" s="23">
         <v>27</v>
@@ -6163,7 +6337,7 @@
         <v>28</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -6195,7 +6369,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B22" s="23">
         <v>29</v>
@@ -6232,7 +6406,7 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S22">
         <v>11</v>
@@ -6264,7 +6438,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B23" s="23">
         <v>31</v>
@@ -6293,7 +6467,7 @@
         <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S23">
         <v>12</v>
@@ -6325,7 +6499,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B24" s="23">
         <v>33</v>
@@ -6362,7 +6536,7 @@
         <v>34</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S24">
         <v>13</v>
@@ -6394,7 +6568,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B25" s="23">
         <v>35</v>
@@ -6423,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S25">
         <v>14</v>
@@ -6455,7 +6629,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B26" s="23">
         <v>37</v>
@@ -6492,7 +6666,7 @@
         <v>38</v>
       </c>
       <c r="P26" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S26">
         <v>15</v>
@@ -6524,7 +6698,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B27" s="23">
         <v>39</v>
@@ -6553,7 +6727,7 @@
         <v>40</v>
       </c>
       <c r="P27" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S27">
         <v>16</v>
@@ -6585,7 +6759,7 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B28" s="23">
         <v>41</v>
@@ -6622,7 +6796,7 @@
         <v>42</v>
       </c>
       <c r="P28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S28">
         <v>17</v>
@@ -6654,7 +6828,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B29" s="23">
         <v>43</v>
@@ -6683,7 +6857,7 @@
         <v>44</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S29">
         <v>18</v>
@@ -6715,7 +6889,7 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B30" s="23">
         <v>45</v>
@@ -6752,7 +6926,7 @@
         <v>46</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S30">
         <v>19</v>
@@ -6784,7 +6958,7 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B31" s="23">
         <v>47</v>
@@ -6813,7 +6987,7 @@
         <v>48</v>
       </c>
       <c r="P31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S31">
         <v>20</v>
@@ -6874,7 +7048,7 @@
     </row>
     <row r="33" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F33" s="25">
         <f>SUM(F8:G31)</f>
@@ -6889,7 +7063,7 @@
       </c>
       <c r="K33" s="25"/>
       <c r="L33" s="21" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M33" s="21"/>
       <c r="N33" s="25">
@@ -6925,7 +7099,7 @@
     </row>
     <row r="34" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F34" s="25">
         <f>F33*1.25</f>
@@ -6940,7 +7114,7 @@
       </c>
       <c r="K34" s="25"/>
       <c r="L34" s="21" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M34" s="21"/>
       <c r="N34" s="25">
@@ -6976,7 +7150,7 @@
     </row>
     <row r="35" spans="3:27" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F35" s="25">
         <f>MAX($F$34,$H$34,$J$34)</f>
@@ -6991,7 +7165,7 @@
       </c>
       <c r="K35" s="25"/>
       <c r="L35" s="21" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="M35" s="21"/>
       <c r="N35" s="26">
@@ -7027,7 +7201,7 @@
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F36" s="26">
         <f>F35/120</f>
@@ -7042,7 +7216,7 @@
       </c>
       <c r="K36" s="26"/>
       <c r="L36" s="21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="M36" s="21"/>
       <c r="N36">
@@ -7084,7 +7258,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -7094,17 +7268,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B4">
         <f>LaborDays</f>
@@ -7112,13 +7286,13 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B6" s="29"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B7" s="9">
         <f>WireTotal+SUM(Intake!E23:E28)</f>
@@ -7126,7 +7300,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B8" s="9">
         <f>GearTotal</f>
@@ -7134,7 +7308,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B9" s="9">
         <f>TrenchFt*TrenchRate*VLOOKUP(Terrain,TerrainTable,2,FALSE)</f>
@@ -7142,232 +7316,240 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B10" s="9">
-        <f>IF(NTotal&gt;0,CivilBase,0)+NDcfc*CivilDcfc+NumL2*CivilL2</f>
+        <f>IF(InstallMethod="Trenched",0,(ROUNDUP(RouteFt/10,0)+1)*EmtRackCost+ROUNDUP((SUMPRODUCT(Intake!$D$47:$D$52,Intake!$F$47:$F$52)+IF(InstallMethod="Surface EMT",SUMPRODUCT(Intake!$D$53:$D$55,Intake!$F$53:$F$55),0))/10,0)*EmtStrapCost)</f>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B11" s="9">
-        <f>NDcfc*SignageDcfc+NumL2*SignageL2</f>
+        <f>IF(NTotal&gt;0,CivilBase,0)+NDcfc*CivilDcfc+NumL2*CivilL2</f>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B12" s="9">
-        <f>AdaCost</f>
+        <f>NDcfc*SignageDcfc+NumL2*SignageL2</f>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B13" s="9">
-        <f>TrenchFt*VLOOKUP(Terrain,TerrainTable,5,FALSE)</f>
+        <f>AdaCost</f>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="B14" s="9">
-        <f>IF(IncGpr="Yes",MAX(1,ROUNDUP(TrenchFt/GprFtPerDay,0))*GprDayRate,0)</f>
+        <f>TrenchFt*VLOOKUP(Terrain,TerrainTable,5,FALSE)</f>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="B15" s="9">
-        <f>IF(NTotal&gt;0,EquipBase+EquipPerDay*LaborDays,0)</f>
+        <f>IF(OR(IncGpr="No",TrenchFt&lt;=0),0,MAX(1,ROUNDUP(TrenchFt/GprFtPerDay,0))*GprDayRate)</f>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B16" s="9">
-        <f>IF(IncPermits="Yes",200+60*NTotal,0)</f>
+        <f>IF(NTotal&lt;=0,0,IF(InstallMethod="Surface EMT",EquipBaseEmt+EquipPerDayEmt*LaborDays,EquipBase+EquipPerDay*LaborDays))</f>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B17" s="9">
+        <f>IF(IncPermits="Yes",200+60*NTotal,0)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="9">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,2500+TransformerPad,800),0)</f>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B18" s="9">
-        <f>SUM(B7:B17)</f>
-      </c>
-    </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>168</v>
+      <c r="A19" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="B19" s="9">
-        <f>B18*ContingencyPct</f>
+        <f>SUM(B7:B18)</f>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20" s="10">
-        <f>B18+B19</f>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="9">
-        <f>LaborBase*(1+ContingencyPct)</f>
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="9">
+        <f>B19*ContingencyPct</f>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="11">
+        <f>B19+B20</f>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B23" s="9">
+        <f>LaborBase*(1+ContingencyPct)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>178</v>
+      </c>
+      <c r="B24" s="9">
         <f>ConstructionTotal*TaxPct</f>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="B24" s="9">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="9">
         <f>ConstructionTotal+LaborCost</f>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="29"/>
-    </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" s="9">
-        <f>IF(IncHardware="Yes",SUM(Intake!F23:F28)*HardwareFactor,0)</f>
-      </c>
+      <c r="A27" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="29"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B28" s="9">
-        <f>IF(IncHardware="Yes",CommDcfc*NDcfc+CommL2*NumL2,0)</f>
+        <f>IF(IncHardware="Yes",SUM(Intake!F23:F28)*HardwareFactor,0)</f>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B29" s="9">
-        <f>IF(IncHardware="Yes",NPorts*NetworkFeeMo*12*ContractYears,0)</f>
+        <f>IF(IncHardware="Yes",CommDcfc*NDcfc+CommL2*NumL2,0)</f>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B30" s="9">
-        <f>IF(IncHardware="Yes",ServicePlanYr*ContractYears,0)</f>
+        <f>IF(IncHardware="Yes",NPorts*NetworkFeeMo*12*ContractYears,0)</f>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B31" s="9">
-        <f>B27*TaxPct</f>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B33" s="29"/>
+        <f>IF(IncHardware="Yes",ServicePlanYr*ContractYears,0)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="9">
+        <f>B28*TaxPct</f>
+      </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="9">
-        <f>IF(IncSitePlan="Yes",2500+150*NTotal+IF(NDcfc&gt;0,1000,0),0)</f>
-      </c>
+      <c r="A34" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="29"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="B35" s="9">
+        <f>IF(IncSitePlan="Yes",2500+150*NTotal+IF(NDcfc&gt;0,1000,0),0)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="9">
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,6000+900*NDcfc+150*NumL2,2500+150*NumL2),0)</f>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>181</v>
-      </c>
-      <c r="B36" s="9">
-        <f>C36*PmRate</f>
-      </c>
-      <c r="C36" s="31">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="9">
+        <f>C37*PmRate</f>
+      </c>
+      <c r="C37" s="31">
         <f>IF(IncCpm="Yes",MAX(24,ROUND(CpmPct*Valuation/PmRate,0)),0)</f>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>182</v>
-      </c>
-      <c r="B37" s="9">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="9">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,500+0.02*Valuation,300),0)</f>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B38" s="9">
-        <f>SUM(B34:B37)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B40" s="14">
-        <f>ConstructionTotal+LaborCost+B23+B27+B28+B29+B30+B31+B38</f>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B39" s="9">
+        <f>SUM(B35:B38)</f>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>185</v>
-      </c>
-      <c r="B41" s="9">
+      <c r="A41" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" s="14">
+        <f>ConstructionTotal+LaborCost+B24+B28+B29+B30+B31+B32+B39</f>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>192</v>
+      </c>
+      <c r="B42" s="9">
         <f>-RebateAmt</f>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="32">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="32">
         <f>TotalCost-RebateAmt</f>
       </c>
     </row>
@@ -7400,33 +7582,33 @@
   <sheetData>
     <row r="2" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="33" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="38" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C3" s="39">
         <v>1</v>
       </c>
       <c r="D3" s="40">
-        <f>Estimate!B7</f>
+        <f>Estimate!B7+Estimate!B10</f>
       </c>
       <c r="E3" s="41">
         <f>ContingencyPct</f>
@@ -7438,13 +7620,13 @@
         <f>F3*C3</f>
       </c>
       <c r="J3" s="43" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K3" s="44"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="38" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C4" s="39">
         <v>1</v>
@@ -7462,7 +7644,7 @@
         <f>F4*C4</f>
       </c>
       <c r="J4" s="45" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K4" s="46">
         <f>IF(LaborDays&gt;0,LaborBase/LaborDays,0)</f>
@@ -7470,7 +7652,7 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C5" s="39">
         <v>1</v>
@@ -7488,7 +7670,7 @@
         <f>F5*C5</f>
       </c>
       <c r="J5" s="45" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="K5" s="47">
         <f>LaborDays</f>
@@ -7496,13 +7678,13 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="40">
-        <f>Estimate!B11</f>
+        <f>Estimate!B12</f>
       </c>
       <c r="E6" s="41">
         <f>ContingencyPct</f>
@@ -7514,7 +7696,7 @@
         <f>F6*C6</f>
       </c>
       <c r="J6" s="45" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K6" s="47">
         <f>K5/30</f>
@@ -7522,7 +7704,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C7" s="39">
         <v>1</v>
@@ -7540,7 +7722,7 @@
         <f>F7*C7</f>
       </c>
       <c r="J7" s="48" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K7" s="49">
         <f>K5*K4</f>
@@ -7548,13 +7730,13 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="38" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C8" s="39">
         <v>1</v>
       </c>
       <c r="D8" s="40">
-        <f>Estimate!B10</f>
+        <f>Estimate!B11</f>
       </c>
       <c r="E8" s="41">
         <f>ContingencyPct</f>
@@ -7568,13 +7750,13 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="38" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C9" s="39">
         <v>1</v>
       </c>
       <c r="D9" s="40">
-        <f>Estimate!B12</f>
+        <f>Estimate!B13</f>
       </c>
       <c r="E9" s="41">
         <f>ContingencyPct</f>
@@ -7588,13 +7770,13 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="38" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C10" s="39">
         <v>1</v>
       </c>
       <c r="D10" s="40">
-        <f>Estimate!B13</f>
+        <f>Estimate!B14</f>
       </c>
       <c r="E10" s="41">
         <f>ContingencyPct</f>
@@ -7608,13 +7790,13 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="38" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C11" s="39">
         <v>1</v>
       </c>
       <c r="D11" s="40">
-        <f>Estimate!B16</f>
+        <f>Estimate!B17</f>
       </c>
       <c r="E11" s="41">
         <f>ContingencyPct</f>
@@ -7634,7 +7816,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="40">
-        <f>Estimate!B17+Estimate!B14</f>
+        <f>Estimate!B18+Estimate!B15</f>
       </c>
       <c r="E12" s="41">
         <f>ContingencyPct</f>
@@ -7648,13 +7830,13 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C13" s="39">
         <v>1</v>
       </c>
       <c r="D13" s="40">
-        <f>Estimate!B15</f>
+        <f>Estimate!B16</f>
       </c>
       <c r="E13" s="41">
         <f>ContingencyPct</f>
@@ -7668,13 +7850,13 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="38" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C14" s="39">
         <v>1</v>
       </c>
       <c r="D14" s="40">
-        <f>Estimate!B34+Estimate!B35+Estimate!B36</f>
+        <f>Estimate!B35+Estimate!B36+Estimate!B37</f>
       </c>
       <c r="E14" s="41">
         <v>0</v>
@@ -7699,7 +7881,7 @@
     <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="55" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C17" s="55"/>
       <c r="D17" s="55"/>
@@ -7709,7 +7891,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="38" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C18" s="39">
         <f>K5</f>
@@ -7740,7 +7922,7 @@
     <row r="20" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="48"/>
       <c r="C20" s="56" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="56"/>
@@ -7761,62 +7943,110 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4">
+        <f>NumL2</f>
+      </c>
+      <c r="C4">
+        <f>IF($B$4&lt;=0,0,IF($B$4&lt;=100,1,1+ROUNDUP(($B$4-100)/300,0)))</f>
+      </c>
+      <c r="D4">
+        <f>IF($B$4&lt;=4,0,IF($B$4&lt;=50,1,IF($B$4&lt;=75,2,IF($B$4&lt;=100,3,3+ROUNDUP(($B$4-100)/60,0)))))</f>
+      </c>
+      <c r="E4">
+        <f>IF($B$4&lt;=25,0,IF($B$4&lt;=50,1,IF($B$4&lt;=75,2,IF($B$4&lt;=100,3,3+ROUNDUP(($B$4-100)/50,0)))))</f>
+      </c>
+      <c r="F4">
+        <f>C4+D4+E4</f>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5">
+        <f>NDcfc</f>
+      </c>
+      <c r="C5">
+        <f>IF($B$5&lt;=0,0,IF($B$5&lt;=100,1,1+ROUNDUP(($B$5-100)/300,0)))</f>
+      </c>
+      <c r="D5">
+        <f>IF($B$5&lt;=4,0,IF($B$5&lt;=50,1,IF($B$5&lt;=75,2,IF($B$5&lt;=100,3,3+ROUNDUP(($B$5-100)/60,0)))))</f>
+      </c>
+      <c r="E5">
+        <f>IF($B$5&lt;=25,0,IF($B$5&lt;=50,1,IF($B$5&lt;=75,2,IF($B$5&lt;=100,3,3+ROUNDUP(($B$5-100)/50,0)))))</f>
+      </c>
+      <c r="F5">
+        <f>C5+D5+E5</f>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="3">
         <f>NTotal</f>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4">
-        <f>IF(NTotal&lt;=0,0,IF(NTotal&lt;=100,1,1+ROUNDUP((NTotal-100)/300,0)))</f>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5">
-        <f>IF(NTotal&lt;=4,0,IF(NTotal&lt;=50,1,IF(NTotal&lt;=75,2,IF(NTotal&lt;=100,3,3+ROUNDUP((NTotal-100)/60,0)))))</f>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6">
-        <f>IF(NTotal&lt;=25,0,IF(NTotal&lt;=50,1,IF(NTotal&lt;=75,2,IF(NTotal&lt;=100,3,3+ROUNDUP((NTotal-100)/50,0)))))</f>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7">
-        <f>AdaVan+AdaStd+AdaAmb</f>
+      <c r="C6" s="3">
+        <f>C4+C5</f>
+      </c>
+      <c r="D6" s="3">
+        <f>D4+D5</f>
+      </c>
+      <c r="E6" s="3">
+        <f>E4+E5</f>
+      </c>
+      <c r="F6" s="3">
+        <f>C6+D6+E6</f>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B9">
         <f>VLOOKUP(Terrain,TerrainTable,4,FALSE)</f>
@@ -7824,7 +8054,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B10" s="9">
         <f>(AdaVan*AdaVanCost+AdaStd*AdaStdCost+AdaAmb*AdaAmbCost)*VLOOKUP(Terrain,TerrainTable,4,FALSE)+IF(NTotal&gt;0,AdaRampCost,0)</f>
@@ -7832,130 +8062,135 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="58" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D15" s="59" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="59" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D17" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="59" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C19" s="59" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D19" s="59" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="60" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="60" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="60" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="60" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="60" t="s">
-        <v>238</v>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="60" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -7976,26 +8211,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B4">
         <f>2</f>
@@ -8004,12 +8239,12 @@
         <f>4</f>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <f>IF(IncSitePlan="Yes",5+ROUNDUP(NTotal/4,0),0)</f>
@@ -8018,12 +8253,12 @@
         <f>IF(IncSitePlan="Yes",10+ROUNDUP(NTotal/4,0),0)</f>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B6">
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,10+ROUNDUP(NDcfc/2,0),7),0)</f>
@@ -8032,12 +8267,12 @@
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,17+ROUNDUP(NDcfc/2,0),14),0)</f>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B7">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,20,5),0)</f>
@@ -8046,12 +8281,12 @@
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,60,15),0)</f>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B8">
         <f>IF(NDcfc&gt;0,85,20)</f>
@@ -8060,12 +8295,12 @@
         <f>IF(NDcfc&gt;0,250,60)</f>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B9">
         <f>LaborDays</f>
@@ -8074,12 +8309,12 @@
         <f>LaborDays+7</f>
       </c>
       <c r="D9" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B10">
         <f>5</f>
@@ -8088,12 +8323,12 @@
         <f>10</f>
       </c>
       <c r="D10" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B12">
         <f>MAX(B4+B5+B6+B7+B9+B10,B8)</f>
@@ -8104,7 +8339,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B13">
         <f>ROUND(B12/21,1)</f>
@@ -8134,7 +8369,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="16" max="16" width="3" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="36" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
@@ -8142,7 +8377,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -8153,63 +8388,66 @@
         <v>20</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>35</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B4" s="61">
         <v>3000</v>
@@ -8218,7 +8456,7 @@
         <v>538</v>
       </c>
       <c r="D4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E4">
         <v>208</v>
@@ -8248,10 +8486,13 @@
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O4" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P4" s="61">
+        <v>803</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -8271,7 +8512,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B5" s="61">
         <v>3500</v>
@@ -8280,7 +8521,7 @@
         <v>532</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E5">
         <v>208</v>
@@ -8310,13 +8551,16 @@
         <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O5" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P5" s="61">
+        <v>790</v>
       </c>
       <c r="Q5" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="R5" s="8">
         <v>1.2</v>
@@ -8342,7 +8586,7 @@
         <v>542</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E6">
         <v>208</v>
@@ -8372,13 +8616,16 @@
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O6" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P6" s="61">
+        <v>813</v>
       </c>
       <c r="Q6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="R6" s="8">
         <v>1.5</v>
@@ -8395,7 +8642,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B7" s="61">
         <v>5000</v>
@@ -8404,7 +8651,7 @@
         <v>611</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E7">
         <v>208</v>
@@ -8434,13 +8681,16 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="O7" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P7" s="61">
+        <v>938</v>
       </c>
       <c r="Q7" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="R7" s="8">
         <v>2.5</v>
@@ -8455,9 +8705,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B8" s="61">
         <v>7500</v>
@@ -8466,7 +8716,7 @@
         <v>943</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E8">
         <v>208</v>
@@ -8496,15 +8746,18 @@
         <v>2</v>
       </c>
       <c r="N8" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="O8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="P8" s="61">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B9" s="61">
         <v>5500</v>
@@ -8513,7 +8766,7 @@
         <v>693</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E9">
         <v>208</v>
@@ -8543,15 +8796,18 @@
         <v>2</v>
       </c>
       <c r="N9" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O9" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P9" s="61">
+        <v>1092</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B10" s="61">
         <v>6500</v>
@@ -8560,7 +8816,7 @@
         <v>710</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E10">
         <v>208</v>
@@ -8590,13 +8846,16 @@
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="O10" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P10" s="61">
+        <v>1135</v>
       </c>
       <c r="Q10" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="R10" s="61">
         <v>40.81</v>
@@ -8604,7 +8863,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B11" s="61">
         <v>8500</v>
@@ -8613,7 +8872,7 @@
         <v>862</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E11">
         <v>208</v>
@@ -8643,13 +8902,16 @@
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="O11" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P11" s="61">
+        <v>1400</v>
       </c>
       <c r="Q11" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="R11" s="62">
         <v>0.1</v>
@@ -8657,7 +8919,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B12" s="61">
         <v>32000</v>
@@ -8666,7 +8928,7 @@
         <v>654</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E12">
         <v>480</v>
@@ -8696,13 +8958,16 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O12" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P12" s="61">
+        <v>1081</v>
       </c>
       <c r="Q12" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="R12" s="62">
         <v>0.0725</v>
@@ -8710,7 +8975,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B13" s="61">
         <v>35000</v>
@@ -8719,7 +8984,7 @@
         <v>654</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E13">
         <v>480</v>
@@ -8749,13 +9014,16 @@
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O13" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P13" s="61">
+        <v>1081</v>
       </c>
       <c r="Q13" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="R13" s="61">
         <v>2250</v>
@@ -8763,7 +9031,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B14" s="61">
         <v>38000</v>
@@ -8772,7 +9040,7 @@
         <v>657</v>
       </c>
       <c r="D14" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E14">
         <v>480</v>
@@ -8802,13 +9070,16 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O14" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P14" s="61">
+        <v>1092</v>
       </c>
       <c r="Q14" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="R14" s="61">
         <v>358</v>
@@ -8816,7 +9087,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B15" s="61">
         <v>42000</v>
@@ -8825,7 +9096,7 @@
         <v>657</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E15">
         <v>480</v>
@@ -8855,13 +9126,16 @@
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O15" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P15" s="61">
+        <v>1092</v>
       </c>
       <c r="Q15" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="R15" s="62">
         <v>0.05</v>
@@ -8869,7 +9143,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B16" s="61">
         <v>52000</v>
@@ -8878,7 +9152,7 @@
         <v>768</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E16">
         <v>480</v>
@@ -8908,13 +9182,16 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O16" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P16" s="61">
+        <v>1236</v>
       </c>
       <c r="Q16" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R16" s="61">
         <v>1500</v>
@@ -8922,7 +9199,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B17" s="61">
         <v>57000</v>
@@ -8931,7 +9208,7 @@
         <v>768</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E17">
         <v>480</v>
@@ -8961,13 +9238,16 @@
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O17" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P17" s="61">
+        <v>1236</v>
       </c>
       <c r="Q17" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="R17" s="8">
         <v>2000</v>
@@ -8975,7 +9255,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B18" s="61">
         <v>60000</v>
@@ -8984,7 +9264,7 @@
         <v>808</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E18">
         <v>480</v>
@@ -9014,13 +9294,16 @@
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O18" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P18" s="61">
+        <v>1295</v>
       </c>
       <c r="Q18" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="R18" s="61">
         <v>6500</v>
@@ -9028,7 +9311,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B19" s="61">
         <v>66000</v>
@@ -9037,7 +9320,7 @@
         <v>808</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E19">
         <v>480</v>
@@ -9067,13 +9350,16 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O19" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P19" s="61">
+        <v>1295</v>
       </c>
       <c r="Q19" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="R19" s="61">
         <v>4900</v>
@@ -9081,7 +9367,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B20" s="61">
         <v>72000</v>
@@ -9090,7 +9376,7 @@
         <v>1003</v>
       </c>
       <c r="D20" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E20">
         <v>480</v>
@@ -9120,13 +9406,16 @@
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="O20" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P20" s="61">
+        <v>1670</v>
       </c>
       <c r="Q20" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="R20" s="61">
         <v>3500</v>
@@ -9134,7 +9423,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B21" s="61">
         <v>79000</v>
@@ -9143,7 +9432,7 @@
         <v>1003</v>
       </c>
       <c r="D21" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E21">
         <v>480</v>
@@ -9173,13 +9462,16 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="O21" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P21" s="61">
+        <v>1670</v>
       </c>
       <c r="Q21" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="R21" s="61">
         <v>5200</v>
@@ -9187,7 +9479,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B22" s="61">
         <v>80000</v>
@@ -9196,7 +9488,7 @@
         <v>1086</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E22">
         <v>480</v>
@@ -9226,13 +9518,16 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="O22" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P22" s="61">
+        <v>1780</v>
       </c>
       <c r="Q22" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="R22" s="61">
         <v>2903</v>
@@ -9240,7 +9535,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B23" s="61">
         <v>88000</v>
@@ -9249,7 +9544,7 @@
         <v>1086</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E23">
         <v>480</v>
@@ -9279,13 +9574,16 @@
         <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="O23" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P23" s="61">
+        <v>1780</v>
       </c>
       <c r="Q23" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R23" s="61">
         <v>758</v>
@@ -9302,7 +9600,7 @@
         <v>1182</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E24">
         <v>480</v>
@@ -9332,13 +9630,16 @@
         <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="O24" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P24" s="61">
+        <v>2024</v>
       </c>
       <c r="Q24" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="R24" s="61">
         <v>302</v>
@@ -9346,7 +9647,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B25" s="61">
         <v>100000</v>
@@ -9355,7 +9656,7 @@
         <v>1182</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E25">
         <v>480</v>
@@ -9385,13 +9686,16 @@
         <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="O25" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P25" s="61">
+        <v>2024</v>
       </c>
       <c r="Q25" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="R25" s="61">
         <v>658</v>
@@ -9399,7 +9703,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B26" s="61">
         <v>105000</v>
@@ -9408,7 +9712,7 @@
         <v>1518</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E26">
         <v>480</v>
@@ -9438,13 +9742,16 @@
         <v>3</v>
       </c>
       <c r="N26" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O26" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P26" s="61">
+        <v>2374</v>
       </c>
       <c r="Q26" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="R26" s="61">
         <v>396</v>
@@ -9452,7 +9759,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B27" s="61">
         <v>115000</v>
@@ -9461,7 +9768,7 @@
         <v>1518</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E27">
         <v>480</v>
@@ -9491,13 +9798,16 @@
         <v>3</v>
       </c>
       <c r="N27" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O27" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P27" s="61">
+        <v>2374</v>
       </c>
       <c r="Q27" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="R27" s="61">
         <v>5000</v>
@@ -9505,7 +9815,7 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B28" s="61">
         <v>120000</v>
@@ -9514,7 +9824,7 @@
         <v>1816</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E28">
         <v>480</v>
@@ -9544,13 +9854,16 @@
         <v>3</v>
       </c>
       <c r="N28" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="O28" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P28" s="61">
+        <v>3043</v>
       </c>
       <c r="Q28" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="R28" s="61">
         <v>1500</v>
@@ -9558,7 +9871,7 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B29" s="61">
         <v>130000</v>
@@ -9567,7 +9880,7 @@
         <v>1816</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E29">
         <v>480</v>
@@ -9597,13 +9910,16 @@
         <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="O29" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P29" s="61">
+        <v>3043</v>
       </c>
       <c r="Q29" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="R29" s="61">
         <v>250</v>
@@ -9611,7 +9927,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B30" s="61">
         <v>135000</v>
@@ -9620,7 +9936,7 @@
         <v>1816</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E30">
         <v>480</v>
@@ -9650,13 +9966,16 @@
         <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P30" s="61">
+        <v>3043</v>
       </c>
       <c r="Q30" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="R30" s="61">
         <v>3519</v>
@@ -9664,7 +9983,7 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B31" s="61">
         <v>147000</v>
@@ -9673,7 +9992,7 @@
         <v>1816</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E31">
         <v>480</v>
@@ -9703,21 +10022,24 @@
         <v>3</v>
       </c>
       <c r="N31" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="O31" t="s">
-        <v>271</v>
+        <v>281</v>
+      </c>
+      <c r="P31" s="61">
+        <v>3043</v>
       </c>
       <c r="Q31" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="R31" s="61">
         <v>261</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B32" s="61">
         <v>155000</v>
@@ -9726,7 +10048,7 @@
         <v>2007</v>
       </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E32">
         <v>480</v>
@@ -9756,15 +10078,24 @@
         <v>3</v>
       </c>
       <c r="N32" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O32" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="P32" s="61">
+        <v>3483</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>341</v>
+      </c>
+      <c r="R32" s="61">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B33" s="61">
         <v>168000</v>
@@ -9773,7 +10104,7 @@
         <v>2007</v>
       </c>
       <c r="D33" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E33">
         <v>480</v>
@@ -9803,28 +10134,57 @@
         <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O33" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="P33" s="61">
+        <v>3483</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>343</v>
+      </c>
+      <c r="R33" s="61">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>345</v>
+      </c>
+      <c r="R34" s="61">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="17:18" x14ac:dyDescent="0.25">
+      <c r="Q35" t="s">
+        <v>346</v>
+      </c>
+      <c r="R35" s="61">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>333</v>
+        <v>347</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>348</v>
+      </c>
+      <c r="R36" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -9872,7 +10232,7 @@
         <v>2000</v>
       </c>
       <c r="B43" s="61">
-        <v>60000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -9880,7 +10240,7 @@
         <v>2500</v>
       </c>
       <c r="B44" s="61">
-        <v>58540</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -9909,15 +10269,15 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -9970,15 +10330,15 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -10039,15 +10399,15 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -10148,15 +10508,15 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -10185,7 +10545,7 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
@@ -10370,29 +10730,29 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B129" s="61">
         <v>0</v>
@@ -10409,7 +10769,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B130" s="61">
         <v>0</v>
@@ -10426,7 +10786,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="B131" s="61">
         <v>0.30329</v>
@@ -10443,7 +10803,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="B132" s="61">
         <v>0.56613</v>
@@ -10460,7 +10820,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B133" s="61">
         <v>0.87104</v>
@@ -10477,7 +10837,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="B134" s="61">
         <v>1.33293</v>
@@ -10494,7 +10854,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B135" s="61">
         <v>1.68126</v>
@@ -10511,7 +10871,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="B136" s="61">
         <v>2.1044</v>
@@ -10528,7 +10888,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B137" s="61">
         <v>2.39833</v>
@@ -10545,7 +10905,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B138" s="61">
         <v>2.95304</v>
@@ -10562,7 +10922,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="B139" s="61">
         <v>3.63758</v>
@@ -10579,7 +10939,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B140" s="61">
         <v>4.5658</v>
@@ -10596,7 +10956,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B141" s="61">
         <v>5.73045</v>
@@ -10613,7 +10973,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B142" s="61">
         <v>6.64016</v>
@@ -10630,7 +10990,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B143" s="61">
         <v>7.9632</v>
@@ -10647,7 +11007,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B144" s="61">
         <v>9.32416</v>
@@ -10664,7 +11024,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B145" s="61">
         <v>10.60671</v>
@@ -10681,7 +11041,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B146" s="61">
         <v>11.334</v>
@@ -10698,7 +11058,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="B147" s="61">
         <v>13.30059</v>
@@ -10715,7 +11075,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B148" s="61">
         <v>16.57382</v>
@@ -10732,7 +11092,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="B149" s="61">
         <v>0</v>
@@ -10749,7 +11109,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B150" s="61">
         <v>25.921</v>
@@ -10766,7 +11126,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="B151" s="61">
         <v>0</v>
@@ -10783,7 +11143,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B152" s="61">
         <v>0</v>
@@ -10800,7 +11160,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="B153" s="61">
         <v>34.398</v>
@@ -10817,7 +11177,7 @@
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -10,11 +10,12 @@
     <sheet sheetId="4" name="Panel 480V" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Panel 208V" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Estimate" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Costs Internal" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="ADA" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Timeline" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="RateCard" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Instructions" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="Peripherals" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Costs Internal" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="ADA" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Timeline" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="RateCard" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Instructions" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="ModelTable">RateCard!$A$4:$P$33</definedName>
@@ -44,25 +45,35 @@
     <definedName name="AdaStdCost">RateCard!$R$19</definedName>
     <definedName name="AdaAmbCost">RateCard!$R$20</definedName>
     <definedName name="AdaRampCost">RateCard!$R$21</definedName>
-    <definedName name="CivilBase">RateCard!$R$22</definedName>
-    <definedName name="CivilDcfc">RateCard!$R$23</definedName>
-    <definedName name="CivilL2">RateCard!$R$24</definedName>
-    <definedName name="SignageDcfc">RateCard!$R$25</definedName>
-    <definedName name="SignageL2">RateCard!$R$26</definedName>
-    <definedName name="TransformerPad">RateCard!$R$27</definedName>
-    <definedName name="CommDcfc">RateCard!$R$28</definedName>
-    <definedName name="CommL2">RateCard!$R$29</definedName>
-    <definedName name="EquipBase">RateCard!$R$30</definedName>
-    <definedName name="EquipPerDay">RateCard!$R$31</definedName>
-    <definedName name="EquipBaseEmt">RateCard!$R$32</definedName>
-    <definedName name="EquipPerDayEmt">RateCard!$R$33</definedName>
-    <definedName name="EmtRackCost">RateCard!$R$34</definedName>
-    <definedName name="EmtStrapCost">RateCard!$R$35</definedName>
-    <definedName name="EmtFtPerDay">RateCard!$R$36</definedName>
-    <definedName name="PermitBase">RateCard!$R$37</definedName>
-    <definedName name="PermitPerChg">RateCard!$R$38</definedName>
-    <definedName name="UtilAppDcfc">RateCard!$R$39</definedName>
-    <definedName name="UtilAppL2">RateCard!$R$40</definedName>
+    <definedName name="ConcreteRate">RateCard!$R$22</definedName>
+    <definedName name="ShortLoadFee">RateCard!$R$23</definedName>
+    <definedName name="AsphaltRate">RateCard!$R$24</definedName>
+    <definedName name="StallSqFt">RateCard!$R$25</definedName>
+    <definedName name="BollardCost">RateCard!$R$26</definedName>
+    <definedName name="BollardPerChg">RateCard!$R$27</definedName>
+    <definedName name="BollardAtGear">RateCard!$R$28</definedName>
+    <definedName name="BollardAtStepdown">RateCard!$R$29</definedName>
+    <definedName name="ConsumDcfc">RateCard!$R$30</definedName>
+    <definedName name="ConsumL2">RateCard!$R$31</definedName>
+    <definedName name="PadYdDcfc">RateCard!$R$32</definedName>
+    <definedName name="PadYdL2">RateCard!$R$33</definedName>
+    <definedName name="PadYdGear">RateCard!$R$34</definedName>
+    <definedName name="PadYdXfmr">RateCard!$R$35</definedName>
+    <definedName name="PadYdBollard">RateCard!$R$36</definedName>
+    <definedName name="TransformerPad">RateCard!$R$37</definedName>
+    <definedName name="CommDcfc">RateCard!$R$38</definedName>
+    <definedName name="CommL2">RateCard!$R$39</definedName>
+    <definedName name="EquipBase">RateCard!$R$40</definedName>
+    <definedName name="EquipPerDay">RateCard!$R$41</definedName>
+    <definedName name="EquipBaseEmt">RateCard!$R$42</definedName>
+    <definedName name="EquipPerDayEmt">RateCard!$R$43</definedName>
+    <definedName name="EmtRackCost">RateCard!$R$44</definedName>
+    <definedName name="EmtStrapCost">RateCard!$R$45</definedName>
+    <definedName name="EmtFtPerDay">RateCard!$R$46</definedName>
+    <definedName name="PermitBase">RateCard!$R$47</definedName>
+    <definedName name="PermitPerChg">RateCard!$R$48</definedName>
+    <definedName name="UtilAppDcfc">RateCard!$R$49</definedName>
+    <definedName name="UtilAppL2">RateCard!$R$50</definedName>
     <definedName name="NTotal">Intake!$B$36</definedName>
     <definedName name="NDcfc">Intake!$B$37</definedName>
     <definedName name="NumL2">Intake!$B$38</definedName>
@@ -98,6 +109,9 @@
     <definedName name="Valuation">Estimate!$B$25</definedName>
     <definedName name="TotalCost">Estimate!$B$41</definedName>
     <definedName name="CustomerTotal">Estimate!$B$43</definedName>
+    <definedName name="PeriphSignage">Peripherals!$D$10</definedName>
+    <definedName name="PeriphCivil">Peripherals!$D$25</definedName>
+    <definedName name="PeriphAsphalt">Peripherals!$D$29</definedName>
     <definedName name="AdaVan">ADA!$C$8</definedName>
     <definedName name="AdaStd">ADA!$D$8</definedName>
     <definedName name="AdaAmb">ADA!$E$8</definedName>
@@ -108,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="471">
   <si>
     <t>RFC INTAKE — EV Charging Project</t>
   </si>
@@ -629,16 +643,16 @@
     <t>Switchgear, panels &amp; transformer (Panel sheet)</t>
   </si>
   <si>
-    <t>Trenching / asphalt cut (terrain-adjusted)</t>
+    <t>Trenching / asphalt cut (terrain-adj.) + stall paving</t>
   </si>
   <si>
     <t>Surface EMT supports — strut racks @ 10 ft + straps (NEC 358.30)</t>
   </si>
   <si>
-    <t>Civil (concrete, rebar, wheel stops)</t>
-  </si>
-  <si>
-    <t>Signage, striping &amp; bollards</t>
+    <t>Civil — concrete, rebar, consumables (Peripherals sheet)</t>
+  </si>
+  <si>
+    <t>Signage, striping &amp; bollards (Peripherals sheet)</t>
   </si>
   <si>
     <t>Accessible EVCS stalls + ramp (ADA sheet)</t>
@@ -713,6 +727,87 @@
     <t>Less: rebates / incentives (CALeVIP etc.)</t>
   </si>
   <si>
+    <t>Peripherals — signage, protection &amp; civil detail (auto from Intake + RateCard)</t>
+  </si>
+  <si>
+    <t>Quantities follow the Intake charger counts; edit rates on the RateCard (or the yellow cells below). Trench-cut asphalt prices on the Estimate; the asphalt here is stall patch-back only.</t>
+  </si>
+  <si>
+    <t>SIGNAGE &amp; PROTECTION</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Bollards (2/charger + 4-5 at switchgear + 3 at step-down/sub-panel)</t>
+  </si>
+  <si>
+    <t>Signs</t>
+  </si>
+  <si>
+    <t>Sign posts</t>
+  </si>
+  <si>
+    <t>Striping (per 10-stall lot)</t>
+  </si>
+  <si>
+    <t>Signage &amp; protection subtotal</t>
+  </si>
+  <si>
+    <t>CONCRETE &amp; CIVIL</t>
+  </si>
+  <si>
+    <t>Concrete order — 2500 PSI (yd, rounded up to whole yards)</t>
+  </si>
+  <si>
+    <t>Concrete short-load fee (order &lt; 8 yd)</t>
+  </si>
+  <si>
+    <t>Rebar (#4 mats — 3/DCFC pad, 2/L2 pad, 2/feeder)</t>
+  </si>
+  <si>
+    <t>Forming &amp; anchoring consumables — DCFC pads</t>
+  </si>
+  <si>
+    <t>Forming &amp; anchoring consumables — L2 pads</t>
+  </si>
+  <si>
+    <t>Wheel stops</t>
+  </si>
+  <si>
+    <t>Christy boxes (1 per 200 trench-ft)</t>
+  </si>
+  <si>
+    <t>GFI test (service &gt; 1000A)</t>
+  </si>
+  <si>
+    <t>Plywood (manual count)</t>
+  </si>
+  <si>
+    <t>2x4 lumber (manual count)</t>
+  </si>
+  <si>
+    <t>Sono tubes (manual count)</t>
+  </si>
+  <si>
+    <t>Civil subtotal (feeds Estimate B11)</t>
+  </si>
+  <si>
+    <t>ASPHALT — STALL PATCH-BACK</t>
+  </si>
+  <si>
+    <t>Qty (SF)</t>
+  </si>
+  <si>
+    <t>Asphalt paving — parking stalls (2 stalls/L2, 1/DCFC × SF/stall)</t>
+  </si>
+  <si>
+    <t>Feeds the Estimate's trenching/asphalt row (B9). Overtype the qty formula with surveyed SF when the patch limits are drawn.</t>
+  </si>
+  <si>
     <t>Electrical Supply &amp; Construction Management Costs</t>
   </si>
   <si>
@@ -725,9 +820,6 @@
     <t>Final Cost</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Wires, Conduits and Peripherals</t>
   </si>
   <si>
@@ -1100,114 +1192,141 @@
     <t>DCFC 180kW</t>
   </si>
   <si>
-    <t>Civil mobilization base $</t>
+    <t>Concrete $/yd (2500 PSI delivered)</t>
   </si>
   <si>
     <t>DCFC 180kW Dual</t>
   </si>
   <si>
-    <t>Civil $/DCFC (concrete, rebar, stops)</t>
-  </si>
-  <si>
     <t>400 kcmil</t>
   </si>
   <si>
-    <t>Civil $/L2</t>
+    <t>Asphalt stall paving $/SF</t>
   </si>
   <si>
     <t>DCFC 200kW Dual</t>
   </si>
   <si>
-    <t>Signage+bollards $/DCFC</t>
+    <t>Stall patch-back SF per stall (9x18)</t>
   </si>
   <si>
     <t>DCFC 240kW</t>
   </si>
   <si>
-    <t>Signage $/L2</t>
+    <t>Bollard installed $/ea</t>
   </si>
   <si>
     <t>DCFC 240kW Dual</t>
   </si>
   <si>
+    <t>Bollards per charger</t>
+  </si>
+  <si>
+    <t>DCFC 275kW</t>
+  </si>
+  <si>
+    <t>250 kcmil</t>
+  </si>
+  <si>
+    <t>Bollards at switchgear (4-5)</t>
+  </si>
+  <si>
+    <t>DCFC 275kW Dual</t>
+  </si>
+  <si>
+    <t>Bollards at step-down TX + sub-panel</t>
+  </si>
+  <si>
+    <t>DCFC 300kW</t>
+  </si>
+  <si>
+    <t>Forming consumables $/DCFC (anchors, ells, forms)</t>
+  </si>
+  <si>
+    <t>DCFC 300kW Dual</t>
+  </si>
+  <si>
+    <t>Forming consumables $/L2</t>
+  </si>
+  <si>
+    <t>DCFC 360kW</t>
+  </si>
+  <si>
+    <t>Concrete yd per DCFC pad</t>
+  </si>
+  <si>
+    <t>DCFC 360kW Dual</t>
+  </si>
+  <si>
+    <t>Concrete yd per L2 pad</t>
+  </si>
+  <si>
+    <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. 'Install EMT $/u' is the same allowance with surface EMT conduit (garage installs; strut racks are a separate Estimate line). Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
+  </si>
+  <si>
+    <t>Concrete yd — switchgear pad</t>
+  </si>
+  <si>
+    <t>Concrete yd — step-down TX + sub-panel pad</t>
+  </si>
+  <si>
+    <t>Main switchgear 480V (website catalog)</t>
+  </si>
+  <si>
+    <t>Concrete yd per bollard footing</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
     <t>Utility transformer pad $ (DCFC)</t>
   </si>
   <si>
-    <t>DCFC 275kW</t>
-  </si>
-  <si>
-    <t>250 kcmil</t>
-  </si>
-  <si>
     <t>Commissioning $/DCFC</t>
   </si>
   <si>
-    <t>DCFC 275kW Dual</t>
-  </si>
-  <si>
     <t>Commissioning $/L2</t>
   </si>
   <si>
-    <t>DCFC 300kW</t>
-  </si>
-  <si>
     <t>Equipment rentals base $</t>
   </si>
   <si>
-    <t>DCFC 300kW Dual</t>
-  </si>
-  <si>
     <t>Equipment rentals $/labor-day</t>
   </si>
   <si>
-    <t>DCFC 360kW</t>
-  </si>
-  <si>
     <t>Equipment base $ (surface EMT — lift, no dig gear)</t>
   </si>
   <si>
-    <t>DCFC 360kW Dual</t>
-  </si>
-  <si>
     <t>Equipment $/labor-day (surface EMT)</t>
   </si>
   <si>
-    <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. 'Install EMT $/u' is the same allowance with surface EMT conduit (garage installs; strut racks are a separate Estimate line). Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
-  </si>
-  <si>
     <t>Strut trapeze rack $ (strut+rod+anchors, NEC 358.30)</t>
   </si>
   <si>
     <t>Strut conduit strap $ (per pipe per rack)</t>
   </si>
   <si>
-    <t>Main switchgear 480V (website catalog)</t>
-  </si>
-  <si>
     <t>Surface EMT route-ft per crew-day</t>
   </si>
   <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Permit issuance base $ (AHJ)</t>
   </si>
   <si>
     <t>Permit issuance $/charger</t>
   </si>
   <si>
+    <t>Sub-panel / distribution 208V</t>
+  </si>
+  <si>
     <t>Utility application $ (DCFC site)</t>
   </si>
   <si>
     <t>Utility application $ (L2-only site)</t>
   </si>
   <si>
-    <t>Sub-panel / distribution 208V</t>
-  </si>
-  <si>
     <t>Step-down transformer 208V (kVA)</t>
   </si>
   <si>
@@ -1341,6 +1460,15 @@
   </si>
   <si>
     <t xml:space="preserve">   utility/permit fee rates (PermitBase, PermitPerChg, UtilAppDcfc, UtilAppL2) are yellow scalars on the RateCard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   PERIPHERALS SHEET: itemized bollards (2/charger + 4-5 at switchgear + 3 at step-down/sub-panel), concrete order rounded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   up to whole yards (2500 PSI ConcreteRate + ShortLoadFee on the RateCard), asphalt stall patch-back (AsphaltRate $/SF),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   forming consumables per pad, rebar, wheel stops. Its subtotals feed Estimate rows 9/11/12 — edit rates, not formulas.</t>
   </si>
   <si>
     <t>3. Every price lives on the RateCard (yellow) — hardware, install allowance, gear catalog, wire $/ft (incl. 450 kcmil Cu &amp; Al),</t>
@@ -1667,6 +1795,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1731,7 +1860,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -3229,6 +3357,161 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4">
+        <f>2</f>
+      </c>
+      <c r="C4">
+        <f>4</f>
+      </c>
+      <c r="D4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5">
+        <f>IF(IncSitePlan="Yes",5+ROUNDUP(NTotal/4,0),0)</f>
+      </c>
+      <c r="C5">
+        <f>IF(IncSitePlan="Yes",10+ROUNDUP(NTotal/4,0),0)</f>
+      </c>
+      <c r="D5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B6">
+        <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,10+ROUNDUP(NDcfc/2,0),7),0)</f>
+      </c>
+      <c r="C6">
+        <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,17+ROUNDUP(NDcfc/2,0),14),0)</f>
+      </c>
+      <c r="D6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B7">
+        <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,20,5),0)</f>
+      </c>
+      <c r="C7">
+        <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,60,15),0)</f>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8">
+        <f>IF(NDcfc&gt;0,85,20)</f>
+      </c>
+      <c r="C8">
+        <f>IF(NDcfc&gt;0,250,60)</f>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9">
+        <f>LaborDays</f>
+      </c>
+      <c r="C9">
+        <f>LaborDays+7</f>
+      </c>
+      <c r="D9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B10">
+        <f>5</f>
+      </c>
+      <c r="C10">
+        <f>10</f>
+      </c>
+      <c r="D10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12">
+        <f>MAX(B4+B5+B6+B7+B9+B10,B8)</f>
+      </c>
+      <c r="C12">
+        <f>MAX(C4+C5+C6+C7+C9+C10,C8)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13">
+        <f>ROUND(B12/21,1)</f>
+      </c>
+      <c r="C13">
+        <f>ROUND(C12/21,1)</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U154"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -3250,7 +3533,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -3261,7 +3544,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>21</v>
@@ -3273,63 +3556,63 @@
         <v>93</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>48</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>46</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>35</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" s="62">
+        <v>314</v>
+      </c>
+      <c r="B4" s="34">
         <v>3000</v>
       </c>
-      <c r="C4" s="62">
+      <c r="C4" s="34">
         <v>538</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E4">
         <v>208</v>
@@ -3359,12 +3642,12 @@
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="O4" t="s">
-        <v>291</v>
-      </c>
-      <c r="P4" s="62">
+        <v>317</v>
+      </c>
+      <c r="P4" s="34">
         <v>803</v>
       </c>
       <c r="Q4" t="s">
@@ -3385,16 +3668,16 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B5" s="62">
+        <v>318</v>
+      </c>
+      <c r="B5" s="34">
         <v>3500</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="34">
         <v>532</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E5">
         <v>208</v>
@@ -3424,16 +3707,16 @@
         <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="O5" t="s">
-        <v>291</v>
-      </c>
-      <c r="P5" s="62">
+        <v>317</v>
+      </c>
+      <c r="P5" s="34">
         <v>790</v>
       </c>
       <c r="Q5" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="R5" s="8">
         <v>1.2</v>
@@ -3452,14 +3735,14 @@
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="62">
+      <c r="B6" s="34">
         <v>4000</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="34">
         <v>542</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E6">
         <v>208</v>
@@ -3489,16 +3772,16 @@
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="O6" t="s">
-        <v>291</v>
-      </c>
-      <c r="P6" s="62">
+        <v>317</v>
+      </c>
+      <c r="P6" s="34">
         <v>813</v>
       </c>
       <c r="Q6" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="R6" s="8">
         <v>1.5</v>
@@ -3515,16 +3798,16 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="62">
+        <v>321</v>
+      </c>
+      <c r="B7" s="34">
         <v>5000</v>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="34">
         <v>611</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E7">
         <v>208</v>
@@ -3554,16 +3837,16 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="O7" t="s">
-        <v>291</v>
-      </c>
-      <c r="P7" s="62">
+        <v>317</v>
+      </c>
+      <c r="P7" s="34">
         <v>938</v>
       </c>
       <c r="Q7" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="R7" s="8">
         <v>2.5</v>
@@ -3580,16 +3863,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
-      </c>
-      <c r="B8" s="62">
+        <v>324</v>
+      </c>
+      <c r="B8" s="34">
         <v>7500</v>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="34">
         <v>943</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E8">
         <v>208</v>
@@ -3619,27 +3902,27 @@
         <v>2</v>
       </c>
       <c r="N8" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="O8" t="s">
-        <v>291</v>
-      </c>
-      <c r="P8" s="62">
+        <v>317</v>
+      </c>
+      <c r="P8" s="34">
         <v>1574</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>300</v>
-      </c>
-      <c r="B9" s="62">
+        <v>326</v>
+      </c>
+      <c r="B9" s="34">
         <v>5500</v>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="34">
         <v>693</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E9">
         <v>208</v>
@@ -3669,27 +3952,27 @@
         <v>2</v>
       </c>
       <c r="N9" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="O9" t="s">
-        <v>291</v>
-      </c>
-      <c r="P9" s="62">
+        <v>317</v>
+      </c>
+      <c r="P9" s="34">
         <v>1092</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="62">
+        <v>327</v>
+      </c>
+      <c r="B10" s="34">
         <v>6500</v>
       </c>
-      <c r="C10" s="62">
+      <c r="C10" s="34">
         <v>710</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E10">
         <v>208</v>
@@ -3719,33 +4002,33 @@
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="O10" t="s">
-        <v>291</v>
-      </c>
-      <c r="P10" s="62">
+        <v>317</v>
+      </c>
+      <c r="P10" s="34">
         <v>1135</v>
       </c>
       <c r="Q10" t="s">
-        <v>302</v>
-      </c>
-      <c r="R10" s="62">
+        <v>328</v>
+      </c>
+      <c r="R10" s="34">
         <v>40.81</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>303</v>
-      </c>
-      <c r="B11" s="62">
+        <v>329</v>
+      </c>
+      <c r="B11" s="34">
         <v>8500</v>
       </c>
-      <c r="C11" s="62">
+      <c r="C11" s="34">
         <v>862</v>
       </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="E11">
         <v>208</v>
@@ -3775,16 +4058,16 @@
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="O11" t="s">
-        <v>291</v>
-      </c>
-      <c r="P11" s="62">
+        <v>317</v>
+      </c>
+      <c r="P11" s="34">
         <v>1400</v>
       </c>
       <c r="Q11" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="R11" s="63">
         <v>0.1</v>
@@ -3792,16 +4075,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B12" s="62">
+        <v>331</v>
+      </c>
+      <c r="B12" s="34">
         <v>32000</v>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="34">
         <v>654</v>
       </c>
       <c r="D12" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E12">
         <v>480</v>
@@ -3831,16 +4114,16 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="O12" t="s">
-        <v>291</v>
-      </c>
-      <c r="P12" s="62">
+        <v>317</v>
+      </c>
+      <c r="P12" s="34">
         <v>1081</v>
       </c>
       <c r="Q12" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="R12" s="63">
         <v>0.0725</v>
@@ -3848,16 +4131,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B13" s="62">
+        <v>335</v>
+      </c>
+      <c r="B13" s="34">
         <v>35000</v>
       </c>
-      <c r="C13" s="62">
+      <c r="C13" s="34">
         <v>654</v>
       </c>
       <c r="D13" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E13">
         <v>480</v>
@@ -3887,33 +4170,33 @@
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="O13" t="s">
-        <v>291</v>
-      </c>
-      <c r="P13" s="62">
+        <v>317</v>
+      </c>
+      <c r="P13" s="34">
         <v>1081</v>
       </c>
       <c r="Q13" t="s">
-        <v>310</v>
-      </c>
-      <c r="R13" s="62">
+        <v>336</v>
+      </c>
+      <c r="R13" s="34">
         <v>2250</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>311</v>
-      </c>
-      <c r="B14" s="62">
+        <v>337</v>
+      </c>
+      <c r="B14" s="34">
         <v>38000</v>
       </c>
-      <c r="C14" s="62">
+      <c r="C14" s="34">
         <v>657</v>
       </c>
       <c r="D14" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E14">
         <v>480</v>
@@ -3943,33 +4226,33 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="O14" t="s">
-        <v>291</v>
-      </c>
-      <c r="P14" s="62">
+        <v>317</v>
+      </c>
+      <c r="P14" s="34">
         <v>1092</v>
       </c>
       <c r="Q14" t="s">
-        <v>312</v>
-      </c>
-      <c r="R14" s="62">
+        <v>338</v>
+      </c>
+      <c r="R14" s="34">
         <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>313</v>
-      </c>
-      <c r="B15" s="62">
+        <v>339</v>
+      </c>
+      <c r="B15" s="34">
         <v>42000</v>
       </c>
-      <c r="C15" s="62">
+      <c r="C15" s="34">
         <v>657</v>
       </c>
       <c r="D15" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E15">
         <v>480</v>
@@ -3999,16 +4282,16 @@
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="O15" t="s">
-        <v>291</v>
-      </c>
-      <c r="P15" s="62">
+        <v>317</v>
+      </c>
+      <c r="P15" s="34">
         <v>1092</v>
       </c>
       <c r="Q15" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="R15" s="63">
         <v>0.05</v>
@@ -4016,16 +4299,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>315</v>
-      </c>
-      <c r="B16" s="62">
+        <v>341</v>
+      </c>
+      <c r="B16" s="34">
         <v>52000</v>
       </c>
-      <c r="C16" s="62">
+      <c r="C16" s="34">
         <v>768</v>
       </c>
       <c r="D16" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E16">
         <v>480</v>
@@ -4055,33 +4338,33 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="O16" t="s">
-        <v>291</v>
-      </c>
-      <c r="P16" s="62">
+        <v>317</v>
+      </c>
+      <c r="P16" s="34">
         <v>1236</v>
       </c>
       <c r="Q16" t="s">
-        <v>317</v>
-      </c>
-      <c r="R16" s="62">
+        <v>343</v>
+      </c>
+      <c r="R16" s="34">
         <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>318</v>
-      </c>
-      <c r="B17" s="62">
+        <v>344</v>
+      </c>
+      <c r="B17" s="34">
         <v>57000</v>
       </c>
-      <c r="C17" s="62">
+      <c r="C17" s="34">
         <v>768</v>
       </c>
       <c r="D17" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E17">
         <v>480</v>
@@ -4111,16 +4394,16 @@
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="O17" t="s">
-        <v>291</v>
-      </c>
-      <c r="P17" s="62">
+        <v>317</v>
+      </c>
+      <c r="P17" s="34">
         <v>1236</v>
       </c>
       <c r="Q17" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="R17" s="8">
         <v>2000</v>
@@ -4128,16 +4411,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>320</v>
-      </c>
-      <c r="B18" s="62">
+        <v>346</v>
+      </c>
+      <c r="B18" s="34">
         <v>60000</v>
       </c>
-      <c r="C18" s="62">
+      <c r="C18" s="34">
         <v>808</v>
       </c>
       <c r="D18" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E18">
         <v>480</v>
@@ -4167,33 +4450,33 @@
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="O18" t="s">
-        <v>291</v>
-      </c>
-      <c r="P18" s="62">
+        <v>317</v>
+      </c>
+      <c r="P18" s="34">
         <v>1295</v>
       </c>
       <c r="Q18" t="s">
-        <v>321</v>
-      </c>
-      <c r="R18" s="62">
+        <v>347</v>
+      </c>
+      <c r="R18" s="34">
         <v>6500</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>322</v>
-      </c>
-      <c r="B19" s="62">
+        <v>348</v>
+      </c>
+      <c r="B19" s="34">
         <v>66000</v>
       </c>
-      <c r="C19" s="62">
+      <c r="C19" s="34">
         <v>808</v>
       </c>
       <c r="D19" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E19">
         <v>480</v>
@@ -4223,33 +4506,33 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="O19" t="s">
-        <v>291</v>
-      </c>
-      <c r="P19" s="62">
+        <v>317</v>
+      </c>
+      <c r="P19" s="34">
         <v>1295</v>
       </c>
       <c r="Q19" t="s">
-        <v>323</v>
-      </c>
-      <c r="R19" s="62">
+        <v>349</v>
+      </c>
+      <c r="R19" s="34">
         <v>4900</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="62">
+        <v>350</v>
+      </c>
+      <c r="B20" s="34">
         <v>72000</v>
       </c>
-      <c r="C20" s="62">
+      <c r="C20" s="34">
         <v>1003</v>
       </c>
       <c r="D20" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E20">
         <v>480</v>
@@ -4279,33 +4562,33 @@
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="O20" t="s">
-        <v>291</v>
-      </c>
-      <c r="P20" s="62">
+        <v>317</v>
+      </c>
+      <c r="P20" s="34">
         <v>1670</v>
       </c>
       <c r="Q20" t="s">
-        <v>326</v>
-      </c>
-      <c r="R20" s="62">
+        <v>352</v>
+      </c>
+      <c r="R20" s="34">
         <v>3500</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>327</v>
-      </c>
-      <c r="B21" s="62">
+        <v>353</v>
+      </c>
+      <c r="B21" s="34">
         <v>79000</v>
       </c>
-      <c r="C21" s="62">
+      <c r="C21" s="34">
         <v>1003</v>
       </c>
       <c r="D21" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E21">
         <v>480</v>
@@ -4335,33 +4618,33 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="O21" t="s">
-        <v>291</v>
-      </c>
-      <c r="P21" s="62">
+        <v>317</v>
+      </c>
+      <c r="P21" s="34">
         <v>1670</v>
       </c>
       <c r="Q21" t="s">
-        <v>328</v>
-      </c>
-      <c r="R21" s="62">
+        <v>354</v>
+      </c>
+      <c r="R21" s="34">
         <v>5200</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>329</v>
-      </c>
-      <c r="B22" s="62">
+        <v>355</v>
+      </c>
+      <c r="B22" s="34">
         <v>80000</v>
       </c>
-      <c r="C22" s="62">
+      <c r="C22" s="34">
         <v>1086</v>
       </c>
       <c r="D22" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E22">
         <v>480</v>
@@ -4391,33 +4674,33 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="O22" t="s">
-        <v>291</v>
-      </c>
-      <c r="P22" s="62">
+        <v>317</v>
+      </c>
+      <c r="P22" s="34">
         <v>1780</v>
       </c>
       <c r="Q22" t="s">
-        <v>330</v>
-      </c>
-      <c r="R22" s="62">
-        <v>2903</v>
+        <v>356</v>
+      </c>
+      <c r="R22" s="34">
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>331</v>
-      </c>
-      <c r="B23" s="62">
+        <v>357</v>
+      </c>
+      <c r="B23" s="34">
         <v>88000</v>
       </c>
-      <c r="C23" s="62">
+      <c r="C23" s="34">
         <v>1086</v>
       </c>
       <c r="D23" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E23">
         <v>480</v>
@@ -4447,33 +4730,33 @@
         <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="O23" t="s">
-        <v>291</v>
-      </c>
-      <c r="P23" s="62">
+        <v>317</v>
+      </c>
+      <c r="P23" s="34">
         <v>1780</v>
       </c>
       <c r="Q23" t="s">
-        <v>332</v>
-      </c>
-      <c r="R23" s="62">
-        <v>758</v>
+        <v>213</v>
+      </c>
+      <c r="R23" s="34">
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="62">
+      <c r="B24" s="34">
         <v>92000</v>
       </c>
-      <c r="C24" s="62">
+      <c r="C24" s="34">
         <v>1182</v>
       </c>
       <c r="D24" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E24">
         <v>480</v>
@@ -4503,33 +4786,33 @@
         <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="O24" t="s">
-        <v>291</v>
-      </c>
-      <c r="P24" s="62">
+        <v>317</v>
+      </c>
+      <c r="P24" s="34">
         <v>2024</v>
       </c>
       <c r="Q24" t="s">
-        <v>334</v>
-      </c>
-      <c r="R24" s="62">
-        <v>302</v>
+        <v>359</v>
+      </c>
+      <c r="R24" s="34">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>335</v>
-      </c>
-      <c r="B25" s="62">
+        <v>360</v>
+      </c>
+      <c r="B25" s="34">
         <v>100000</v>
       </c>
-      <c r="C25" s="62">
+      <c r="C25" s="34">
         <v>1182</v>
       </c>
       <c r="D25" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E25">
         <v>480</v>
@@ -4559,33 +4842,33 @@
         <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="O25" t="s">
-        <v>291</v>
-      </c>
-      <c r="P25" s="62">
+        <v>317</v>
+      </c>
+      <c r="P25" s="34">
         <v>2024</v>
       </c>
       <c r="Q25" t="s">
-        <v>336</v>
-      </c>
-      <c r="R25" s="62">
-        <v>658</v>
+        <v>361</v>
+      </c>
+      <c r="R25" s="8">
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>337</v>
-      </c>
-      <c r="B26" s="62">
+        <v>362</v>
+      </c>
+      <c r="B26" s="34">
         <v>105000</v>
       </c>
-      <c r="C26" s="62">
+      <c r="C26" s="34">
         <v>1518</v>
       </c>
       <c r="D26" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E26">
         <v>480</v>
@@ -4615,33 +4898,33 @@
         <v>3</v>
       </c>
       <c r="N26" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="O26" t="s">
-        <v>291</v>
-      </c>
-      <c r="P26" s="62">
+        <v>317</v>
+      </c>
+      <c r="P26" s="34">
         <v>2374</v>
       </c>
       <c r="Q26" t="s">
-        <v>338</v>
-      </c>
-      <c r="R26" s="62">
-        <v>396</v>
+        <v>363</v>
+      </c>
+      <c r="R26" s="34">
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>339</v>
-      </c>
-      <c r="B27" s="62">
+        <v>364</v>
+      </c>
+      <c r="B27" s="34">
         <v>115000</v>
       </c>
-      <c r="C27" s="62">
+      <c r="C27" s="34">
         <v>1518</v>
       </c>
       <c r="D27" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E27">
         <v>480</v>
@@ -4671,33 +4954,33 @@
         <v>3</v>
       </c>
       <c r="N27" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="O27" t="s">
-        <v>291</v>
-      </c>
-      <c r="P27" s="62">
+        <v>317</v>
+      </c>
+      <c r="P27" s="34">
         <v>2374</v>
       </c>
       <c r="Q27" t="s">
-        <v>340</v>
-      </c>
-      <c r="R27" s="62">
-        <v>5000</v>
+        <v>365</v>
+      </c>
+      <c r="R27" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>341</v>
-      </c>
-      <c r="B28" s="62">
+        <v>366</v>
+      </c>
+      <c r="B28" s="34">
         <v>120000</v>
       </c>
-      <c r="C28" s="62">
+      <c r="C28" s="34">
         <v>1816</v>
       </c>
       <c r="D28" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E28">
         <v>480</v>
@@ -4727,33 +5010,33 @@
         <v>3</v>
       </c>
       <c r="N28" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="O28" t="s">
-        <v>291</v>
-      </c>
-      <c r="P28" s="62">
+        <v>317</v>
+      </c>
+      <c r="P28" s="34">
         <v>3043</v>
       </c>
       <c r="Q28" t="s">
-        <v>343</v>
-      </c>
-      <c r="R28" s="62">
-        <v>1500</v>
+        <v>368</v>
+      </c>
+      <c r="R28" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>344</v>
-      </c>
-      <c r="B29" s="62">
+        <v>369</v>
+      </c>
+      <c r="B29" s="34">
         <v>130000</v>
       </c>
-      <c r="C29" s="62">
+      <c r="C29" s="34">
         <v>1816</v>
       </c>
       <c r="D29" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E29">
         <v>480</v>
@@ -4783,33 +5066,33 @@
         <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="O29" t="s">
-        <v>291</v>
-      </c>
-      <c r="P29" s="62">
+        <v>317</v>
+      </c>
+      <c r="P29" s="34">
         <v>3043</v>
       </c>
       <c r="Q29" t="s">
-        <v>345</v>
-      </c>
-      <c r="R29" s="62">
-        <v>250</v>
+        <v>370</v>
+      </c>
+      <c r="R29" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>346</v>
-      </c>
-      <c r="B30" s="62">
+        <v>371</v>
+      </c>
+      <c r="B30" s="34">
         <v>135000</v>
       </c>
-      <c r="C30" s="62">
+      <c r="C30" s="34">
         <v>1816</v>
       </c>
       <c r="D30" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E30">
         <v>480</v>
@@ -4839,33 +5122,33 @@
         <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="O30" t="s">
-        <v>291</v>
-      </c>
-      <c r="P30" s="62">
+        <v>317</v>
+      </c>
+      <c r="P30" s="34">
         <v>3043</v>
       </c>
       <c r="Q30" t="s">
-        <v>347</v>
-      </c>
-      <c r="R30" s="62">
-        <v>3519</v>
+        <v>372</v>
+      </c>
+      <c r="R30" s="34">
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>348</v>
-      </c>
-      <c r="B31" s="62">
+        <v>373</v>
+      </c>
+      <c r="B31" s="34">
         <v>147000</v>
       </c>
-      <c r="C31" s="62">
+      <c r="C31" s="34">
         <v>1816</v>
       </c>
       <c r="D31" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E31">
         <v>480</v>
@@ -4895,33 +5178,33 @@
         <v>3</v>
       </c>
       <c r="N31" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="O31" t="s">
-        <v>291</v>
-      </c>
-      <c r="P31" s="62">
+        <v>317</v>
+      </c>
+      <c r="P31" s="34">
         <v>3043</v>
       </c>
       <c r="Q31" t="s">
-        <v>349</v>
-      </c>
-      <c r="R31" s="62">
-        <v>261</v>
+        <v>374</v>
+      </c>
+      <c r="R31" s="34">
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>350</v>
-      </c>
-      <c r="B32" s="62">
+        <v>375</v>
+      </c>
+      <c r="B32" s="34">
         <v>155000</v>
       </c>
-      <c r="C32" s="62">
+      <c r="C32" s="34">
         <v>2007</v>
       </c>
       <c r="D32" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E32">
         <v>480</v>
@@ -4954,30 +5237,30 @@
         <v>60</v>
       </c>
       <c r="O32" t="s">
-        <v>291</v>
-      </c>
-      <c r="P32" s="62">
+        <v>317</v>
+      </c>
+      <c r="P32" s="34">
         <v>3483</v>
       </c>
       <c r="Q32" t="s">
-        <v>351</v>
-      </c>
-      <c r="R32" s="62">
-        <v>4043</v>
+        <v>376</v>
+      </c>
+      <c r="R32" s="8">
+        <v>0.75</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>352</v>
-      </c>
-      <c r="B33" s="62">
+        <v>377</v>
+      </c>
+      <c r="B33" s="34">
         <v>168000</v>
       </c>
-      <c r="C33" s="62">
+      <c r="C33" s="34">
         <v>2007</v>
       </c>
       <c r="D33" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E33">
         <v>480</v>
@@ -5010,178 +5293,240 @@
         <v>60</v>
       </c>
       <c r="O33" t="s">
-        <v>291</v>
-      </c>
-      <c r="P33" s="62">
+        <v>317</v>
+      </c>
+      <c r="P33" s="34">
         <v>3483</v>
       </c>
       <c r="Q33" t="s">
-        <v>353</v>
-      </c>
-      <c r="R33" s="62">
-        <v>35</v>
+        <v>378</v>
+      </c>
+      <c r="R33" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="Q34" t="s">
-        <v>355</v>
-      </c>
-      <c r="R34" s="62">
-        <v>28</v>
+        <v>380</v>
+      </c>
+      <c r="R34" s="8">
+        <v>1.75</v>
       </c>
     </row>
     <row r="35" spans="17:18" x14ac:dyDescent="0.25">
       <c r="Q35" t="s">
-        <v>356</v>
-      </c>
-      <c r="R35" s="62">
-        <v>3.25</v>
+        <v>381</v>
+      </c>
+      <c r="R35" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="Q36" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="R36" s="8">
-        <v>100</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="Q37" t="s">
-        <v>361</v>
-      </c>
-      <c r="R37" s="62">
-        <v>200</v>
+        <v>386</v>
+      </c>
+      <c r="R37" s="34">
+        <v>5000</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>400</v>
       </c>
-      <c r="B38" s="62">
+      <c r="B38" s="34">
         <v>20426.82</v>
       </c>
       <c r="Q38" t="s">
-        <v>362</v>
-      </c>
-      <c r="R38" s="62">
-        <v>60</v>
+        <v>387</v>
+      </c>
+      <c r="R38" s="34">
+        <v>1500</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>800</v>
       </c>
-      <c r="B39" s="62">
+      <c r="B39" s="34">
         <v>31187</v>
       </c>
       <c r="Q39" t="s">
-        <v>363</v>
-      </c>
-      <c r="R39" s="62">
-        <v>2500</v>
+        <v>388</v>
+      </c>
+      <c r="R39" s="34">
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1000</v>
       </c>
-      <c r="B40" s="62">
+      <c r="B40" s="34">
         <v>36812.5</v>
       </c>
       <c r="Q40" t="s">
-        <v>364</v>
-      </c>
-      <c r="R40" s="62">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="R40" s="34">
+        <v>3519</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1200</v>
       </c>
-      <c r="B41" s="62">
+      <c r="B41" s="34">
         <v>43292.68</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q41" t="s">
+        <v>390</v>
+      </c>
+      <c r="R41" s="34">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1600</v>
       </c>
-      <c r="B42" s="62">
+      <c r="B42" s="34">
         <v>56750</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q42" t="s">
+        <v>391</v>
+      </c>
+      <c r="R42" s="34">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2000</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="34">
         <v>55000</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q43" t="s">
+        <v>392</v>
+      </c>
+      <c r="R43" s="34">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2500</v>
       </c>
-      <c r="B44" s="62">
+      <c r="B44" s="34">
         <v>60000</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q44" t="s">
+        <v>393</v>
+      </c>
+      <c r="R44" s="34">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3000</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="34">
         <v>65000</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q45" t="s">
+        <v>394</v>
+      </c>
+      <c r="R45" s="34">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>4000</v>
       </c>
-      <c r="B46" s="62">
+      <c r="B46" s="34">
         <v>67500</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q46" t="s">
+        <v>395</v>
+      </c>
+      <c r="R46" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>5000</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="34">
         <v>70000</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="Q47" t="s">
+        <v>396</v>
+      </c>
+      <c r="R47" s="34">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="17:18" x14ac:dyDescent="0.25">
+      <c r="Q48" t="s">
+        <v>397</v>
+      </c>
+      <c r="R48" s="34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>399</v>
+      </c>
+      <c r="R49" s="34">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>360</v>
+        <v>385</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>400</v>
+      </c>
+      <c r="R50" s="34">
+        <v>800</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>150</v>
       </c>
-      <c r="B51" s="62">
+      <c r="B51" s="34">
         <v>1000</v>
       </c>
     </row>
@@ -5189,7 +5534,7 @@
       <c r="A52">
         <v>250</v>
       </c>
-      <c r="B52" s="62">
+      <c r="B52" s="34">
         <v>1120</v>
       </c>
     </row>
@@ -5197,7 +5542,7 @@
       <c r="A53">
         <v>400</v>
       </c>
-      <c r="B53" s="62">
+      <c r="B53" s="34">
         <v>1660</v>
       </c>
     </row>
@@ -5205,7 +5550,7 @@
       <c r="A54">
         <v>600</v>
       </c>
-      <c r="B54" s="62">
+      <c r="B54" s="34">
         <v>5387</v>
       </c>
     </row>
@@ -5213,7 +5558,7 @@
       <c r="A55">
         <v>800</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="34">
         <v>4650</v>
       </c>
     </row>
@@ -5221,28 +5566,28 @@
       <c r="A56">
         <v>1000</v>
       </c>
-      <c r="B56" s="62">
+      <c r="B56" s="34">
         <v>30000</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>75</v>
       </c>
-      <c r="B60" s="62">
+      <c r="B60" s="34">
         <v>2970</v>
       </c>
     </row>
@@ -5250,7 +5595,7 @@
       <c r="A61">
         <v>112.5</v>
       </c>
-      <c r="B61" s="62">
+      <c r="B61" s="34">
         <v>3250</v>
       </c>
     </row>
@@ -5258,7 +5603,7 @@
       <c r="A62">
         <v>150</v>
       </c>
-      <c r="B62" s="62">
+      <c r="B62" s="34">
         <v>5298</v>
       </c>
     </row>
@@ -5266,7 +5611,7 @@
       <c r="A63">
         <v>175</v>
       </c>
-      <c r="B63" s="62">
+      <c r="B63" s="34">
         <v>6000</v>
       </c>
     </row>
@@ -5274,7 +5619,7 @@
       <c r="A64">
         <v>225</v>
       </c>
-      <c r="B64" s="62">
+      <c r="B64" s="34">
         <v>7144</v>
       </c>
     </row>
@@ -5282,7 +5627,7 @@
       <c r="A65">
         <v>300</v>
       </c>
-      <c r="B65" s="62">
+      <c r="B65" s="34">
         <v>10493</v>
       </c>
     </row>
@@ -5290,28 +5635,28 @@
       <c r="A66">
         <v>500</v>
       </c>
-      <c r="B66" s="62">
+      <c r="B66" s="34">
         <v>14500</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>100</v>
       </c>
-      <c r="B70" s="62">
+      <c r="B70" s="34">
         <v>350</v>
       </c>
     </row>
@@ -5319,7 +5664,7 @@
       <c r="A71">
         <v>125</v>
       </c>
-      <c r="B71" s="62">
+      <c r="B71" s="34">
         <v>420</v>
       </c>
     </row>
@@ -5327,7 +5672,7 @@
       <c r="A72">
         <v>150</v>
       </c>
-      <c r="B72" s="62">
+      <c r="B72" s="34">
         <v>480</v>
       </c>
     </row>
@@ -5335,7 +5680,7 @@
       <c r="A73">
         <v>175</v>
       </c>
-      <c r="B73" s="62">
+      <c r="B73" s="34">
         <v>550</v>
       </c>
     </row>
@@ -5343,7 +5688,7 @@
       <c r="A74">
         <v>200</v>
       </c>
-      <c r="B74" s="62">
+      <c r="B74" s="34">
         <v>650</v>
       </c>
     </row>
@@ -5351,7 +5696,7 @@
       <c r="A75">
         <v>225</v>
       </c>
-      <c r="B75" s="62">
+      <c r="B75" s="34">
         <v>700</v>
       </c>
     </row>
@@ -5359,7 +5704,7 @@
       <c r="A76">
         <v>250</v>
       </c>
-      <c r="B76" s="62">
+      <c r="B76" s="34">
         <v>750</v>
       </c>
     </row>
@@ -5367,7 +5712,7 @@
       <c r="A77">
         <v>300</v>
       </c>
-      <c r="B77" s="62">
+      <c r="B77" s="34">
         <v>800</v>
       </c>
     </row>
@@ -5375,7 +5720,7 @@
       <c r="A78">
         <v>350</v>
       </c>
-      <c r="B78" s="62">
+      <c r="B78" s="34">
         <v>1000</v>
       </c>
     </row>
@@ -5383,7 +5728,7 @@
       <c r="A79">
         <v>400</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="34">
         <v>1200</v>
       </c>
     </row>
@@ -5391,7 +5736,7 @@
       <c r="A80">
         <v>500</v>
       </c>
-      <c r="B80" s="62">
+      <c r="B80" s="34">
         <v>1800</v>
       </c>
     </row>
@@ -5399,28 +5744,28 @@
       <c r="A81">
         <v>600</v>
       </c>
-      <c r="B81" s="62">
+      <c r="B81" s="34">
         <v>2200</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>40</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="34">
         <v>60</v>
       </c>
     </row>
@@ -5428,7 +5773,7 @@
       <c r="A86">
         <v>50</v>
       </c>
-      <c r="B86" s="62">
+      <c r="B86" s="34">
         <v>75</v>
       </c>
     </row>
@@ -5436,13 +5781,13 @@
       <c r="A87">
         <v>60</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="34">
         <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
@@ -5627,34 +5972,34 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>370</v>
+        <v>405</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>375</v>
-      </c>
-      <c r="B129" s="62">
+        <v>410</v>
+      </c>
+      <c r="B129" s="34">
         <v>0</v>
       </c>
-      <c r="C129" s="62">
+      <c r="C129" s="34">
         <v>0</v>
       </c>
       <c r="D129">
@@ -5666,12 +6011,12 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>376</v>
-      </c>
-      <c r="B130" s="62">
+        <v>411</v>
+      </c>
+      <c r="B130" s="34">
         <v>0</v>
       </c>
-      <c r="C130" s="62">
+      <c r="C130" s="34">
         <v>0</v>
       </c>
       <c r="D130">
@@ -5683,12 +6028,12 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>377</v>
-      </c>
-      <c r="B131" s="62">
+        <v>412</v>
+      </c>
+      <c r="B131" s="34">
         <v>0.30329</v>
       </c>
-      <c r="C131" s="62">
+      <c r="C131" s="34">
         <v>0.28</v>
       </c>
       <c r="D131">
@@ -5700,12 +6045,12 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>378</v>
-      </c>
-      <c r="B132" s="62">
+        <v>413</v>
+      </c>
+      <c r="B132" s="34">
         <v>0.56613</v>
       </c>
-      <c r="C132" s="62">
+      <c r="C132" s="34">
         <v>0</v>
       </c>
       <c r="D132">
@@ -5717,12 +6062,12 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>290</v>
-      </c>
-      <c r="B133" s="62">
+        <v>316</v>
+      </c>
+      <c r="B133" s="34">
         <v>0.87104</v>
       </c>
-      <c r="C133" s="62">
+      <c r="C133" s="34">
         <v>0.30636</v>
       </c>
       <c r="D133">
@@ -5734,12 +6079,12 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>379</v>
-      </c>
-      <c r="B134" s="62">
+        <v>414</v>
+      </c>
+      <c r="B134" s="34">
         <v>1.33293</v>
       </c>
-      <c r="C134" s="62">
+      <c r="C134" s="34">
         <v>0.37998</v>
       </c>
       <c r="D134">
@@ -5751,12 +6096,12 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>296</v>
-      </c>
-      <c r="B135" s="62">
+        <v>322</v>
+      </c>
+      <c r="B135" s="34">
         <v>1.68126</v>
       </c>
-      <c r="C135" s="62">
+      <c r="C135" s="34">
         <v>0.36681</v>
       </c>
       <c r="D135">
@@ -5768,12 +6113,12 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>380</v>
-      </c>
-      <c r="B136" s="62">
+        <v>415</v>
+      </c>
+      <c r="B136" s="34">
         <v>2.1044</v>
       </c>
-      <c r="C136" s="62">
+      <c r="C136" s="34">
         <v>0.4821</v>
       </c>
       <c r="D136">
@@ -5785,12 +6130,12 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>299</v>
-      </c>
-      <c r="B137" s="62">
+        <v>325</v>
+      </c>
+      <c r="B137" s="34">
         <v>2.39833</v>
       </c>
-      <c r="C137" s="62">
+      <c r="C137" s="34">
         <v>0.66733</v>
       </c>
       <c r="D137">
@@ -5802,12 +6147,12 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>307</v>
-      </c>
-      <c r="B138" s="62">
+        <v>333</v>
+      </c>
+      <c r="B138" s="34">
         <v>2.95304</v>
       </c>
-      <c r="C138" s="62">
+      <c r="C138" s="34">
         <v>0.75045</v>
       </c>
       <c r="D138">
@@ -5819,12 +6164,12 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>381</v>
-      </c>
-      <c r="B139" s="62">
+        <v>416</v>
+      </c>
+      <c r="B139" s="34">
         <v>3.63758</v>
       </c>
-      <c r="C139" s="62">
+      <c r="C139" s="34">
         <v>0.88701</v>
       </c>
       <c r="D139">
@@ -5836,12 +6181,12 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>316</v>
-      </c>
-      <c r="B140" s="62">
+        <v>342</v>
+      </c>
+      <c r="B140" s="34">
         <v>4.5658</v>
       </c>
-      <c r="C140" s="62">
+      <c r="C140" s="34">
         <v>1.09956</v>
       </c>
       <c r="D140">
@@ -5855,10 +6200,10 @@
       <c r="A141" t="s">
         <v>58</v>
       </c>
-      <c r="B141" s="62">
+      <c r="B141" s="34">
         <v>5.73045</v>
       </c>
-      <c r="C141" s="62">
+      <c r="C141" s="34">
         <v>1.2278</v>
       </c>
       <c r="D141">
@@ -5870,12 +6215,12 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>342</v>
-      </c>
-      <c r="B142" s="62">
+        <v>367</v>
+      </c>
+      <c r="B142" s="34">
         <v>6.64016</v>
       </c>
-      <c r="C142" s="62">
+      <c r="C142" s="34">
         <v>1.49616</v>
       </c>
       <c r="D142">
@@ -5887,12 +6232,12 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>325</v>
-      </c>
-      <c r="B143" s="62">
+        <v>351</v>
+      </c>
+      <c r="B143" s="34">
         <v>7.9632</v>
       </c>
-      <c r="C143" s="62">
+      <c r="C143" s="34">
         <v>2.06137</v>
       </c>
       <c r="D143">
@@ -5906,10 +6251,10 @@
       <c r="A144" t="s">
         <v>60</v>
       </c>
-      <c r="B144" s="62">
+      <c r="B144" s="34">
         <v>9.32416</v>
       </c>
-      <c r="C144" s="62">
+      <c r="C144" s="34">
         <v>2.10412</v>
       </c>
       <c r="D144">
@@ -5921,12 +6266,12 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>333</v>
-      </c>
-      <c r="B145" s="62">
+        <v>358</v>
+      </c>
+      <c r="B145" s="34">
         <v>10.60671</v>
       </c>
-      <c r="C145" s="62">
+      <c r="C145" s="34">
         <v>2.45797</v>
       </c>
       <c r="D145">
@@ -5938,12 +6283,12 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>382</v>
-      </c>
-      <c r="B146" s="62">
+        <v>417</v>
+      </c>
+      <c r="B146" s="34">
         <v>11.334</v>
       </c>
-      <c r="C146" s="62">
+      <c r="C146" s="34">
         <v>2.589</v>
       </c>
       <c r="D146">
@@ -5955,12 +6300,12 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>383</v>
-      </c>
-      <c r="B147" s="62">
+        <v>418</v>
+      </c>
+      <c r="B147" s="34">
         <v>13.30059</v>
       </c>
-      <c r="C147" s="62">
+      <c r="C147" s="34">
         <v>2.7204</v>
       </c>
       <c r="D147">
@@ -5974,10 +6319,10 @@
       <c r="A148" t="s">
         <v>55</v>
       </c>
-      <c r="B148" s="62">
+      <c r="B148" s="34">
         <v>16.57382</v>
       </c>
-      <c r="C148" s="62">
+      <c r="C148" s="34">
         <v>3.44354</v>
       </c>
       <c r="D148">
@@ -5989,12 +6334,12 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>384</v>
-      </c>
-      <c r="B149" s="62">
+        <v>419</v>
+      </c>
+      <c r="B149" s="34">
         <v>0</v>
       </c>
-      <c r="C149" s="62">
+      <c r="C149" s="34">
         <v>4.809</v>
       </c>
       <c r="D149">
@@ -6006,12 +6351,12 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>385</v>
-      </c>
-      <c r="B150" s="62">
+        <v>420</v>
+      </c>
+      <c r="B150" s="34">
         <v>25.921</v>
       </c>
-      <c r="C150" s="62">
+      <c r="C150" s="34">
         <v>4.859</v>
       </c>
       <c r="D150">
@@ -6023,12 +6368,12 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>386</v>
-      </c>
-      <c r="B151" s="62">
+        <v>421</v>
+      </c>
+      <c r="B151" s="34">
         <v>0</v>
       </c>
-      <c r="C151" s="62">
+      <c r="C151" s="34">
         <v>0</v>
       </c>
       <c r="D151">
@@ -6040,12 +6385,12 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>387</v>
-      </c>
-      <c r="B152" s="62">
+        <v>422</v>
+      </c>
+      <c r="B152" s="34">
         <v>0</v>
       </c>
-      <c r="C152" s="62">
+      <c r="C152" s="34">
         <v>7.566</v>
       </c>
       <c r="D152">
@@ -6057,12 +6402,12 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>388</v>
-      </c>
-      <c r="B153" s="62">
+        <v>423</v>
+      </c>
+      <c r="B153" s="34">
         <v>34.398</v>
       </c>
-      <c r="C153" s="62">
+      <c r="C153" s="34">
         <v>6.668</v>
       </c>
       <c r="D153">
@@ -6074,7 +6419,7 @@
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>389</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6083,9 +6428,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="114" customWidth="1"/>
@@ -6093,232 +6438,247 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="64" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="64" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>399</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="64" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="64" t="s">
-        <v>401</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="64" t="s">
-        <v>402</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
-        <v>403</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="64" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="64" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="64" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="64" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
-        <v>413</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="64" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="64" t="s">
-        <v>264</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>415</v>
+      <c r="A27" s="64" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="64" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="64" t="s">
-        <v>417</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
-        <v>418</v>
+      <c r="A30" s="19" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="64" t="s">
-        <v>264</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>419</v>
+      <c r="A32" s="64" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="64" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="64" t="s">
-        <v>421</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="64" t="s">
-        <v>264</v>
+      <c r="A35" s="19" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>422</v>
+      <c r="A36" s="64" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="64" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="64" t="s">
-        <v>424</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="64" t="s">
-        <v>425</v>
+      <c r="A39" s="19" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="64" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="64" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="64" t="s">
-        <v>428</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="64" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="64" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="64" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="64" t="s">
-        <v>432</v>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="64" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="64" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="64" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -12167,7 +12527,7 @@
         <v>173</v>
       </c>
       <c r="B9" s="9">
-        <f>TrenchFt*TrenchRate*VLOOKUP(Terrain,TerrainTable,2,FALSE)</f>
+        <f>TrenchFt*TrenchRate*VLOOKUP(Terrain,TerrainTable,2,FALSE)+PeriphAsphalt</f>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -12183,7 +12543,7 @@
         <v>175</v>
       </c>
       <c r="B11" s="9">
-        <f>IF(NTotal&gt;0,CivilBase,0)+NDcfc*CivilDcfc+NumL2*CivilL2</f>
+        <f>PeriphCivil</f>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -12191,7 +12551,7 @@
         <v>176</v>
       </c>
       <c r="B12" s="9">
-        <f>NDcfc*SignageDcfc+NumL2*SignageL2</f>
+        <f>PeriphSignage</f>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -12416,6 +12776,334 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6">
+        <f>NTotal*BollardPerChg+IF(NDcfc&gt;0,BollardAtGear,0)+IF(AND(NDcfc&gt;0,NumL2&gt;0),BollardAtStepdown,0)</f>
+      </c>
+      <c r="C6" s="9">
+        <f>BollardCost</f>
+      </c>
+      <c r="D6" s="9">
+        <f>B6*C6</f>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7">
+        <f>NTotal</f>
+      </c>
+      <c r="C7" s="34">
+        <v>40</v>
+      </c>
+      <c r="D7" s="9">
+        <f>B7*C7</f>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8">
+        <f>NumL2+ROUNDUP(NDcfc/2,0)</f>
+      </c>
+      <c r="C8" s="34">
+        <v>56.1</v>
+      </c>
+      <c r="D8" s="9">
+        <f>B8*C8</f>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9">
+        <f>(NumL2*2+NDcfc)/10</f>
+      </c>
+      <c r="C9" s="34">
+        <v>1500</v>
+      </c>
+      <c r="D9" s="9">
+        <f>B9*C9</f>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="11">
+        <f>SUM(D6:D9)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14">
+        <f>IF(InstallMethod="Surface EMT",0,CEILING(NDcfc*PadYdDcfc+IF(InstallMethod="Trenched",NumL2*PadYdL2,0)+IF(NDcfc&gt;0,PadYdGear,0)+IF(AND(NDcfc&gt;0,NumL2&gt;0),PadYdXfmr,0)+B6*PadYdBollard,1))</f>
+      </c>
+      <c r="C14" s="9">
+        <f>ConcreteRate</f>
+      </c>
+      <c r="D14" s="9">
+        <f>B14*C14</f>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15">
+        <f>IF(AND(B14&gt;0,B14&lt;8),1,0)</f>
+      </c>
+      <c r="C15" s="9">
+        <f>ShortLoadFee</f>
+      </c>
+      <c r="D15" s="9">
+        <f>B15*C15</f>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16">
+        <f>IF(InstallMethod="Surface EMT",0,NDcfc*3+IF(InstallMethod="Trenched",NumL2*2,0)+IF(AND(NDcfc&gt;0,NumL2&gt;0),3,IF(NTotal&gt;0,1,0))*2)</f>
+      </c>
+      <c r="C16" s="34">
+        <v>25.65</v>
+      </c>
+      <c r="D16" s="9">
+        <f>B16*C16</f>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17">
+        <f>NDcfc</f>
+      </c>
+      <c r="C17" s="9">
+        <f>ConsumDcfc</f>
+      </c>
+      <c r="D17" s="9">
+        <f>B17*C17</f>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18">
+        <f>NumL2</f>
+      </c>
+      <c r="C18" s="9">
+        <f>ConsumL2</f>
+      </c>
+      <c r="D18" s="9">
+        <f>B18*C18</f>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19">
+        <f>NTotal</f>
+      </c>
+      <c r="C19" s="34">
+        <v>70.58</v>
+      </c>
+      <c r="D19" s="9">
+        <f>B19*C19</f>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20">
+        <f>IF(TrenchFt&gt;0,MAX(1,ROUNDUP(TrenchFt/200,0)),0)</f>
+      </c>
+      <c r="C20" s="34">
+        <v>160</v>
+      </c>
+      <c r="D20" s="9">
+        <f>B20*C20</f>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21">
+        <f>IF(NDcfc&gt;0,IF(SgSuggested&gt;1000,1,0),0)</f>
+      </c>
+      <c r="C21" s="34">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="9">
+        <f>B21*C21</f>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="34">
+        <v>55</v>
+      </c>
+      <c r="D22" s="9">
+        <f>B22*C22</f>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0</v>
+      </c>
+      <c r="C23" s="34">
+        <v>10</v>
+      </c>
+      <c r="D23" s="9">
+        <f>B23*C23</f>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0</v>
+      </c>
+      <c r="C24" s="34">
+        <v>19</v>
+      </c>
+      <c r="D24" s="9">
+        <f>B24*C24</f>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" s="11">
+        <f>SUM(D14:D24)</f>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29">
+        <f>IF(InstallMethod="Surface EMT",0,(NumL2*2+NDcfc)*StallSqFt)</f>
+      </c>
+      <c r="C29" s="9">
+        <f>AsphaltRate</f>
+      </c>
+      <c r="D29" s="9">
+        <f>B29*C29</f>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFCD5B5"/>
@@ -12437,353 +13125,353 @@
   </cols>
   <sheetData>
     <row r="2" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="37" t="s">
+      <c r="B2" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G2" s="38" t="s">
+      <c r="F2" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="40">
+      <c r="B3" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="41">
         <v>1</v>
       </c>
-      <c r="D3" s="41">
+      <c r="D3" s="42">
         <f>Estimate!B7+Estimate!B10</f>
       </c>
-      <c r="E3" s="42">
+      <c r="E3" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="42">
         <f>(D3*E3)+D3</f>
       </c>
-      <c r="G3" s="43">
+      <c r="G3" s="44">
         <f>F3*C3</f>
       </c>
-      <c r="J3" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="K3" s="45"/>
+      <c r="J3" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" s="46"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="40">
+      <c r="B4" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="41">
         <v>1</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="42">
         <f>Panel!F22</f>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="42">
         <f>(D4*E4)+D4</f>
       </c>
-      <c r="G4" s="43">
+      <c r="G4" s="44">
         <f>F4*C4</f>
       </c>
-      <c r="J4" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="K4" s="47">
+      <c r="J4" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="K4" s="48">
         <f>IF(LaborDays&gt;0,LaborBase/LaborDays,0)</f>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="40">
+      <c r="B5" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="41">
         <v>1</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="42">
         <f>Panel!F42+Panel!F48+Panel!F66</f>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="42">
         <f>(D5*E5)+D5</f>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="44">
         <f>F5*C5</f>
       </c>
-      <c r="J5" s="46" t="s">
-        <v>211</v>
-      </c>
-      <c r="K5" s="48">
+      <c r="J5" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="K5" s="49">
         <f>LaborDays</f>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="40">
+      <c r="B6" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="41">
         <v>1</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="42">
         <f>Estimate!B12</f>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="42">
         <f>(D6*E6)+D6</f>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="44">
         <f>F6*C6</f>
       </c>
-      <c r="J6" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" s="48">
+      <c r="J6" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="K6" s="49">
         <f>K5/30</f>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="40">
+      <c r="B7" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="41">
         <v>1</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="42">
         <f>Estimate!B9</f>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="42">
         <f>(D7*E7)+D7</f>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="44">
         <f>F7*C7</f>
       </c>
-      <c r="J7" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="K7" s="50">
+      <c r="J7" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="K7" s="51">
         <f>K5*K4</f>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="40">
+      <c r="B8" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="41">
         <v>1</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <f>Estimate!B11</f>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="42">
         <f>(D8*E8)+D8</f>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="44">
         <f>F8*C8</f>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="40">
+      <c r="B9" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="41">
         <v>1</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="42">
         <f>Estimate!B13</f>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="42">
         <f>(D9*E9)+D9</f>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="44">
         <f>F9*C9</f>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="40">
+      <c r="B10" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="41">
         <v>1</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="42">
         <f>Estimate!B14</f>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="42">
         <f>(D10*E10)+D10</f>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="44">
         <f>F10*C10</f>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="40">
+      <c r="B11" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="41">
         <v>1</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="42">
         <f>Estimate!B17</f>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="42">
         <f>(D11*E11)+D11</f>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <f>F11*C11</f>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="41">
         <v>1</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="42">
         <f>Estimate!B18+Estimate!B15</f>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="42">
         <f>(D12*E12)+D12</f>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <f>F12*C12</f>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="C13" s="40">
+      <c r="B13" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="41">
         <v>1</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="42">
         <f>Estimate!B16</f>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <f>(D13*E13)+D13</f>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="44">
         <f>F13*C13</f>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="C14" s="40">
+      <c r="B14" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="41">
         <v>1</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <f>Estimate!B35+Estimate!B36+Estimate!B37</f>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="43">
         <v>0</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <f>(D14*E14)+D14</f>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="44">
         <f>F14*C14</f>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="55">
+      <c r="B15" s="52"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="56">
         <f>SUM(G3:G13)</f>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
+      <c r="B17" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="C18" s="40">
+      <c r="B18" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="41">
         <f>K5</f>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="42">
         <f>K4</f>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="43">
         <f>ContingencyPct</f>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="42">
         <f>(D18*E18)+D18</f>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <f>F18*C18</f>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="55">
+      <c r="B19" s="52"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="56">
         <f>SUM(G18)</f>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="49"/>
-      <c r="C20" s="57" t="s">
+      <c r="B20" s="50"/>
+      <c r="C20" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="58">
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="59">
         <f>G15+G19</f>
       </c>
     </row>
@@ -12797,7 +13485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -12812,29 +13500,29 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>205</v>
@@ -12842,7 +13530,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="B4">
         <f>NumL2</f>
@@ -12862,7 +13550,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="B5">
         <f>NDcfc</f>
@@ -12882,7 +13570,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B6" s="3">
         <f>NTotal</f>
@@ -12902,7 +13590,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -12910,7 +13598,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="C8" s="3">
         <f>IF(ISNUMBER(C7),C7,C6)</f>
@@ -12927,7 +13615,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="B9">
         <f>VLOOKUP(Terrain,TerrainTable,4,FALSE)</f>
@@ -12935,7 +13623,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="B10" s="9">
         <f>(AdaVan*AdaVanCost+AdaStd*AdaStdCost+AdaAmb*AdaAmbCost)*VLOOKUP(Terrain,TerrainTable,4,FALSE)+IF(NTotal&gt;0,AdaRampCost,0)</f>
@@ -12943,290 +13631,135 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="59" t="s">
-        <v>238</v>
-      </c>
-      <c r="B14" s="59" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="59" t="s">
-        <v>229</v>
+      <c r="A14" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" s="60" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="B15" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>241</v>
+      <c r="A15" s="61" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="B16" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>241</v>
+      <c r="A16" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="60" t="s">
-        <v>243</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>240</v>
+      <c r="A17" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="B18" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>245</v>
+      <c r="A18" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>271</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C19" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="D19" s="60" t="s">
-        <v>247</v>
+      <c r="A19" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="D20" s="60" t="s">
-        <v>251</v>
+      <c r="A20" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="61" t="s">
-        <v>252</v>
+      <c r="A22" s="62" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="61" t="s">
-        <v>253</v>
+      <c r="A23" s="62" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="61" t="s">
-        <v>254</v>
+      <c r="A24" s="62" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="61" t="s">
-        <v>255</v>
+      <c r="A25" s="62" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="61" t="s">
-        <v>256</v>
+      <c r="A26" s="62" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="61" t="s">
-        <v>257</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4">
-        <f>2</f>
-      </c>
-      <c r="C4">
-        <f>4</f>
-      </c>
-      <c r="D4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5">
-        <f>IF(IncSitePlan="Yes",5+ROUNDUP(NTotal/4,0),0)</f>
-      </c>
-      <c r="C5">
-        <f>IF(IncSitePlan="Yes",10+ROUNDUP(NTotal/4,0),0)</f>
-      </c>
-      <c r="D5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6">
-        <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,10+ROUNDUP(NDcfc/2,0),7),0)</f>
-      </c>
-      <c r="C6">
-        <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,17+ROUNDUP(NDcfc/2,0),14),0)</f>
-      </c>
-      <c r="D6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7">
-        <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,20,5),0)</f>
-      </c>
-      <c r="C7">
-        <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,60,15),0)</f>
-      </c>
-      <c r="D7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8">
-        <f>IF(NDcfc&gt;0,85,20)</f>
-      </c>
-      <c r="C8">
-        <f>IF(NDcfc&gt;0,250,60)</f>
-      </c>
-      <c r="D8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9">
-        <f>LaborDays</f>
-      </c>
-      <c r="C9">
-        <f>LaborDays+7</f>
-      </c>
-      <c r="D9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10">
-        <f>5</f>
-      </c>
-      <c r="C10">
-        <f>10</f>
-      </c>
-      <c r="D10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B12">
-        <f>MAX(B4+B5+B6+B7+B9+B10,B8)</f>
-      </c>
-      <c r="C12">
-        <f>MAX(C4+C5+C6+C7+C9+C10,C8)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>273</v>
-      </c>
-      <c r="B13">
-        <f>ROUND(B12/21,1)</f>
-      </c>
-      <c r="C13">
-        <f>ROUND(C12/21,1)</f>
+      <c r="A27" s="62" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -41,39 +41,40 @@
     <definedName name="CpmPct">RateCard!$R$15</definedName>
     <definedName name="GprDayRate">RateCard!$R$16</definedName>
     <definedName name="GprFtPerDay">RateCard!$R$17</definedName>
-    <definedName name="AdaVanCost">RateCard!$R$18</definedName>
-    <definedName name="AdaStdCost">RateCard!$R$19</definedName>
-    <definedName name="AdaAmbCost">RateCard!$R$20</definedName>
-    <definedName name="AdaRampCost">RateCard!$R$21</definedName>
-    <definedName name="ConcreteRate">RateCard!$R$22</definedName>
-    <definedName name="ShortLoadFee">RateCard!$R$23</definedName>
-    <definedName name="AsphaltRate">RateCard!$R$24</definedName>
-    <definedName name="StallSqFt">RateCard!$R$25</definedName>
-    <definedName name="BollardCost">RateCard!$R$26</definedName>
-    <definedName name="BollardPerChg">RateCard!$R$27</definedName>
-    <definedName name="BollardAtGear">RateCard!$R$28</definedName>
-    <definedName name="BollardAtStepdown">RateCard!$R$29</definedName>
-    <definedName name="ConsumDcfc">RateCard!$R$30</definedName>
-    <definedName name="ConsumL2">RateCard!$R$31</definedName>
-    <definedName name="PadYdDcfc">RateCard!$R$32</definedName>
-    <definedName name="PadYdL2">RateCard!$R$33</definedName>
-    <definedName name="PadYdGear">RateCard!$R$34</definedName>
-    <definedName name="PadYdXfmr">RateCard!$R$35</definedName>
-    <definedName name="PadYdBollard">RateCard!$R$36</definedName>
-    <definedName name="TransformerPad">RateCard!$R$37</definedName>
-    <definedName name="CommDcfc">RateCard!$R$38</definedName>
-    <definedName name="CommL2">RateCard!$R$39</definedName>
-    <definedName name="EquipBase">RateCard!$R$40</definedName>
-    <definedName name="EquipPerDay">RateCard!$R$41</definedName>
-    <definedName name="EquipBaseEmt">RateCard!$R$42</definedName>
-    <definedName name="EquipPerDayEmt">RateCard!$R$43</definedName>
-    <definedName name="EmtRackCost">RateCard!$R$44</definedName>
-    <definedName name="EmtStrapCost">RateCard!$R$45</definedName>
-    <definedName name="EmtFtPerDay">RateCard!$R$46</definedName>
-    <definedName name="PermitBase">RateCard!$R$47</definedName>
-    <definedName name="PermitPerChg">RateCard!$R$48</definedName>
-    <definedName name="UtilAppDcfc">RateCard!$R$49</definedName>
-    <definedName name="UtilAppL2">RateCard!$R$50</definedName>
+    <definedName name="DataBoxCost">RateCard!$R$18</definedName>
+    <definedName name="AdaVanCost">RateCard!$R$19</definedName>
+    <definedName name="AdaStdCost">RateCard!$R$20</definedName>
+    <definedName name="AdaAmbCost">RateCard!$R$21</definedName>
+    <definedName name="AdaRampCost">RateCard!$R$22</definedName>
+    <definedName name="ConcreteRate">RateCard!$R$23</definedName>
+    <definedName name="ShortLoadFee">RateCard!$R$24</definedName>
+    <definedName name="AsphaltRate">RateCard!$R$25</definedName>
+    <definedName name="StallSqFt">RateCard!$R$26</definedName>
+    <definedName name="BollardCost">RateCard!$R$27</definedName>
+    <definedName name="BollardPerChg">RateCard!$R$28</definedName>
+    <definedName name="BollardAtGear">RateCard!$R$29</definedName>
+    <definedName name="BollardAtStepdown">RateCard!$R$30</definedName>
+    <definedName name="ConsumDcfc">RateCard!$R$31</definedName>
+    <definedName name="ConsumL2">RateCard!$R$32</definedName>
+    <definedName name="PadYdDcfc">RateCard!$R$33</definedName>
+    <definedName name="PadYdL2">RateCard!$R$34</definedName>
+    <definedName name="PadYdGear">RateCard!$R$35</definedName>
+    <definedName name="PadYdXfmr">RateCard!$R$36</definedName>
+    <definedName name="PadYdBollard">RateCard!$R$37</definedName>
+    <definedName name="TransformerPad">RateCard!$R$38</definedName>
+    <definedName name="CommDcfc">RateCard!$R$39</definedName>
+    <definedName name="CommL2">RateCard!$R$40</definedName>
+    <definedName name="EquipBase">RateCard!$R$41</definedName>
+    <definedName name="EquipPerDay">RateCard!$R$42</definedName>
+    <definedName name="EquipBaseEmt">RateCard!$R$43</definedName>
+    <definedName name="EquipPerDayEmt">RateCard!$R$44</definedName>
+    <definedName name="EmtRackCost">RateCard!$R$45</definedName>
+    <definedName name="EmtStrapCost">RateCard!$R$46</definedName>
+    <definedName name="EmtFtPerDay">RateCard!$R$47</definedName>
+    <definedName name="PermitBase">RateCard!$R$48</definedName>
+    <definedName name="PermitPerChg">RateCard!$R$49</definedName>
+    <definedName name="UtilAppDcfc">RateCard!$R$50</definedName>
+    <definedName name="UtilAppL2">RateCard!$R$51</definedName>
     <definedName name="NTotal">Intake!$B$36</definedName>
     <definedName name="NDcfc">Intake!$B$37</definedName>
     <definedName name="NumL2">Intake!$B$38</definedName>
@@ -122,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="472">
   <si>
     <t>RFC INTAKE — EV Charging Project</t>
   </si>
@@ -637,7 +638,7 @@
     <t>Electrical supply &amp; construction</t>
   </si>
   <si>
-    <t>Wire runs (Takeoff + feeders) + conduit &amp; install allowance</t>
+    <t>Wire runs (Takeoff + feeders) + conduit &amp; install allowance + data box</t>
   </si>
   <si>
     <t>Switchgear, panels &amp; transformer (Panel sheet)</t>
@@ -1165,123 +1166,126 @@
     <t>DCFC 120kW</t>
   </si>
   <si>
+    <t>Data/comms box $ (one per site)</t>
+  </si>
+  <si>
+    <t>DCFC 120kW Dual</t>
+  </si>
+  <si>
     <t>ADA van stall $ (flat lot)</t>
   </si>
   <si>
-    <t>DCFC 120kW Dual</t>
+    <t>DCFC 160kW</t>
+  </si>
+  <si>
+    <t>300 kcmil</t>
   </si>
   <si>
     <t>ADA standard stall $ (flat lot)</t>
   </si>
   <si>
-    <t>DCFC 160kW</t>
-  </si>
-  <si>
-    <t>300 kcmil</t>
+    <t>DCFC 160kW Dual</t>
   </si>
   <si>
     <t>ADA ambulatory stall $ (flat lot)</t>
   </si>
   <si>
-    <t>DCFC 160kW Dual</t>
+    <t>DCFC 180kW</t>
   </si>
   <si>
     <t>ADA ramp $</t>
   </si>
   <si>
-    <t>DCFC 180kW</t>
+    <t>DCFC 180kW Dual</t>
   </si>
   <si>
     <t>Concrete $/yd (2500 PSI delivered)</t>
   </si>
   <si>
-    <t>DCFC 180kW Dual</t>
-  </si>
-  <si>
     <t>400 kcmil</t>
   </si>
   <si>
+    <t>DCFC 200kW Dual</t>
+  </si>
+  <si>
     <t>Asphalt stall paving $/SF</t>
   </si>
   <si>
-    <t>DCFC 200kW Dual</t>
+    <t>DCFC 240kW</t>
   </si>
   <si>
     <t>Stall patch-back SF per stall (9x18)</t>
   </si>
   <si>
-    <t>DCFC 240kW</t>
+    <t>DCFC 240kW Dual</t>
   </si>
   <si>
     <t>Bollard installed $/ea</t>
   </si>
   <si>
-    <t>DCFC 240kW Dual</t>
+    <t>DCFC 275kW</t>
+  </si>
+  <si>
+    <t>250 kcmil</t>
   </si>
   <si>
     <t>Bollards per charger</t>
   </si>
   <si>
-    <t>DCFC 275kW</t>
-  </si>
-  <si>
-    <t>250 kcmil</t>
+    <t>DCFC 275kW Dual</t>
   </si>
   <si>
     <t>Bollards at switchgear (4-5)</t>
   </si>
   <si>
-    <t>DCFC 275kW Dual</t>
+    <t>DCFC 300kW</t>
   </si>
   <si>
     <t>Bollards at step-down TX + sub-panel</t>
   </si>
   <si>
-    <t>DCFC 300kW</t>
+    <t>DCFC 300kW Dual</t>
   </si>
   <si>
     <t>Forming consumables $/DCFC (anchors, ells, forms)</t>
   </si>
   <si>
-    <t>DCFC 300kW Dual</t>
+    <t>DCFC 360kW</t>
   </si>
   <si>
     <t>Forming consumables $/L2</t>
   </si>
   <si>
-    <t>DCFC 360kW</t>
+    <t>DCFC 360kW Dual</t>
   </si>
   <si>
     <t>Concrete yd per DCFC pad</t>
   </si>
   <si>
-    <t>DCFC 360kW Dual</t>
+    <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. 'Install EMT $/u' is the same allowance with surface EMT conduit (garage installs; strut racks are a separate Estimate line). Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
   </si>
   <si>
     <t>Concrete yd per L2 pad</t>
   </si>
   <si>
-    <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. 'Install EMT $/u' is the same allowance with surface EMT conduit (garage installs; strut racks are a separate Estimate line). Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
-  </si>
-  <si>
     <t>Concrete yd — switchgear pad</t>
   </si>
   <si>
+    <t>Main switchgear 480V (website catalog)</t>
+  </si>
+  <si>
     <t>Concrete yd — step-down TX + sub-panel pad</t>
   </si>
   <si>
-    <t>Main switchgear 480V (website catalog)</t>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
   <si>
     <t>Concrete yd per bollard footing</t>
   </si>
   <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Utility transformer pad $ (DCFC)</t>
   </si>
   <si>
@@ -1315,10 +1319,10 @@
     <t>Permit issuance base $ (AHJ)</t>
   </si>
   <si>
+    <t>Sub-panel / distribution 208V</t>
+  </si>
+  <si>
     <t>Permit issuance $/charger</t>
-  </si>
-  <si>
-    <t>Sub-panel / distribution 208V</t>
   </si>
   <si>
     <t>Utility application $ (DCFC site)</t>
@@ -3609,7 +3613,7 @@
         <v>3000</v>
       </c>
       <c r="C4" s="34">
-        <v>538</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
         <v>315</v>
@@ -3648,7 +3652,7 @@
         <v>317</v>
       </c>
       <c r="P4" s="34">
-        <v>803</v>
+        <v>553</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -3674,7 +3678,7 @@
         <v>3500</v>
       </c>
       <c r="C5" s="34">
-        <v>532</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
         <v>315</v>
@@ -3713,7 +3717,7 @@
         <v>317</v>
       </c>
       <c r="P5" s="34">
-        <v>790</v>
+        <v>540</v>
       </c>
       <c r="Q5" t="s">
         <v>319</v>
@@ -3739,7 +3743,7 @@
         <v>4000</v>
       </c>
       <c r="C6" s="34">
-        <v>542</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
         <v>315</v>
@@ -3778,7 +3782,7 @@
         <v>317</v>
       </c>
       <c r="P6" s="34">
-        <v>813</v>
+        <v>563</v>
       </c>
       <c r="Q6" t="s">
         <v>320</v>
@@ -3804,7 +3808,7 @@
         <v>5000</v>
       </c>
       <c r="C7" s="34">
-        <v>611</v>
+        <v>361</v>
       </c>
       <c r="D7" t="s">
         <v>315</v>
@@ -3843,7 +3847,7 @@
         <v>317</v>
       </c>
       <c r="P7" s="34">
-        <v>938</v>
+        <v>688</v>
       </c>
       <c r="Q7" t="s">
         <v>323</v>
@@ -3869,7 +3873,7 @@
         <v>7500</v>
       </c>
       <c r="C8" s="34">
-        <v>943</v>
+        <v>693</v>
       </c>
       <c r="D8" t="s">
         <v>315</v>
@@ -3908,7 +3912,7 @@
         <v>317</v>
       </c>
       <c r="P8" s="34">
-        <v>1574</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -3919,7 +3923,7 @@
         <v>5500</v>
       </c>
       <c r="C9" s="34">
-        <v>693</v>
+        <v>443</v>
       </c>
       <c r="D9" t="s">
         <v>315</v>
@@ -3958,7 +3962,7 @@
         <v>317</v>
       </c>
       <c r="P9" s="34">
-        <v>1092</v>
+        <v>842</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -3969,7 +3973,7 @@
         <v>6500</v>
       </c>
       <c r="C10" s="34">
-        <v>710</v>
+        <v>460</v>
       </c>
       <c r="D10" t="s">
         <v>315</v>
@@ -4008,7 +4012,7 @@
         <v>317</v>
       </c>
       <c r="P10" s="34">
-        <v>1135</v>
+        <v>885</v>
       </c>
       <c r="Q10" t="s">
         <v>328</v>
@@ -4025,7 +4029,7 @@
         <v>8500</v>
       </c>
       <c r="C11" s="34">
-        <v>862</v>
+        <v>612</v>
       </c>
       <c r="D11" t="s">
         <v>315</v>
@@ -4064,7 +4068,7 @@
         <v>317</v>
       </c>
       <c r="P11" s="34">
-        <v>1400</v>
+        <v>1150</v>
       </c>
       <c r="Q11" t="s">
         <v>330</v>
@@ -4081,7 +4085,7 @@
         <v>32000</v>
       </c>
       <c r="C12" s="34">
-        <v>654</v>
+        <v>404</v>
       </c>
       <c r="D12" t="s">
         <v>332</v>
@@ -4120,7 +4124,7 @@
         <v>317</v>
       </c>
       <c r="P12" s="34">
-        <v>1081</v>
+        <v>831</v>
       </c>
       <c r="Q12" t="s">
         <v>334</v>
@@ -4137,7 +4141,7 @@
         <v>35000</v>
       </c>
       <c r="C13" s="34">
-        <v>654</v>
+        <v>404</v>
       </c>
       <c r="D13" t="s">
         <v>332</v>
@@ -4176,7 +4180,7 @@
         <v>317</v>
       </c>
       <c r="P13" s="34">
-        <v>1081</v>
+        <v>831</v>
       </c>
       <c r="Q13" t="s">
         <v>336</v>
@@ -4193,7 +4197,7 @@
         <v>38000</v>
       </c>
       <c r="C14" s="34">
-        <v>657</v>
+        <v>407</v>
       </c>
       <c r="D14" t="s">
         <v>332</v>
@@ -4232,7 +4236,7 @@
         <v>317</v>
       </c>
       <c r="P14" s="34">
-        <v>1092</v>
+        <v>842</v>
       </c>
       <c r="Q14" t="s">
         <v>338</v>
@@ -4249,7 +4253,7 @@
         <v>42000</v>
       </c>
       <c r="C15" s="34">
-        <v>657</v>
+        <v>407</v>
       </c>
       <c r="D15" t="s">
         <v>332</v>
@@ -4288,7 +4292,7 @@
         <v>317</v>
       </c>
       <c r="P15" s="34">
-        <v>1092</v>
+        <v>842</v>
       </c>
       <c r="Q15" t="s">
         <v>340</v>
@@ -4305,7 +4309,7 @@
         <v>52000</v>
       </c>
       <c r="C16" s="34">
-        <v>768</v>
+        <v>518</v>
       </c>
       <c r="D16" t="s">
         <v>332</v>
@@ -4344,7 +4348,7 @@
         <v>317</v>
       </c>
       <c r="P16" s="34">
-        <v>1236</v>
+        <v>986</v>
       </c>
       <c r="Q16" t="s">
         <v>343</v>
@@ -4361,7 +4365,7 @@
         <v>57000</v>
       </c>
       <c r="C17" s="34">
-        <v>768</v>
+        <v>518</v>
       </c>
       <c r="D17" t="s">
         <v>332</v>
@@ -4400,7 +4404,7 @@
         <v>317</v>
       </c>
       <c r="P17" s="34">
-        <v>1236</v>
+        <v>986</v>
       </c>
       <c r="Q17" t="s">
         <v>345</v>
@@ -4417,7 +4421,7 @@
         <v>60000</v>
       </c>
       <c r="C18" s="34">
-        <v>808</v>
+        <v>558</v>
       </c>
       <c r="D18" t="s">
         <v>332</v>
@@ -4456,13 +4460,13 @@
         <v>317</v>
       </c>
       <c r="P18" s="34">
-        <v>1295</v>
+        <v>1045</v>
       </c>
       <c r="Q18" t="s">
         <v>347</v>
       </c>
       <c r="R18" s="34">
-        <v>6500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -4473,7 +4477,7 @@
         <v>66000</v>
       </c>
       <c r="C19" s="34">
-        <v>808</v>
+        <v>558</v>
       </c>
       <c r="D19" t="s">
         <v>332</v>
@@ -4512,13 +4516,13 @@
         <v>317</v>
       </c>
       <c r="P19" s="34">
-        <v>1295</v>
+        <v>1045</v>
       </c>
       <c r="Q19" t="s">
         <v>349</v>
       </c>
       <c r="R19" s="34">
-        <v>4900</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4529,7 +4533,7 @@
         <v>72000</v>
       </c>
       <c r="C20" s="34">
-        <v>1003</v>
+        <v>753</v>
       </c>
       <c r="D20" t="s">
         <v>332</v>
@@ -4568,13 +4572,13 @@
         <v>317</v>
       </c>
       <c r="P20" s="34">
-        <v>1670</v>
+        <v>1420</v>
       </c>
       <c r="Q20" t="s">
         <v>352</v>
       </c>
       <c r="R20" s="34">
-        <v>3500</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4585,7 +4589,7 @@
         <v>79000</v>
       </c>
       <c r="C21" s="34">
-        <v>1003</v>
+        <v>753</v>
       </c>
       <c r="D21" t="s">
         <v>332</v>
@@ -4624,13 +4628,13 @@
         <v>317</v>
       </c>
       <c r="P21" s="34">
-        <v>1670</v>
+        <v>1420</v>
       </c>
       <c r="Q21" t="s">
         <v>354</v>
       </c>
       <c r="R21" s="34">
-        <v>5200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4641,7 +4645,7 @@
         <v>80000</v>
       </c>
       <c r="C22" s="34">
-        <v>1086</v>
+        <v>836</v>
       </c>
       <c r="D22" t="s">
         <v>332</v>
@@ -4680,13 +4684,13 @@
         <v>317</v>
       </c>
       <c r="P22" s="34">
-        <v>1780</v>
+        <v>1530</v>
       </c>
       <c r="Q22" t="s">
         <v>356</v>
       </c>
       <c r="R22" s="34">
-        <v>165</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4697,7 +4701,7 @@
         <v>88000</v>
       </c>
       <c r="C23" s="34">
-        <v>1086</v>
+        <v>836</v>
       </c>
       <c r="D23" t="s">
         <v>332</v>
@@ -4736,13 +4740,13 @@
         <v>317</v>
       </c>
       <c r="P23" s="34">
-        <v>1780</v>
+        <v>1530</v>
       </c>
       <c r="Q23" t="s">
-        <v>213</v>
+        <v>358</v>
       </c>
       <c r="R23" s="34">
-        <v>125</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4753,7 +4757,7 @@
         <v>92000</v>
       </c>
       <c r="C24" s="34">
-        <v>1182</v>
+        <v>932</v>
       </c>
       <c r="D24" t="s">
         <v>332</v>
@@ -4786,19 +4790,19 @@
         <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O24" t="s">
         <v>317</v>
       </c>
       <c r="P24" s="34">
-        <v>2024</v>
+        <v>1774</v>
       </c>
       <c r="Q24" t="s">
-        <v>359</v>
+        <v>213</v>
       </c>
       <c r="R24" s="34">
-        <v>5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -4809,7 +4813,7 @@
         <v>100000</v>
       </c>
       <c r="C25" s="34">
-        <v>1182</v>
+        <v>932</v>
       </c>
       <c r="D25" t="s">
         <v>332</v>
@@ -4842,19 +4846,19 @@
         <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O25" t="s">
         <v>317</v>
       </c>
       <c r="P25" s="34">
-        <v>2024</v>
+        <v>1774</v>
       </c>
       <c r="Q25" t="s">
         <v>361</v>
       </c>
-      <c r="R25" s="8">
-        <v>162</v>
+      <c r="R25" s="34">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -4865,7 +4869,7 @@
         <v>105000</v>
       </c>
       <c r="C26" s="34">
-        <v>1518</v>
+        <v>1268</v>
       </c>
       <c r="D26" t="s">
         <v>332</v>
@@ -4904,13 +4908,13 @@
         <v>317</v>
       </c>
       <c r="P26" s="34">
-        <v>2374</v>
+        <v>2124</v>
       </c>
       <c r="Q26" t="s">
         <v>363</v>
       </c>
-      <c r="R26" s="34">
-        <v>110</v>
+      <c r="R26" s="8">
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -4921,7 +4925,7 @@
         <v>115000</v>
       </c>
       <c r="C27" s="34">
-        <v>1518</v>
+        <v>1268</v>
       </c>
       <c r="D27" t="s">
         <v>332</v>
@@ -4960,13 +4964,13 @@
         <v>317</v>
       </c>
       <c r="P27" s="34">
-        <v>2374</v>
+        <v>2124</v>
       </c>
       <c r="Q27" t="s">
         <v>365</v>
       </c>
-      <c r="R27" s="8">
-        <v>2</v>
+      <c r="R27" s="34">
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -4977,7 +4981,7 @@
         <v>120000</v>
       </c>
       <c r="C28" s="34">
-        <v>1816</v>
+        <v>1566</v>
       </c>
       <c r="D28" t="s">
         <v>332</v>
@@ -5016,13 +5020,13 @@
         <v>317</v>
       </c>
       <c r="P28" s="34">
-        <v>3043</v>
+        <v>2793</v>
       </c>
       <c r="Q28" t="s">
         <v>368</v>
       </c>
       <c r="R28" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5033,7 +5037,7 @@
         <v>130000</v>
       </c>
       <c r="C29" s="34">
-        <v>1816</v>
+        <v>1566</v>
       </c>
       <c r="D29" t="s">
         <v>332</v>
@@ -5072,13 +5076,13 @@
         <v>317</v>
       </c>
       <c r="P29" s="34">
-        <v>3043</v>
+        <v>2793</v>
       </c>
       <c r="Q29" t="s">
         <v>370</v>
       </c>
       <c r="R29" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5089,7 +5093,7 @@
         <v>135000</v>
       </c>
       <c r="C30" s="34">
-        <v>1816</v>
+        <v>1566</v>
       </c>
       <c r="D30" t="s">
         <v>332</v>
@@ -5128,13 +5132,13 @@
         <v>317</v>
       </c>
       <c r="P30" s="34">
-        <v>3043</v>
+        <v>2793</v>
       </c>
       <c r="Q30" t="s">
         <v>372</v>
       </c>
-      <c r="R30" s="34">
-        <v>550</v>
+      <c r="R30" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5145,7 +5149,7 @@
         <v>147000</v>
       </c>
       <c r="C31" s="34">
-        <v>1816</v>
+        <v>1566</v>
       </c>
       <c r="D31" t="s">
         <v>332</v>
@@ -5184,13 +5188,13 @@
         <v>317</v>
       </c>
       <c r="P31" s="34">
-        <v>3043</v>
+        <v>2793</v>
       </c>
       <c r="Q31" t="s">
         <v>374</v>
       </c>
       <c r="R31" s="34">
-        <v>275</v>
+        <v>550</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5201,7 +5205,7 @@
         <v>155000</v>
       </c>
       <c r="C32" s="34">
-        <v>2007</v>
+        <v>1757</v>
       </c>
       <c r="D32" t="s">
         <v>332</v>
@@ -5240,13 +5244,13 @@
         <v>317</v>
       </c>
       <c r="P32" s="34">
-        <v>3483</v>
+        <v>3233</v>
       </c>
       <c r="Q32" t="s">
         <v>376</v>
       </c>
-      <c r="R32" s="8">
-        <v>0.75</v>
+      <c r="R32" s="34">
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -5257,7 +5261,7 @@
         <v>168000</v>
       </c>
       <c r="C33" s="34">
-        <v>2007</v>
+        <v>1757</v>
       </c>
       <c r="D33" t="s">
         <v>332</v>
@@ -5296,13 +5300,13 @@
         <v>317</v>
       </c>
       <c r="P33" s="34">
-        <v>3483</v>
+        <v>3233</v>
       </c>
       <c r="Q33" t="s">
         <v>378</v>
       </c>
       <c r="R33" s="8">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -5313,7 +5317,7 @@
         <v>380</v>
       </c>
       <c r="R34" s="8">
-        <v>1.75</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="35" spans="17:18" x14ac:dyDescent="0.25">
@@ -5321,7 +5325,7 @@
         <v>381</v>
       </c>
       <c r="R35" s="8">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -5332,7 +5336,7 @@
         <v>383</v>
       </c>
       <c r="R36" s="8">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -5345,8 +5349,8 @@
       <c r="Q37" t="s">
         <v>386</v>
       </c>
-      <c r="R37" s="34">
-        <v>5000</v>
+      <c r="R37" s="8">
+        <v>0.08</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -5360,7 +5364,7 @@
         <v>387</v>
       </c>
       <c r="R38" s="34">
-        <v>1500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -5374,7 +5378,7 @@
         <v>388</v>
       </c>
       <c r="R39" s="34">
-        <v>250</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -5388,7 +5392,7 @@
         <v>389</v>
       </c>
       <c r="R40" s="34">
-        <v>3519</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -5402,7 +5406,7 @@
         <v>390</v>
       </c>
       <c r="R41" s="34">
-        <v>261</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -5416,7 +5420,7 @@
         <v>391</v>
       </c>
       <c r="R42" s="34">
-        <v>4043</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -5430,7 +5434,7 @@
         <v>392</v>
       </c>
       <c r="R43" s="34">
-        <v>35</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -5444,7 +5448,7 @@
         <v>393</v>
       </c>
       <c r="R44" s="34">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -5458,7 +5462,7 @@
         <v>394</v>
       </c>
       <c r="R45" s="34">
-        <v>3.25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -5471,8 +5475,8 @@
       <c r="Q46" t="s">
         <v>395</v>
       </c>
-      <c r="R46" s="8">
-        <v>100</v>
+      <c r="R46" s="34">
+        <v>3.25</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -5485,8 +5489,8 @@
       <c r="Q47" t="s">
         <v>396</v>
       </c>
-      <c r="R47" s="34">
-        <v>200</v>
+      <c r="R47" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="17:18" x14ac:dyDescent="0.25">
@@ -5494,7 +5498,7 @@
         <v>397</v>
       </c>
       <c r="R48" s="34">
-        <v>60</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -5505,7 +5509,7 @@
         <v>399</v>
       </c>
       <c r="R49" s="34">
-        <v>2500</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -5519,15 +5523,21 @@
         <v>400</v>
       </c>
       <c r="R50" s="34">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>150</v>
       </c>
       <c r="B51" s="34">
         <v>1000</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>401</v>
+      </c>
+      <c r="R51" s="34">
+        <v>800</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -5572,7 +5582,7 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -5641,7 +5651,7 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -5750,7 +5760,7 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -5787,7 +5797,7 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
@@ -5972,7 +5982,7 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5980,21 +5990,21 @@
         <v>384</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B129" s="34">
         <v>0</v>
@@ -6011,7 +6021,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B130" s="34">
         <v>0</v>
@@ -6028,7 +6038,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B131" s="34">
         <v>0.30329</v>
@@ -6045,7 +6055,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B132" s="34">
         <v>0.56613</v>
@@ -6079,7 +6089,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B134" s="34">
         <v>1.33293</v>
@@ -6113,7 +6123,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B136" s="34">
         <v>2.1044</v>
@@ -6164,7 +6174,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B139" s="34">
         <v>3.63758</v>
@@ -6266,7 +6276,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B145" s="34">
         <v>10.60671</v>
@@ -6283,7 +6293,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B146" s="34">
         <v>11.334</v>
@@ -6300,7 +6310,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B147" s="34">
         <v>13.30059</v>
@@ -6334,7 +6344,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B149" s="34">
         <v>0</v>
@@ -6351,7 +6361,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B150" s="34">
         <v>25.921</v>
@@ -6368,7 +6378,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B151" s="34">
         <v>0</v>
@@ -6385,7 +6395,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B152" s="34">
         <v>0</v>
@@ -6402,7 +6412,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B153" s="34">
         <v>34.398</v>
@@ -6419,7 +6429,7 @@
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -6438,142 +6448,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="64" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="64" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="64" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="64" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="64" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="64" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="64" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="64" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="64" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="64" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="64" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="64" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="64" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -6583,22 +6593,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="64" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="64" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="64" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -6608,17 +6618,17 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="64" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="64" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
@@ -6628,57 +6638,57 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="64" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="64" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="64" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="64" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="64" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="64" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="64" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="64" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="64" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="64" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -12511,7 +12521,7 @@
         <v>171</v>
       </c>
       <c r="B7" s="9">
-        <f>WireTotal+SUM(Intake!E23:E34)</f>
+        <f>WireTotal+SUM(Intake!E23:E34)+IF(NTotal&gt;0,DataBoxCost,0)</f>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -13152,7 +13162,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="42">
-        <f>Estimate!B7+Estimate!B10</f>
+        <f>Estimate!B7+Estimate!B10+Estimate!B15</f>
       </c>
       <c r="E3" s="43">
         <f>ContingencyPct</f>
@@ -13360,7 +13370,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="42">
-        <f>Estimate!B18+Estimate!B15</f>
+        <f>Estimate!B18</f>
       </c>
       <c r="E12" s="43">
         <f>ContingencyPct</f>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -18,20 +18,20 @@
     <sheet sheetId="12" name="Instructions" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="ModelTable">RateCard!$A$4:$P$33</definedName>
-    <definedName name="SgSizes">RateCard!$A$38:$A$47</definedName>
-    <definedName name="SgTable">RateCard!$A$38:$B$47</definedName>
-    <definedName name="PnlSizes">RateCard!$A$51:$A$56</definedName>
-    <definedName name="PnlTable">RateCard!$A$51:$B$56</definedName>
-    <definedName name="TxSizes">RateCard!$A$60:$A$66</definedName>
-    <definedName name="TxTable">RateCard!$A$60:$B$66</definedName>
-    <definedName name="Brk480Sizes">RateCard!$A$70:$A$81</definedName>
-    <definedName name="BrkTbl480">RateCard!$A$70:$B$81</definedName>
-    <definedName name="Brk208Sizes">RateCard!$A$85:$A$87</definedName>
-    <definedName name="BrkTbl208">RateCard!$A$85:$B$87</definedName>
-    <definedName name="StdBrk">RateCard!$A$90:$A$125</definedName>
-    <definedName name="WireSizes">RateCard!$A$129:$A$153</definedName>
-    <definedName name="WireTable">RateCard!$A$129:$E$153</definedName>
+    <definedName name="ModelTable">RateCard!$A$4:$P$38</definedName>
+    <definedName name="SgSizes">RateCard!$A$43:$A$52</definedName>
+    <definedName name="SgTable">RateCard!$A$43:$B$52</definedName>
+    <definedName name="PnlSizes">RateCard!$A$56:$A$61</definedName>
+    <definedName name="PnlTable">RateCard!$A$56:$B$61</definedName>
+    <definedName name="TxSizes">RateCard!$A$65:$A$71</definedName>
+    <definedName name="TxTable">RateCard!$A$65:$B$71</definedName>
+    <definedName name="Brk480Sizes">RateCard!$A$75:$A$86</definedName>
+    <definedName name="BrkTbl480">RateCard!$A$75:$B$86</definedName>
+    <definedName name="Brk208Sizes">RateCard!$A$90:$A$92</definedName>
+    <definedName name="BrkTbl208">RateCard!$A$90:$B$92</definedName>
+    <definedName name="StdBrk">RateCard!$A$95:$A$130</definedName>
+    <definedName name="WireSizes">RateCard!$A$134:$A$158</definedName>
+    <definedName name="WireTable">RateCard!$A$134:$E$158</definedName>
     <definedName name="TerrainTable">RateCard!$Q$4:$U$7</definedName>
     <definedName name="TrenchRate">RateCard!$R$10</definedName>
     <definedName name="ContingencyPct">RateCard!$R$11</definedName>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="477">
   <si>
     <t>RFC INTAKE — EV Charging Project</t>
   </si>
@@ -713,7 +713,7 @@
     <t>SLD / electrical engineering (PE)</t>
   </si>
   <si>
-    <t>Construction PM — hours in col C</t>
+    <t>Construction PM (% of loaded labour — CEO basis)</t>
   </si>
   <si>
     <t>Plan check (AHJ, % of valuation for DCFC)</t>
@@ -1133,7 +1133,7 @@
     <t>DCFC 50kW Dual</t>
   </si>
   <si>
-    <t>Labor crew $/day</t>
+    <t>Labor crew $/day (CEO basis, fully burdened)</t>
   </si>
   <si>
     <t>DCFC 60kW</t>
@@ -1145,7 +1145,7 @@
     <t>DCFC 60kW Dual</t>
   </si>
   <si>
-    <t>CPM % of construction</t>
+    <t>Construction PM % of loaded labour (CEO basis)</t>
   </si>
   <si>
     <t>DCFC 100kW</t>
@@ -1262,19 +1262,52 @@
     <t>Concrete yd per DCFC pad</t>
   </si>
   <si>
+    <t>DCFC 30kW</t>
+  </si>
+  <si>
+    <t>8 AWG</t>
+  </si>
+  <si>
+    <t>Concrete yd per L2 pad</t>
+  </si>
+  <si>
+    <t>L2 Single 48A</t>
+  </si>
+  <si>
+    <t>Concrete yd — switchgear pad</t>
+  </si>
+  <si>
+    <t>Power cabinet 360kW</t>
+  </si>
+  <si>
+    <t>Concrete yd — step-down TX + sub-panel pad</t>
+  </si>
+  <si>
+    <t>Power cabinet 480kW</t>
+  </si>
+  <si>
+    <t>Concrete yd per bollard footing</t>
+  </si>
+  <si>
+    <t>Power cabinet 1280kW</t>
+  </si>
+  <si>
+    <t>Utility transformer pad $ (DCFC)</t>
+  </si>
+  <si>
     <t>Install $/u = conduit, terminations &amp; install hardware (engine-calibrated) — wire is priced on the Intake's Wire Runs block. 'Install EMT $/u' is the same allowance with surface EMT conduit (garage installs; strut racks are a separate Estimate line). Hardware $/u are budgetary — swap in CTX/vendor quotes.</t>
   </si>
   <si>
-    <t>Concrete yd per L2 pad</t>
-  </si>
-  <si>
-    <t>Concrete yd — switchgear pad</t>
+    <t>Commissioning $/DCFC</t>
+  </si>
+  <si>
+    <t>Commissioning $/L2</t>
   </si>
   <si>
     <t>Main switchgear 480V (website catalog)</t>
   </si>
   <si>
-    <t>Concrete yd — step-down TX + sub-panel pad</t>
+    <t>Equipment rentals base $</t>
   </si>
   <si>
     <t>Size</t>
@@ -1283,21 +1316,6 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Concrete yd per bollard footing</t>
-  </si>
-  <si>
-    <t>Utility transformer pad $ (DCFC)</t>
-  </si>
-  <si>
-    <t>Commissioning $/DCFC</t>
-  </si>
-  <si>
-    <t>Commissioning $/L2</t>
-  </si>
-  <si>
-    <t>Equipment rentals base $</t>
-  </si>
-  <si>
     <t>Equipment rentals $/labor-day</t>
   </si>
   <si>
@@ -1319,18 +1337,18 @@
     <t>Permit issuance base $ (AHJ)</t>
   </si>
   <si>
+    <t>Permit issuance $/charger</t>
+  </si>
+  <si>
+    <t>Utility application $ (DCFC site)</t>
+  </si>
+  <si>
+    <t>Utility application $ (L2-only site)</t>
+  </si>
+  <si>
     <t>Sub-panel / distribution 208V</t>
   </si>
   <si>
-    <t>Permit issuance $/charger</t>
-  </si>
-  <si>
-    <t>Utility application $ (DCFC site)</t>
-  </si>
-  <si>
-    <t>Utility application $ (L2-only site)</t>
-  </si>
-  <si>
     <t>Step-down transformer 208V (kVA)</t>
   </si>
   <si>
@@ -1367,9 +1385,6 @@
     <t>10 AWG</t>
   </si>
   <si>
-    <t>8 AWG</t>
-  </si>
-  <si>
     <t>4 AWG</t>
   </si>
   <si>
@@ -1532,13 +1547,13 @@
     <t>• Permits: L2-only = streamlined flat fees (AB 1236); DCFC = plan check ≈ 2% of construction valuation + issuance + utility fees.</t>
   </si>
   <si>
-    <t>• Design: site plan $2.5k + $150/charger (+$1k DCFC); SLD $6k + $900/DCFC + $150/L2 (PE). CPM = 5% of construction at $358/h.</t>
+    <t>• Design: site plan $2.5k + $150/charger (+$1k DCFC); SLD $6k + $900/DCFC + $150/L2 (PE). Construction PM = 15% of loaded labour (CEO basis).</t>
   </si>
   <si>
     <t>• 450 kcmil: ampacity and the Al $/ft are interpolated (not NEC 310.16 / not on the vendor list) — verify before quoting.</t>
   </si>
   <si>
-    <t>• Charger hardware and 'budgetary' breaker prices are allowances — swap in CTX price-book / vendor quotes on the RateCard.</t>
+    <t>• Charger hardware = CTX price-book list prices (EVSE Project Intake 2.9.0); breaker prices are allowances — swap in vendor quotes on the RateCard.</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1797,7 +1812,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3336,7 +3350,7 @@
   </sheetData>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" sqref="A23:A34">
-      <formula1>RateCard!$A$4:$A$33</formula1>
+      <formula1>RateCard!$A$4:$A$38</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="B45">
       <formula1>"flat,sloped,hilly,rocky"</formula1>
@@ -3345,7 +3359,7 @@
       <formula1>"Trenched,Surface EMT,Hybrid"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B53:B67">
-      <formula1>RateCard!$A$129:$A$153</formula1>
+      <formula1>RateCard!$A$134:$A$158</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="B78:B83">
       <formula1>"Yes,No"</formula1>
@@ -3516,7 +3530,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U154"/>
+  <dimension ref="A1:U159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3609,10 +3623,10 @@
       <c r="A4" t="s">
         <v>314</v>
       </c>
-      <c r="B4" s="34">
-        <v>3000</v>
-      </c>
-      <c r="C4" s="34">
+      <c r="B4" s="33">
+        <v>1402.5</v>
+      </c>
+      <c r="C4" s="33">
         <v>288</v>
       </c>
       <c r="D4" t="s">
@@ -3651,7 +3665,7 @@
       <c r="O4" t="s">
         <v>317</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="33">
         <v>553</v>
       </c>
       <c r="Q4" t="s">
@@ -3674,10 +3688,10 @@
       <c r="A5" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="34">
-        <v>3500</v>
-      </c>
-      <c r="C5" s="34">
+      <c r="B5" s="33">
+        <v>1402.5</v>
+      </c>
+      <c r="C5" s="33">
         <v>282</v>
       </c>
       <c r="D5" t="s">
@@ -3716,7 +3730,7 @@
       <c r="O5" t="s">
         <v>317</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="33">
         <v>540</v>
       </c>
       <c r="Q5" t="s">
@@ -3739,10 +3753,10 @@
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="34">
-        <v>4000</v>
-      </c>
-      <c r="C6" s="34">
+      <c r="B6" s="33">
+        <v>1402.5</v>
+      </c>
+      <c r="C6" s="33">
         <v>292</v>
       </c>
       <c r="D6" t="s">
@@ -3781,7 +3795,7 @@
       <c r="O6" t="s">
         <v>317</v>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="33">
         <v>563</v>
       </c>
       <c r="Q6" t="s">
@@ -3804,10 +3818,10 @@
       <c r="A7" t="s">
         <v>321</v>
       </c>
-      <c r="B7" s="34">
-        <v>5000</v>
-      </c>
-      <c r="C7" s="34">
+      <c r="B7" s="33">
+        <v>1650</v>
+      </c>
+      <c r="C7" s="33">
         <v>361</v>
       </c>
       <c r="D7" t="s">
@@ -3846,7 +3860,7 @@
       <c r="O7" t="s">
         <v>317</v>
       </c>
-      <c r="P7" s="34">
+      <c r="P7" s="33">
         <v>688</v>
       </c>
       <c r="Q7" t="s">
@@ -3869,10 +3883,10 @@
       <c r="A8" t="s">
         <v>324</v>
       </c>
-      <c r="B8" s="34">
-        <v>7500</v>
-      </c>
-      <c r="C8" s="34">
+      <c r="B8" s="33">
+        <v>1952.5</v>
+      </c>
+      <c r="C8" s="33">
         <v>693</v>
       </c>
       <c r="D8" t="s">
@@ -3911,7 +3925,7 @@
       <c r="O8" t="s">
         <v>317</v>
       </c>
-      <c r="P8" s="34">
+      <c r="P8" s="33">
         <v>1324</v>
       </c>
     </row>
@@ -3919,10 +3933,10 @@
       <c r="A9" t="s">
         <v>326</v>
       </c>
-      <c r="B9" s="34">
-        <v>5500</v>
-      </c>
-      <c r="C9" s="34">
+      <c r="B9" s="33">
+        <v>1952.5</v>
+      </c>
+      <c r="C9" s="33">
         <v>443</v>
       </c>
       <c r="D9" t="s">
@@ -3961,7 +3975,7 @@
       <c r="O9" t="s">
         <v>317</v>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="33">
         <v>842</v>
       </c>
     </row>
@@ -3969,10 +3983,10 @@
       <c r="A10" t="s">
         <v>327</v>
       </c>
-      <c r="B10" s="34">
-        <v>6500</v>
-      </c>
-      <c r="C10" s="34">
+      <c r="B10" s="33">
+        <v>1952.5</v>
+      </c>
+      <c r="C10" s="33">
         <v>460</v>
       </c>
       <c r="D10" t="s">
@@ -4011,13 +4025,13 @@
       <c r="O10" t="s">
         <v>317</v>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="33">
         <v>885</v>
       </c>
       <c r="Q10" t="s">
         <v>328</v>
       </c>
-      <c r="R10" s="34">
+      <c r="R10" s="33">
         <v>40.81</v>
       </c>
     </row>
@@ -4025,10 +4039,10 @@
       <c r="A11" t="s">
         <v>329</v>
       </c>
-      <c r="B11" s="34">
-        <v>8500</v>
-      </c>
-      <c r="C11" s="34">
+      <c r="B11" s="33">
+        <v>2194.5</v>
+      </c>
+      <c r="C11" s="33">
         <v>612</v>
       </c>
       <c r="D11" t="s">
@@ -4067,13 +4081,13 @@
       <c r="O11" t="s">
         <v>317</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="33">
         <v>1150</v>
       </c>
       <c r="Q11" t="s">
         <v>330</v>
       </c>
-      <c r="R11" s="63">
+      <c r="R11" s="62">
         <v>0.1</v>
       </c>
     </row>
@@ -4081,10 +4095,10 @@
       <c r="A12" t="s">
         <v>331</v>
       </c>
-      <c r="B12" s="34">
-        <v>32000</v>
-      </c>
-      <c r="C12" s="34">
+      <c r="B12" s="33">
+        <v>23600</v>
+      </c>
+      <c r="C12" s="33">
         <v>404</v>
       </c>
       <c r="D12" t="s">
@@ -4123,13 +4137,13 @@
       <c r="O12" t="s">
         <v>317</v>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="33">
         <v>831</v>
       </c>
       <c r="Q12" t="s">
         <v>334</v>
       </c>
-      <c r="R12" s="63">
+      <c r="R12" s="62">
         <v>0.0725</v>
       </c>
     </row>
@@ -4137,10 +4151,10 @@
       <c r="A13" t="s">
         <v>335</v>
       </c>
-      <c r="B13" s="34">
-        <v>35000</v>
-      </c>
-      <c r="C13" s="34">
+      <c r="B13" s="33">
+        <v>23600</v>
+      </c>
+      <c r="C13" s="33">
         <v>404</v>
       </c>
       <c r="D13" t="s">
@@ -4179,24 +4193,24 @@
       <c r="O13" t="s">
         <v>317</v>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="33">
         <v>831</v>
       </c>
       <c r="Q13" t="s">
         <v>336</v>
       </c>
-      <c r="R13" s="34">
-        <v>2250</v>
+      <c r="R13" s="33">
+        <v>2750</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>337</v>
       </c>
-      <c r="B14" s="34">
-        <v>38000</v>
-      </c>
-      <c r="C14" s="34">
+      <c r="B14" s="33">
+        <v>28500</v>
+      </c>
+      <c r="C14" s="33">
         <v>407</v>
       </c>
       <c r="D14" t="s">
@@ -4235,13 +4249,13 @@
       <c r="O14" t="s">
         <v>317</v>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="33">
         <v>842</v>
       </c>
       <c r="Q14" t="s">
         <v>338</v>
       </c>
-      <c r="R14" s="34">
+      <c r="R14" s="33">
         <v>358</v>
       </c>
     </row>
@@ -4249,10 +4263,10 @@
       <c r="A15" t="s">
         <v>339</v>
       </c>
-      <c r="B15" s="34">
-        <v>42000</v>
-      </c>
-      <c r="C15" s="34">
+      <c r="B15" s="33">
+        <v>28500</v>
+      </c>
+      <c r="C15" s="33">
         <v>407</v>
       </c>
       <c r="D15" t="s">
@@ -4291,24 +4305,24 @@
       <c r="O15" t="s">
         <v>317</v>
       </c>
-      <c r="P15" s="34">
+      <c r="P15" s="33">
         <v>842</v>
       </c>
       <c r="Q15" t="s">
         <v>340</v>
       </c>
-      <c r="R15" s="63">
-        <v>0.05</v>
+      <c r="R15" s="62">
+        <v>0.15</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>341</v>
       </c>
-      <c r="B16" s="34">
-        <v>52000</v>
-      </c>
-      <c r="C16" s="34">
+      <c r="B16" s="33">
+        <v>45500</v>
+      </c>
+      <c r="C16" s="33">
         <v>518</v>
       </c>
       <c r="D16" t="s">
@@ -4347,13 +4361,13 @@
       <c r="O16" t="s">
         <v>317</v>
       </c>
-      <c r="P16" s="34">
+      <c r="P16" s="33">
         <v>986</v>
       </c>
       <c r="Q16" t="s">
         <v>343</v>
       </c>
-      <c r="R16" s="34">
+      <c r="R16" s="33">
         <v>1500</v>
       </c>
     </row>
@@ -4361,10 +4375,10 @@
       <c r="A17" t="s">
         <v>344</v>
       </c>
-      <c r="B17" s="34">
-        <v>57000</v>
-      </c>
-      <c r="C17" s="34">
+      <c r="B17" s="33">
+        <v>45500</v>
+      </c>
+      <c r="C17" s="33">
         <v>518</v>
       </c>
       <c r="D17" t="s">
@@ -4403,7 +4417,7 @@
       <c r="O17" t="s">
         <v>317</v>
       </c>
-      <c r="P17" s="34">
+      <c r="P17" s="33">
         <v>986</v>
       </c>
       <c r="Q17" t="s">
@@ -4417,10 +4431,10 @@
       <c r="A18" t="s">
         <v>346</v>
       </c>
-      <c r="B18" s="34">
-        <v>60000</v>
-      </c>
-      <c r="C18" s="34">
+      <c r="B18" s="33">
+        <v>54000</v>
+      </c>
+      <c r="C18" s="33">
         <v>558</v>
       </c>
       <c r="D18" t="s">
@@ -4459,13 +4473,13 @@
       <c r="O18" t="s">
         <v>317</v>
       </c>
-      <c r="P18" s="34">
+      <c r="P18" s="33">
         <v>1045</v>
       </c>
       <c r="Q18" t="s">
         <v>347</v>
       </c>
-      <c r="R18" s="34">
+      <c r="R18" s="33">
         <v>1500</v>
       </c>
     </row>
@@ -4473,10 +4487,10 @@
       <c r="A19" t="s">
         <v>348</v>
       </c>
-      <c r="B19" s="34">
-        <v>66000</v>
-      </c>
-      <c r="C19" s="34">
+      <c r="B19" s="33">
+        <v>54000</v>
+      </c>
+      <c r="C19" s="33">
         <v>558</v>
       </c>
       <c r="D19" t="s">
@@ -4515,13 +4529,13 @@
       <c r="O19" t="s">
         <v>317</v>
       </c>
-      <c r="P19" s="34">
+      <c r="P19" s="33">
         <v>1045</v>
       </c>
       <c r="Q19" t="s">
         <v>349</v>
       </c>
-      <c r="R19" s="34">
+      <c r="R19" s="33">
         <v>6500</v>
       </c>
     </row>
@@ -4529,10 +4543,10 @@
       <c r="A20" t="s">
         <v>350</v>
       </c>
-      <c r="B20" s="34">
-        <v>72000</v>
-      </c>
-      <c r="C20" s="34">
+      <c r="B20" s="33">
+        <v>57000</v>
+      </c>
+      <c r="C20" s="33">
         <v>753</v>
       </c>
       <c r="D20" t="s">
@@ -4571,13 +4585,13 @@
       <c r="O20" t="s">
         <v>317</v>
       </c>
-      <c r="P20" s="34">
+      <c r="P20" s="33">
         <v>1420</v>
       </c>
       <c r="Q20" t="s">
         <v>352</v>
       </c>
-      <c r="R20" s="34">
+      <c r="R20" s="33">
         <v>4900</v>
       </c>
     </row>
@@ -4585,10 +4599,10 @@
       <c r="A21" t="s">
         <v>353</v>
       </c>
-      <c r="B21" s="34">
-        <v>79000</v>
-      </c>
-      <c r="C21" s="34">
+      <c r="B21" s="33">
+        <v>57000</v>
+      </c>
+      <c r="C21" s="33">
         <v>753</v>
       </c>
       <c r="D21" t="s">
@@ -4627,13 +4641,13 @@
       <c r="O21" t="s">
         <v>317</v>
       </c>
-      <c r="P21" s="34">
+      <c r="P21" s="33">
         <v>1420</v>
       </c>
       <c r="Q21" t="s">
         <v>354</v>
       </c>
-      <c r="R21" s="34">
+      <c r="R21" s="33">
         <v>3500</v>
       </c>
     </row>
@@ -4641,10 +4655,10 @@
       <c r="A22" t="s">
         <v>355</v>
       </c>
-      <c r="B22" s="34">
-        <v>80000</v>
-      </c>
-      <c r="C22" s="34">
+      <c r="B22" s="33">
+        <v>62000</v>
+      </c>
+      <c r="C22" s="33">
         <v>836</v>
       </c>
       <c r="D22" t="s">
@@ -4683,13 +4697,13 @@
       <c r="O22" t="s">
         <v>317</v>
       </c>
-      <c r="P22" s="34">
+      <c r="P22" s="33">
         <v>1530</v>
       </c>
       <c r="Q22" t="s">
         <v>356</v>
       </c>
-      <c r="R22" s="34">
+      <c r="R22" s="33">
         <v>5200</v>
       </c>
     </row>
@@ -4697,10 +4711,10 @@
       <c r="A23" t="s">
         <v>357</v>
       </c>
-      <c r="B23" s="34">
-        <v>88000</v>
-      </c>
-      <c r="C23" s="34">
+      <c r="B23" s="33">
+        <v>62000</v>
+      </c>
+      <c r="C23" s="33">
         <v>836</v>
       </c>
       <c r="D23" t="s">
@@ -4739,13 +4753,13 @@
       <c r="O23" t="s">
         <v>317</v>
       </c>
-      <c r="P23" s="34">
+      <c r="P23" s="33">
         <v>1530</v>
       </c>
       <c r="Q23" t="s">
         <v>358</v>
       </c>
-      <c r="R23" s="34">
+      <c r="R23" s="33">
         <v>165</v>
       </c>
     </row>
@@ -4753,10 +4767,10 @@
       <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="34">
-        <v>92000</v>
-      </c>
-      <c r="C24" s="34">
+      <c r="B24" s="33">
+        <v>68000</v>
+      </c>
+      <c r="C24" s="33">
         <v>932</v>
       </c>
       <c r="D24" t="s">
@@ -4795,13 +4809,13 @@
       <c r="O24" t="s">
         <v>317</v>
       </c>
-      <c r="P24" s="34">
+      <c r="P24" s="33">
         <v>1774</v>
       </c>
       <c r="Q24" t="s">
         <v>213</v>
       </c>
-      <c r="R24" s="34">
+      <c r="R24" s="33">
         <v>125</v>
       </c>
     </row>
@@ -4809,10 +4823,10 @@
       <c r="A25" t="s">
         <v>360</v>
       </c>
-      <c r="B25" s="34">
-        <v>100000</v>
-      </c>
-      <c r="C25" s="34">
+      <c r="B25" s="33">
+        <v>68000</v>
+      </c>
+      <c r="C25" s="33">
         <v>932</v>
       </c>
       <c r="D25" t="s">
@@ -4851,13 +4865,13 @@
       <c r="O25" t="s">
         <v>317</v>
       </c>
-      <c r="P25" s="34">
+      <c r="P25" s="33">
         <v>1774</v>
       </c>
       <c r="Q25" t="s">
         <v>361</v>
       </c>
-      <c r="R25" s="34">
+      <c r="R25" s="33">
         <v>5</v>
       </c>
     </row>
@@ -4865,10 +4879,10 @@
       <c r="A26" t="s">
         <v>362</v>
       </c>
-      <c r="B26" s="34">
-        <v>105000</v>
-      </c>
-      <c r="C26" s="34">
+      <c r="B26" s="33">
+        <v>80000</v>
+      </c>
+      <c r="C26" s="33">
         <v>1268</v>
       </c>
       <c r="D26" t="s">
@@ -4907,7 +4921,7 @@
       <c r="O26" t="s">
         <v>317</v>
       </c>
-      <c r="P26" s="34">
+      <c r="P26" s="33">
         <v>2124</v>
       </c>
       <c r="Q26" t="s">
@@ -4921,10 +4935,10 @@
       <c r="A27" t="s">
         <v>364</v>
       </c>
-      <c r="B27" s="34">
-        <v>115000</v>
-      </c>
-      <c r="C27" s="34">
+      <c r="B27" s="33">
+        <v>80000</v>
+      </c>
+      <c r="C27" s="33">
         <v>1268</v>
       </c>
       <c r="D27" t="s">
@@ -4963,13 +4977,13 @@
       <c r="O27" t="s">
         <v>317</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="33">
         <v>2124</v>
       </c>
       <c r="Q27" t="s">
         <v>365</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="33">
         <v>110</v>
       </c>
     </row>
@@ -4977,10 +4991,10 @@
       <c r="A28" t="s">
         <v>366</v>
       </c>
-      <c r="B28" s="34">
-        <v>120000</v>
-      </c>
-      <c r="C28" s="34">
+      <c r="B28" s="33">
+        <v>85500</v>
+      </c>
+      <c r="C28" s="33">
         <v>1566</v>
       </c>
       <c r="D28" t="s">
@@ -5019,7 +5033,7 @@
       <c r="O28" t="s">
         <v>317</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="33">
         <v>2793</v>
       </c>
       <c r="Q28" t="s">
@@ -5033,10 +5047,10 @@
       <c r="A29" t="s">
         <v>369</v>
       </c>
-      <c r="B29" s="34">
-        <v>130000</v>
-      </c>
-      <c r="C29" s="34">
+      <c r="B29" s="33">
+        <v>85500</v>
+      </c>
+      <c r="C29" s="33">
         <v>1566</v>
       </c>
       <c r="D29" t="s">
@@ -5075,7 +5089,7 @@
       <c r="O29" t="s">
         <v>317</v>
       </c>
-      <c r="P29" s="34">
+      <c r="P29" s="33">
         <v>2793</v>
       </c>
       <c r="Q29" t="s">
@@ -5089,10 +5103,10 @@
       <c r="A30" t="s">
         <v>371</v>
       </c>
-      <c r="B30" s="34">
-        <v>135000</v>
-      </c>
-      <c r="C30" s="34">
+      <c r="B30" s="33">
+        <v>89500</v>
+      </c>
+      <c r="C30" s="33">
         <v>1566</v>
       </c>
       <c r="D30" t="s">
@@ -5131,7 +5145,7 @@
       <c r="O30" t="s">
         <v>317</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="33">
         <v>2793</v>
       </c>
       <c r="Q30" t="s">
@@ -5145,10 +5159,10 @@
       <c r="A31" t="s">
         <v>373</v>
       </c>
-      <c r="B31" s="34">
-        <v>147000</v>
-      </c>
-      <c r="C31" s="34">
+      <c r="B31" s="33">
+        <v>89500</v>
+      </c>
+      <c r="C31" s="33">
         <v>1566</v>
       </c>
       <c r="D31" t="s">
@@ -5187,13 +5201,13 @@
       <c r="O31" t="s">
         <v>317</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="33">
         <v>2793</v>
       </c>
       <c r="Q31" t="s">
         <v>374</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="33">
         <v>550</v>
       </c>
     </row>
@@ -5201,10 +5215,10 @@
       <c r="A32" t="s">
         <v>375</v>
       </c>
-      <c r="B32" s="34">
-        <v>155000</v>
-      </c>
-      <c r="C32" s="34">
+      <c r="B32" s="33">
+        <v>99000</v>
+      </c>
+      <c r="C32" s="33">
         <v>1757</v>
       </c>
       <c r="D32" t="s">
@@ -5243,13 +5257,13 @@
       <c r="O32" t="s">
         <v>317</v>
       </c>
-      <c r="P32" s="34">
+      <c r="P32" s="33">
         <v>3233</v>
       </c>
       <c r="Q32" t="s">
         <v>376</v>
       </c>
-      <c r="R32" s="34">
+      <c r="R32" s="33">
         <v>275</v>
       </c>
     </row>
@@ -5257,10 +5271,10 @@
       <c r="A33" t="s">
         <v>377</v>
       </c>
-      <c r="B33" s="34">
-        <v>168000</v>
-      </c>
-      <c r="C33" s="34">
+      <c r="B33" s="33">
+        <v>99000</v>
+      </c>
+      <c r="C33" s="33">
         <v>1757</v>
       </c>
       <c r="D33" t="s">
@@ -5299,7 +5313,7 @@
       <c r="O33" t="s">
         <v>317</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="33">
         <v>3233</v>
       </c>
       <c r="Q33" t="s">
@@ -5310,1126 +5324,1374 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" t="s">
         <v>379</v>
       </c>
+      <c r="B34" s="33">
+        <v>0</v>
+      </c>
+      <c r="C34" s="33">
+        <v>270</v>
+      </c>
+      <c r="D34" t="s">
+        <v>332</v>
+      </c>
+      <c r="E34">
+        <v>480</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>36.1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>30</v>
+      </c>
+      <c r="K34">
+        <v>36.1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
+      </c>
+      <c r="N34" t="s">
+        <v>380</v>
+      </c>
+      <c r="O34" t="s">
+        <v>317</v>
+      </c>
+      <c r="P34" s="33">
+        <v>490</v>
+      </c>
       <c r="Q34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R34" s="8">
         <v>0.35</v>
       </c>
     </row>
-    <row r="35" spans="17:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>382</v>
+      </c>
+      <c r="B35" s="33">
+        <v>0</v>
+      </c>
+      <c r="C35" s="33">
+        <v>301</v>
+      </c>
+      <c r="D35" t="s">
+        <v>315</v>
+      </c>
+      <c r="E35">
+        <v>208</v>
+      </c>
+      <c r="F35">
+        <v>60</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>48</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>9.984</v>
+      </c>
+      <c r="K35">
+        <v>48</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
+      <c r="N35" t="s">
+        <v>316</v>
+      </c>
+      <c r="O35" t="s">
+        <v>317</v>
+      </c>
+      <c r="P35" s="33">
+        <v>572</v>
+      </c>
       <c r="Q35" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="R35" s="8">
         <v>1.75</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>382</v>
+      <c r="A36" t="s">
+        <v>384</v>
+      </c>
+      <c r="B36" s="33">
+        <v>0</v>
+      </c>
+      <c r="C36" s="33">
+        <v>1195</v>
+      </c>
+      <c r="D36" t="s">
+        <v>332</v>
+      </c>
+      <c r="E36">
+        <v>480</v>
+      </c>
+      <c r="F36">
+        <v>300</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="H36">
+        <v>472.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>196.5</v>
+      </c>
+      <c r="K36">
+        <v>236.4</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>3</v>
+      </c>
+      <c r="N36" t="s">
+        <v>333</v>
+      </c>
+      <c r="O36" t="s">
+        <v>317</v>
+      </c>
+      <c r="P36" s="33">
+        <v>1712</v>
       </c>
       <c r="Q36" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="R36" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>385</v>
+      <c r="A37" t="s">
+        <v>386</v>
+      </c>
+      <c r="B37" s="33">
+        <v>0</v>
+      </c>
+      <c r="C37" s="33">
+        <v>970</v>
+      </c>
+      <c r="D37" t="s">
+        <v>332</v>
+      </c>
+      <c r="E37">
+        <v>480</v>
+      </c>
+      <c r="F37">
+        <v>400</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>630.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>262</v>
+      </c>
+      <c r="K37">
+        <v>315.2</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>3</v>
+      </c>
+      <c r="N37" t="s">
+        <v>342</v>
+      </c>
+      <c r="O37" t="s">
+        <v>317</v>
+      </c>
+      <c r="P37" s="33">
+        <v>1684</v>
       </c>
       <c r="Q37" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R37" s="8">
         <v>0.08</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" t="s">
+        <v>388</v>
+      </c>
+      <c r="B38" s="33">
+        <v>0</v>
+      </c>
+      <c r="C38" s="33">
+        <v>2147</v>
+      </c>
+      <c r="D38" t="s">
+        <v>332</v>
+      </c>
+      <c r="E38">
+        <v>480</v>
+      </c>
+      <c r="F38">
         <v>400</v>
       </c>
-      <c r="B38" s="34">
-        <v>20426.82</v>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>1680.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>232.9</v>
+      </c>
+      <c r="K38">
+        <v>280.1</v>
+      </c>
+      <c r="L38">
+        <v>6</v>
+      </c>
+      <c r="M38">
+        <v>3</v>
+      </c>
+      <c r="N38" t="s">
+        <v>316</v>
+      </c>
+      <c r="O38" t="s">
+        <v>317</v>
+      </c>
+      <c r="P38" s="33">
+        <v>3085</v>
       </c>
       <c r="Q38" t="s">
-        <v>387</v>
-      </c>
-      <c r="R38" s="34">
+        <v>389</v>
+      </c>
+      <c r="R38" s="33">
         <v>5000</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>800</v>
-      </c>
-      <c r="B39" s="34">
-        <v>31187</v>
+      <c r="A39" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="Q39" t="s">
-        <v>388</v>
-      </c>
-      <c r="R39" s="34">
+        <v>391</v>
+      </c>
+      <c r="R39" s="33">
         <v>1500</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>1000</v>
-      </c>
-      <c r="B40" s="34">
-        <v>36812.5</v>
-      </c>
+    <row r="40" spans="17:18" x14ac:dyDescent="0.25">
       <c r="Q40" t="s">
-        <v>389</v>
-      </c>
-      <c r="R40" s="34">
+        <v>392</v>
+      </c>
+      <c r="R40" s="33">
         <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>1200</v>
-      </c>
-      <c r="B41" s="34">
-        <v>43292.68</v>
+      <c r="A41" s="3" t="s">
+        <v>393</v>
       </c>
       <c r="Q41" t="s">
-        <v>390</v>
-      </c>
-      <c r="R41" s="34">
+        <v>394</v>
+      </c>
+      <c r="R41" s="33">
         <v>3519</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>1600</v>
-      </c>
-      <c r="B42" s="34">
-        <v>56750</v>
+      <c r="A42" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>396</v>
       </c>
       <c r="Q42" t="s">
-        <v>391</v>
-      </c>
-      <c r="R42" s="34">
+        <v>397</v>
+      </c>
+      <c r="R42" s="33">
         <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>2000</v>
-      </c>
-      <c r="B43" s="34">
-        <v>55000</v>
+        <v>400</v>
+      </c>
+      <c r="B43" s="33">
+        <v>20426.82</v>
       </c>
       <c r="Q43" t="s">
-        <v>392</v>
-      </c>
-      <c r="R43" s="34">
+        <v>398</v>
+      </c>
+      <c r="R43" s="33">
         <v>4043</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>2500</v>
-      </c>
-      <c r="B44" s="34">
-        <v>60000</v>
+        <v>800</v>
+      </c>
+      <c r="B44" s="33">
+        <v>31187</v>
       </c>
       <c r="Q44" t="s">
-        <v>393</v>
-      </c>
-      <c r="R44" s="34">
+        <v>399</v>
+      </c>
+      <c r="R44" s="33">
         <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>3000</v>
-      </c>
-      <c r="B45" s="34">
-        <v>65000</v>
+        <v>1000</v>
+      </c>
+      <c r="B45" s="33">
+        <v>36812.5</v>
       </c>
       <c r="Q45" t="s">
-        <v>394</v>
-      </c>
-      <c r="R45" s="34">
+        <v>400</v>
+      </c>
+      <c r="R45" s="33">
         <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>4000</v>
-      </c>
-      <c r="B46" s="34">
-        <v>67500</v>
+        <v>1200</v>
+      </c>
+      <c r="B46" s="33">
+        <v>43292.68</v>
       </c>
       <c r="Q46" t="s">
-        <v>395</v>
-      </c>
-      <c r="R46" s="34">
+        <v>401</v>
+      </c>
+      <c r="R46" s="33">
         <v>3.25</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>5000</v>
-      </c>
-      <c r="B47" s="34">
-        <v>70000</v>
+        <v>1600</v>
+      </c>
+      <c r="B47" s="33">
+        <v>56750</v>
       </c>
       <c r="Q47" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="R47" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="17:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2000</v>
+      </c>
+      <c r="B48" s="33">
+        <v>55000</v>
+      </c>
       <c r="Q48" t="s">
-        <v>397</v>
-      </c>
-      <c r="R48" s="34">
+        <v>403</v>
+      </c>
+      <c r="R48" s="33">
         <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>398</v>
+      <c r="A49">
+        <v>2500</v>
+      </c>
+      <c r="B49" s="33">
+        <v>60000</v>
       </c>
       <c r="Q49" t="s">
-        <v>399</v>
-      </c>
-      <c r="R49" s="34">
+        <v>404</v>
+      </c>
+      <c r="R49" s="33">
         <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>385</v>
+      <c r="A50">
+        <v>3000</v>
+      </c>
+      <c r="B50" s="33">
+        <v>65000</v>
       </c>
       <c r="Q50" t="s">
-        <v>400</v>
-      </c>
-      <c r="R50" s="34">
+        <v>405</v>
+      </c>
+      <c r="R50" s="33">
         <v>2500</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>150</v>
-      </c>
-      <c r="B51" s="34">
-        <v>1000</v>
+        <v>4000</v>
+      </c>
+      <c r="B51" s="33">
+        <v>67500</v>
       </c>
       <c r="Q51" t="s">
-        <v>401</v>
-      </c>
-      <c r="R51" s="34">
+        <v>406</v>
+      </c>
+      <c r="R51" s="33">
         <v>800</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>250</v>
-      </c>
-      <c r="B52" s="34">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>400</v>
-      </c>
-      <c r="B53" s="34">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>600</v>
-      </c>
-      <c r="B54" s="34">
-        <v>5387</v>
+        <v>5000</v>
+      </c>
+      <c r="B52" s="33">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>800</v>
-      </c>
-      <c r="B55" s="34">
-        <v>4650</v>
+      <c r="A55" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
+        <v>150</v>
+      </c>
+      <c r="B56" s="33">
         <v>1000</v>
       </c>
-      <c r="B56" s="34">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>402</v>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>250</v>
+      </c>
+      <c r="B57" s="33">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>400</v>
+      </c>
+      <c r="B58" s="33">
+        <v>1660</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>385</v>
+      <c r="A59">
+        <v>600</v>
+      </c>
+      <c r="B59" s="33">
+        <v>5387</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>75</v>
-      </c>
-      <c r="B60" s="34">
-        <v>2970</v>
+        <v>800</v>
+      </c>
+      <c r="B60" s="33">
+        <v>4650</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>112.5</v>
-      </c>
-      <c r="B61" s="34">
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>150</v>
-      </c>
-      <c r="B62" s="34">
-        <v>5298</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>175</v>
-      </c>
-      <c r="B63" s="34">
-        <v>6000</v>
+        <v>1000</v>
+      </c>
+      <c r="B61" s="33">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>225</v>
-      </c>
-      <c r="B64" s="34">
-        <v>7144</v>
+      <c r="A64" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>300</v>
-      </c>
-      <c r="B65" s="34">
-        <v>10493</v>
+        <v>75</v>
+      </c>
+      <c r="B65" s="33">
+        <v>2970</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>500</v>
-      </c>
-      <c r="B66" s="34">
-        <v>14500</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>403</v>
+        <v>112.5</v>
+      </c>
+      <c r="B66" s="33">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>150</v>
+      </c>
+      <c r="B67" s="33">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>175</v>
+      </c>
+      <c r="B68" s="33">
+        <v>6000</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>385</v>
+      <c r="A69">
+        <v>225</v>
+      </c>
+      <c r="B69" s="33">
+        <v>7144</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>100</v>
-      </c>
-      <c r="B70" s="34">
-        <v>350</v>
+        <v>300</v>
+      </c>
+      <c r="B70" s="33">
+        <v>10493</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>125</v>
-      </c>
-      <c r="B71" s="34">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>150</v>
-      </c>
-      <c r="B72" s="34">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>175</v>
-      </c>
-      <c r="B73" s="34">
-        <v>550</v>
+        <v>500</v>
+      </c>
+      <c r="B71" s="33">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>200</v>
-      </c>
-      <c r="B74" s="34">
-        <v>650</v>
+      <c r="A74" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>225</v>
-      </c>
-      <c r="B75" s="34">
-        <v>700</v>
+        <v>100</v>
+      </c>
+      <c r="B75" s="33">
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>250</v>
-      </c>
-      <c r="B76" s="34">
-        <v>750</v>
+        <v>125</v>
+      </c>
+      <c r="B76" s="33">
+        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>300</v>
-      </c>
-      <c r="B77" s="34">
-        <v>800</v>
+        <v>150</v>
+      </c>
+      <c r="B77" s="33">
+        <v>480</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>350</v>
-      </c>
-      <c r="B78" s="34">
-        <v>1000</v>
+        <v>175</v>
+      </c>
+      <c r="B78" s="33">
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>400</v>
-      </c>
-      <c r="B79" s="34">
-        <v>1200</v>
+        <v>200</v>
+      </c>
+      <c r="B79" s="33">
+        <v>650</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>500</v>
-      </c>
-      <c r="B80" s="34">
-        <v>1800</v>
+        <v>225</v>
+      </c>
+      <c r="B80" s="33">
+        <v>700</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>600</v>
-      </c>
-      <c r="B81" s="34">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>404</v>
+        <v>250</v>
+      </c>
+      <c r="B81" s="33">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>300</v>
+      </c>
+      <c r="B82" s="33">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>350</v>
+      </c>
+      <c r="B83" s="33">
+        <v>1000</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>385</v>
+      <c r="A84">
+        <v>400</v>
+      </c>
+      <c r="B84" s="33">
+        <v>1200</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>40</v>
-      </c>
-      <c r="B85" s="34">
-        <v>60</v>
+        <v>500</v>
+      </c>
+      <c r="B85" s="33">
+        <v>1800</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
+        <v>600</v>
+      </c>
+      <c r="B86" s="33">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>40</v>
+      </c>
+      <c r="B90" s="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91">
         <v>50</v>
       </c>
-      <c r="B86" s="34">
+      <c r="B91" s="33">
         <v>75</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92">
         <v>60</v>
       </c>
-      <c r="B87" s="34">
+      <c r="B92" s="33">
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>30</v>
-      </c>
-    </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>35</v>
+      <c r="A94" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>90</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>125</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>150</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>175</v>
+        <v>90</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>225</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>250</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>350</v>
+        <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>450</v>
+        <v>225</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>1000</v>
+        <v>450</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>1200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>1600</v>
+        <v>600</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>2000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>2500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>4000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
         <v>5000</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>411</v>
-      </c>
-      <c r="B129" s="34">
-        <v>0</v>
-      </c>
-      <c r="C129" s="34">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>20</v>
-      </c>
-      <c r="E129">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B130" s="34">
-        <v>0</v>
-      </c>
-      <c r="C130" s="34">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>25</v>
-      </c>
-      <c r="E130">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B133" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B131" s="34">
-        <v>0.30329</v>
-      </c>
-      <c r="C131" s="34">
-        <v>0.28</v>
-      </c>
-      <c r="D131">
-        <v>35</v>
-      </c>
-      <c r="E131">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="C133" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B132" s="34">
-        <v>0.56613</v>
-      </c>
-      <c r="C132" s="34">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>50</v>
-      </c>
-      <c r="E132">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>316</v>
-      </c>
-      <c r="B133" s="34">
-        <v>0.87104</v>
-      </c>
-      <c r="C133" s="34">
-        <v>0.30636</v>
-      </c>
-      <c r="D133">
-        <v>65</v>
-      </c>
-      <c r="E133">
-        <v>50</v>
+      <c r="D133" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>415</v>
-      </c>
-      <c r="B134" s="34">
-        <v>1.33293</v>
-      </c>
-      <c r="C134" s="34">
-        <v>0.37998</v>
+        <v>417</v>
+      </c>
+      <c r="B134" s="33">
+        <v>0</v>
+      </c>
+      <c r="C134" s="33">
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E134">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>322</v>
-      </c>
-      <c r="B135" s="34">
-        <v>1.68126</v>
-      </c>
-      <c r="C135" s="34">
-        <v>0.36681</v>
+        <v>418</v>
+      </c>
+      <c r="B135" s="33">
+        <v>0</v>
+      </c>
+      <c r="C135" s="33">
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E135">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>416</v>
-      </c>
-      <c r="B136" s="34">
-        <v>2.1044</v>
-      </c>
-      <c r="C136" s="34">
-        <v>0.4821</v>
+        <v>419</v>
+      </c>
+      <c r="B136" s="33">
+        <v>0.30329</v>
+      </c>
+      <c r="C136" s="33">
+        <v>0.28</v>
       </c>
       <c r="D136">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="E136">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>325</v>
-      </c>
-      <c r="B137" s="34">
-        <v>2.39833</v>
-      </c>
-      <c r="C137" s="34">
-        <v>0.66733</v>
+        <v>380</v>
+      </c>
+      <c r="B137" s="33">
+        <v>0.56613</v>
+      </c>
+      <c r="C137" s="33">
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="E137">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>333</v>
-      </c>
-      <c r="B138" s="34">
-        <v>2.95304</v>
-      </c>
-      <c r="C138" s="34">
-        <v>0.75045</v>
+        <v>316</v>
+      </c>
+      <c r="B138" s="33">
+        <v>0.87104</v>
+      </c>
+      <c r="C138" s="33">
+        <v>0.30636</v>
       </c>
       <c r="D138">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="E138">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>417</v>
-      </c>
-      <c r="B139" s="34">
-        <v>3.63758</v>
-      </c>
-      <c r="C139" s="34">
-        <v>0.88701</v>
+        <v>420</v>
+      </c>
+      <c r="B139" s="33">
+        <v>1.33293</v>
+      </c>
+      <c r="C139" s="33">
+        <v>0.37998</v>
       </c>
       <c r="D139">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="E139">
-        <v>135</v>
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>342</v>
-      </c>
-      <c r="B140" s="34">
-        <v>4.5658</v>
-      </c>
-      <c r="C140" s="34">
-        <v>1.09956</v>
+        <v>322</v>
+      </c>
+      <c r="B140" s="33">
+        <v>1.68126</v>
+      </c>
+      <c r="C140" s="33">
+        <v>0.36681</v>
       </c>
       <c r="D140">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E140">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>58</v>
-      </c>
-      <c r="B141" s="34">
-        <v>5.73045</v>
-      </c>
-      <c r="C141" s="34">
-        <v>1.2278</v>
+        <v>421</v>
+      </c>
+      <c r="B141" s="33">
+        <v>2.1044</v>
+      </c>
+      <c r="C141" s="33">
+        <v>0.4821</v>
       </c>
       <c r="D141">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="E141">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>367</v>
-      </c>
-      <c r="B142" s="34">
-        <v>6.64016</v>
-      </c>
-      <c r="C142" s="34">
-        <v>1.49616</v>
+        <v>325</v>
+      </c>
+      <c r="B142" s="33">
+        <v>2.39833</v>
+      </c>
+      <c r="C142" s="33">
+        <v>0.66733</v>
       </c>
       <c r="D142">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="E142">
-        <v>205</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>351</v>
-      </c>
-      <c r="B143" s="34">
-        <v>7.9632</v>
-      </c>
-      <c r="C143" s="34">
-        <v>2.06137</v>
+        <v>333</v>
+      </c>
+      <c r="B143" s="33">
+        <v>2.95304</v>
+      </c>
+      <c r="C143" s="33">
+        <v>0.75045</v>
       </c>
       <c r="D143">
-        <v>285</v>
+        <v>150</v>
       </c>
       <c r="E143">
-        <v>230</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>60</v>
-      </c>
-      <c r="B144" s="34">
-        <v>9.32416</v>
-      </c>
-      <c r="C144" s="34">
-        <v>2.10412</v>
+        <v>422</v>
+      </c>
+      <c r="B144" s="33">
+        <v>3.63758</v>
+      </c>
+      <c r="C144" s="33">
+        <v>0.88701</v>
       </c>
       <c r="D144">
-        <v>310</v>
+        <v>175</v>
       </c>
       <c r="E144">
-        <v>250</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>359</v>
-      </c>
-      <c r="B145" s="34">
-        <v>10.60671</v>
-      </c>
-      <c r="C145" s="34">
-        <v>2.45797</v>
+        <v>342</v>
+      </c>
+      <c r="B145" s="33">
+        <v>4.5658</v>
+      </c>
+      <c r="C145" s="33">
+        <v>1.09956</v>
       </c>
       <c r="D145">
-        <v>335</v>
+        <v>200</v>
       </c>
       <c r="E145">
-        <v>270</v>
+        <v>155</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>418</v>
-      </c>
-      <c r="B146" s="34">
-        <v>11.334</v>
-      </c>
-      <c r="C146" s="34">
-        <v>2.589</v>
+        <v>58</v>
+      </c>
+      <c r="B146" s="33">
+        <v>5.73045</v>
+      </c>
+      <c r="C146" s="33">
+        <v>1.2278</v>
       </c>
       <c r="D146">
-        <v>355</v>
+        <v>230</v>
       </c>
       <c r="E146">
-        <v>290</v>
+        <v>180</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>419</v>
-      </c>
-      <c r="B147" s="34">
-        <v>13.30059</v>
-      </c>
-      <c r="C147" s="34">
-        <v>2.7204</v>
+        <v>367</v>
+      </c>
+      <c r="B147" s="33">
+        <v>6.64016</v>
+      </c>
+      <c r="C147" s="33">
+        <v>1.49616</v>
       </c>
       <c r="D147">
-        <v>380</v>
+        <v>255</v>
       </c>
       <c r="E147">
-        <v>310</v>
+        <v>205</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>55</v>
-      </c>
-      <c r="B148" s="34">
-        <v>16.57382</v>
-      </c>
-      <c r="C148" s="34">
-        <v>3.44354</v>
+        <v>351</v>
+      </c>
+      <c r="B148" s="33">
+        <v>7.9632</v>
+      </c>
+      <c r="C148" s="33">
+        <v>2.06137</v>
       </c>
       <c r="D148">
-        <v>420</v>
+        <v>285</v>
       </c>
       <c r="E148">
-        <v>340</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>420</v>
-      </c>
-      <c r="B149" s="34">
-        <v>0</v>
-      </c>
-      <c r="C149" s="34">
-        <v>4.809</v>
+        <v>60</v>
+      </c>
+      <c r="B149" s="33">
+        <v>9.32416</v>
+      </c>
+      <c r="C149" s="33">
+        <v>2.10412</v>
       </c>
       <c r="D149">
-        <v>460</v>
+        <v>310</v>
       </c>
       <c r="E149">
-        <v>375</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>421</v>
-      </c>
-      <c r="B150" s="34">
-        <v>25.921</v>
-      </c>
-      <c r="C150" s="34">
-        <v>4.859</v>
+        <v>359</v>
+      </c>
+      <c r="B150" s="33">
+        <v>10.60671</v>
+      </c>
+      <c r="C150" s="33">
+        <v>2.45797</v>
       </c>
       <c r="D150">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="E150">
-        <v>385</v>
+        <v>270</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>422</v>
-      </c>
-      <c r="B151" s="34">
-        <v>0</v>
-      </c>
-      <c r="C151" s="34">
-        <v>0</v>
+        <v>423</v>
+      </c>
+      <c r="B151" s="33">
+        <v>11.334</v>
+      </c>
+      <c r="C151" s="33">
+        <v>2.589</v>
       </c>
       <c r="D151">
-        <v>490</v>
+        <v>355</v>
       </c>
       <c r="E151">
-        <v>395</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>423</v>
-      </c>
-      <c r="B152" s="34">
-        <v>0</v>
-      </c>
-      <c r="C152" s="34">
-        <v>7.566</v>
+        <v>424</v>
+      </c>
+      <c r="B152" s="33">
+        <v>13.30059</v>
+      </c>
+      <c r="C152" s="33">
+        <v>2.7204</v>
       </c>
       <c r="D152">
-        <v>520</v>
+        <v>380</v>
       </c>
       <c r="E152">
-        <v>425</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>424</v>
-      </c>
-      <c r="B153" s="34">
+        <v>55</v>
+      </c>
+      <c r="B153" s="33">
+        <v>16.57382</v>
+      </c>
+      <c r="C153" s="33">
+        <v>3.44354</v>
+      </c>
+      <c r="D153">
+        <v>420</v>
+      </c>
+      <c r="E153">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>425</v>
+      </c>
+      <c r="B154" s="33">
+        <v>0</v>
+      </c>
+      <c r="C154" s="33">
+        <v>4.809</v>
+      </c>
+      <c r="D154">
+        <v>460</v>
+      </c>
+      <c r="E154">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>426</v>
+      </c>
+      <c r="B155" s="33">
+        <v>25.921</v>
+      </c>
+      <c r="C155" s="33">
+        <v>4.859</v>
+      </c>
+      <c r="D155">
+        <v>475</v>
+      </c>
+      <c r="E155">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>427</v>
+      </c>
+      <c r="B156" s="33">
+        <v>0</v>
+      </c>
+      <c r="C156" s="33">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>490</v>
+      </c>
+      <c r="E156">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>428</v>
+      </c>
+      <c r="B157" s="33">
+        <v>0</v>
+      </c>
+      <c r="C157" s="33">
+        <v>7.566</v>
+      </c>
+      <c r="D157">
+        <v>520</v>
+      </c>
+      <c r="E157">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>429</v>
+      </c>
+      <c r="B158" s="33">
         <v>34.398</v>
       </c>
-      <c r="C153" s="34">
+      <c r="C158" s="33">
         <v>6.668</v>
       </c>
-      <c r="D153">
+      <c r="D158">
         <v>545</v>
       </c>
-      <c r="E153">
+      <c r="E158">
         <v>445</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
-        <v>425</v>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -6448,247 +6710,247 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>427</v>
+      <c r="A2" s="63" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>428</v>
+      <c r="A3" s="63" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
-        <v>429</v>
+      <c r="A4" s="63" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
-        <v>430</v>
+      <c r="A5" s="63" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
-        <v>431</v>
+      <c r="A6" s="63" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
-        <v>432</v>
+      <c r="A7" s="63" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
-        <v>433</v>
+      <c r="A8" s="63" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
-        <v>434</v>
+      <c r="A9" s="63" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
-        <v>435</v>
+      <c r="A10" s="63" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
-        <v>436</v>
+      <c r="A11" s="63" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
-        <v>437</v>
+      <c r="A12" s="63" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
-        <v>438</v>
+      <c r="A13" s="63" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
-        <v>439</v>
+      <c r="A14" s="63" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
-        <v>440</v>
+      <c r="A15" s="63" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="64" t="s">
-        <v>441</v>
+      <c r="A16" s="63" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
-        <v>442</v>
+      <c r="A17" s="63" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
-        <v>443</v>
+      <c r="A18" s="63" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
-        <v>444</v>
+      <c r="A19" s="63" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
-        <v>445</v>
+      <c r="A20" s="63" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="64" t="s">
-        <v>446</v>
+      <c r="A21" s="63" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
-        <v>447</v>
+      <c r="A22" s="63" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
-        <v>448</v>
+      <c r="A23" s="63" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>449</v>
+      <c r="A24" s="63" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
-        <v>450</v>
+      <c r="A25" s="63" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="64" t="s">
-        <v>451</v>
+      <c r="A26" s="63" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="64" t="s">
-        <v>452</v>
+      <c r="A27" s="63" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="64" t="s">
-        <v>453</v>
+      <c r="A28" s="63" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="64" t="s">
+      <c r="A29" s="63" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
-        <v>455</v>
+      <c r="A31" s="63" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="64" t="s">
-        <v>456</v>
+      <c r="A32" s="63" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="64" t="s">
-        <v>457</v>
+      <c r="A33" s="63" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="64" t="s">
+      <c r="A34" s="63" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="64" t="s">
-        <v>459</v>
+      <c r="A36" s="63" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="64" t="s">
-        <v>460</v>
+      <c r="A37" s="63" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="64" t="s">
+      <c r="A38" s="63" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="64" t="s">
-        <v>462</v>
+      <c r="A40" s="63" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="64" t="s">
-        <v>463</v>
+      <c r="A41" s="63" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="64" t="s">
-        <v>464</v>
+      <c r="A42" s="63" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="64" t="s">
-        <v>465</v>
+      <c r="A43" s="63" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="64" t="s">
-        <v>466</v>
+      <c r="A44" s="63" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="64" t="s">
-        <v>467</v>
+      <c r="A45" s="63" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="64" t="s">
-        <v>468</v>
+      <c r="A46" s="63" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="64" t="s">
-        <v>469</v>
+      <c r="A47" s="63" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="64" t="s">
-        <v>470</v>
+      <c r="A48" s="63" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="64" t="s">
-        <v>471</v>
+      <c r="A49" s="63" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -7845,10 +8107,10 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="D10:D28">
-      <formula1>RateCard!$A$129:$A$153</formula1>
+      <formula1>RateCard!$A$134:$A$158</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D5:D28">
-      <formula1>RateCard!$A$129:$A$153</formula1>
+      <formula1>RateCard!$A$134:$A$158</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E10:E28">
       <formula1>"Cu,Al"</formula1>
@@ -12484,7 +12746,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -12728,15 +12990,12 @@
         <f>IF(IncSLD="Yes",IF(NDcfc&gt;0,6000+900*NDcfc+150*NumL2,2500+150*NumL2),0)</f>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>196</v>
       </c>
       <c r="B37" s="9">
-        <f>C37*PmRate</f>
-      </c>
-      <c r="C37" s="32">
-        <f>IF(IncCpm="Yes",MAX(24,ROUND(CpmPct*Valuation/PmRate,0)),0)</f>
+        <f>IF(IncCpm="Yes",LaborCost*CpmPct,0)</f>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -12775,7 +13034,7 @@
       <c r="A43" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="32">
         <f>TotalCost-RebateAmt</f>
       </c>
     </row>
@@ -12845,7 +13104,7 @@
       <c r="B7">
         <f>NTotal</f>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <v>40</v>
       </c>
       <c r="D7" s="9">
@@ -12859,7 +13118,7 @@
       <c r="B8">
         <f>NumL2+ROUNDUP(NDcfc/2,0)</f>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>56.1</v>
       </c>
       <c r="D8" s="9">
@@ -12873,7 +13132,7 @@
       <c r="B9">
         <f>(NumL2*2+NDcfc)/10</f>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="33">
         <v>1500</v>
       </c>
       <c r="D9" s="9">
@@ -12942,7 +13201,7 @@
       <c r="B16">
         <f>IF(InstallMethod="Surface EMT",0,NDcfc*3+IF(InstallMethod="Trenched",NumL2*2,0)+IF(AND(NDcfc&gt;0,NumL2&gt;0),3,IF(NTotal&gt;0,1,0))*2)</f>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>25.65</v>
       </c>
       <c r="D16" s="9">
@@ -12984,7 +13243,7 @@
       <c r="B19">
         <f>NTotal</f>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <v>70.58</v>
       </c>
       <c r="D19" s="9">
@@ -12998,7 +13257,7 @@
       <c r="B20">
         <f>IF(TrenchFt&gt;0,MAX(1,ROUNDUP(TrenchFt/200,0)),0)</f>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="33">
         <v>160</v>
       </c>
       <c r="D20" s="9">
@@ -13012,7 +13271,7 @@
       <c r="B21">
         <f>IF(NDcfc&gt;0,IF(SgSuggested&gt;1000,1,0),0)</f>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>2000</v>
       </c>
       <c r="D21" s="9">
@@ -13026,7 +13285,7 @@
       <c r="B22" s="8">
         <v>0</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>55</v>
       </c>
       <c r="D22" s="9">
@@ -13040,7 +13299,7 @@
       <c r="B23" s="8">
         <v>0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <v>10</v>
       </c>
       <c r="D23" s="9">
@@ -13054,7 +13313,7 @@
       <c r="B24" s="8">
         <v>0</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <v>19</v>
       </c>
       <c r="D24" s="9">
@@ -13135,353 +13394,353 @@
   </cols>
   <sheetData>
     <row r="2" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="38" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="C3" s="41">
+      <c r="C3" s="40">
         <v>1</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="41">
         <f>Estimate!B7+Estimate!B10+Estimate!B15</f>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="41">
         <f>(D3*E3)+D3</f>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="43">
         <f>F3*C3</f>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>233</v>
       </c>
-      <c r="K3" s="46"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="41">
+      <c r="C4" s="40">
         <v>1</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="41">
         <f>Panel!F22</f>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="41">
         <f>(D4*E4)+D4</f>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="43">
         <f>F4*C4</f>
       </c>
-      <c r="J4" s="47" t="s">
+      <c r="J4" s="46" t="s">
         <v>235</v>
       </c>
-      <c r="K4" s="48">
+      <c r="K4" s="47">
         <f>IF(LaborDays&gt;0,LaborBase/LaborDays,0)</f>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="40">
         <v>1</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="41">
         <f>Panel!F42+Panel!F48+Panel!F66</f>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="41">
         <f>(D5*E5)+D5</f>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="43">
         <f>F5*C5</f>
       </c>
-      <c r="J5" s="47" t="s">
+      <c r="J5" s="46" t="s">
         <v>237</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="48">
         <f>LaborDays</f>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="40">
         <v>1</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="41">
         <f>Estimate!B12</f>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="41">
         <f>(D6*E6)+D6</f>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="43">
         <f>F6*C6</f>
       </c>
-      <c r="J6" s="47" t="s">
+      <c r="J6" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="48">
         <f>K5/30</f>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="40">
         <v>1</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="41">
         <f>Estimate!B9</f>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="41">
         <f>(D7*E7)+D7</f>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="43">
         <f>F7*C7</f>
       </c>
-      <c r="J7" s="50" t="s">
+      <c r="J7" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="K7" s="51">
+      <c r="K7" s="50">
         <f>K5*K4</f>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="40">
         <v>1</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="41">
         <f>Estimate!B11</f>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="41">
         <f>(D8*E8)+D8</f>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="43">
         <f>F8*C8</f>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="39" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="40">
         <v>1</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="41">
         <f>Estimate!B13</f>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <f>(D9*E9)+D9</f>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="43">
         <f>F9*C9</f>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="40">
         <v>1</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="41">
         <f>Estimate!B14</f>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="41">
         <f>(D10*E10)+D10</f>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="43">
         <f>F10*C10</f>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="40">
         <v>1</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="41">
         <f>Estimate!B17</f>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="41">
         <f>(D11*E11)+D11</f>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="43">
         <f>F11*C11</f>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="40">
         <v>1</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="41">
         <f>Estimate!B18</f>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="41">
         <f>(D12*E12)+D12</f>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="43">
         <f>F12*C12</f>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>1</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="41">
         <f>Estimate!B16</f>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="41">
         <f>(D13*E13)+D13</f>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="43">
         <f>F13*C13</f>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="40">
         <v>1</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="41">
         <f>Estimate!B35+Estimate!B36+Estimate!B37</f>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="42">
         <v>0</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="41">
         <f>(D14*E14)+D14</f>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="43">
         <f>F14*C14</f>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="56">
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="55">
         <f>SUM(G3:G13)</f>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="40">
         <f>K5</f>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="41">
         <f>K4</f>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="42">
         <f>ContingencyPct</f>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="41">
         <f>(D18*E18)+D18</f>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <f>F18*C18</f>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="52"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="56">
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="55">
         <f>SUM(G18)</f>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="50"/>
-      <c r="C20" s="58" t="s">
+      <c r="B20" s="49"/>
+      <c r="C20" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="59">
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="58">
         <f>G15+G19</f>
       </c>
     </row>
@@ -13645,130 +13904,130 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="59" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="59" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="60" t="s">
+      <c r="D14" s="59" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="61" t="s">
+      <c r="D15" s="60" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="60" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="60" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="60" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="60" t="s">
         <v>271</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="D18" s="60" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="D19" s="60" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="60" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="61" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="61" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="61" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="61" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="61" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="61" t="s">
         <v>283</v>
       </c>
     </row>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -19,19 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="ModelTable">RateCard!$A$4:$P$38</definedName>
-    <definedName name="SgSizes">RateCard!$A$43:$A$52</definedName>
-    <definedName name="SgTable">RateCard!$A$43:$B$52</definedName>
-    <definedName name="PnlSizes">RateCard!$A$56:$A$61</definedName>
-    <definedName name="PnlTable">RateCard!$A$56:$B$61</definedName>
-    <definedName name="TxSizes">RateCard!$A$65:$A$71</definedName>
-    <definedName name="TxTable">RateCard!$A$65:$B$71</definedName>
-    <definedName name="Brk480Sizes">RateCard!$A$75:$A$86</definedName>
-    <definedName name="BrkTbl480">RateCard!$A$75:$B$86</definedName>
-    <definedName name="Brk208Sizes">RateCard!$A$90:$A$92</definedName>
-    <definedName name="BrkTbl208">RateCard!$A$90:$B$92</definedName>
-    <definedName name="StdBrk">RateCard!$A$95:$A$130</definedName>
-    <definedName name="WireSizes">RateCard!$A$134:$A$158</definedName>
-    <definedName name="WireTable">RateCard!$A$134:$E$158</definedName>
+    <definedName name="SgSizes">RateCard!$A$43:$A$54</definedName>
+    <definedName name="SgTable">RateCard!$A$43:$B$54</definedName>
+    <definedName name="PnlSizes">RateCard!$A$58:$A$63</definedName>
+    <definedName name="PnlTable">RateCard!$A$58:$B$63</definedName>
+    <definedName name="TxSizes">RateCard!$A$67:$A$73</definedName>
+    <definedName name="TxTable">RateCard!$A$67:$B$73</definedName>
+    <definedName name="Brk480Sizes">RateCard!$A$77:$A$88</definedName>
+    <definedName name="BrkTbl480">RateCard!$A$77:$B$88</definedName>
+    <definedName name="Brk208Sizes">RateCard!$A$92:$A$94</definedName>
+    <definedName name="BrkTbl208">RateCard!$A$92:$B$94</definedName>
+    <definedName name="StdBrk">RateCard!$A$97:$A$133</definedName>
+    <definedName name="WireSizes">RateCard!$A$137:$A$161</definedName>
+    <definedName name="WireTable">RateCard!$A$137:$E$161</definedName>
     <definedName name="TerrainTable">RateCard!$Q$4:$U$7</definedName>
     <definedName name="TrenchRate">RateCard!$R$10</definedName>
     <definedName name="ContingencyPct">RateCard!$R$11</definedName>
@@ -3359,7 +3359,7 @@
       <formula1>"Trenched,Surface EMT,Hybrid"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B53:B67">
-      <formula1>RateCard!$A$134:$A$158</formula1>
+      <formula1>RateCard!$A$137:$A$161</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="B78:B83">
       <formula1>"Yes,No"</formula1>
@@ -3530,7 +3530,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U159"/>
+  <dimension ref="A1:U162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -4099,7 +4099,7 @@
         <v>23600</v>
       </c>
       <c r="C12" s="33">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D12" t="s">
         <v>332</v>
@@ -4138,7 +4138,7 @@
         <v>317</v>
       </c>
       <c r="P12" s="33">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="Q12" t="s">
         <v>334</v>
@@ -4155,7 +4155,7 @@
         <v>23600</v>
       </c>
       <c r="C13" s="33">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" t="s">
         <v>332</v>
@@ -4194,7 +4194,7 @@
         <v>317</v>
       </c>
       <c r="P13" s="33">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="Q13" t="s">
         <v>336</v>
@@ -4211,7 +4211,7 @@
         <v>28500</v>
       </c>
       <c r="C14" s="33">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D14" t="s">
         <v>332</v>
@@ -4250,7 +4250,7 @@
         <v>317</v>
       </c>
       <c r="P14" s="33">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="Q14" t="s">
         <v>338</v>
@@ -4267,7 +4267,7 @@
         <v>28500</v>
       </c>
       <c r="C15" s="33">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D15" t="s">
         <v>332</v>
@@ -4306,7 +4306,7 @@
         <v>317</v>
       </c>
       <c r="P15" s="33">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="Q15" t="s">
         <v>340</v>
@@ -5663,10 +5663,10 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="B44" s="33">
-        <v>31187</v>
+        <v>25500</v>
       </c>
       <c r="Q44" t="s">
         <v>399</v>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="B45" s="33">
-        <v>36812.5</v>
+        <v>31187</v>
       </c>
       <c r="Q45" t="s">
         <v>400</v>
@@ -5691,10 +5691,10 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="B46" s="33">
-        <v>43292.68</v>
+        <v>36812.5</v>
       </c>
       <c r="Q46" t="s">
         <v>401</v>
@@ -5705,10 +5705,10 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="B47" s="33">
-        <v>56750</v>
+        <v>43292.68</v>
       </c>
       <c r="Q47" t="s">
         <v>402</v>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="B48" s="33">
-        <v>55000</v>
+        <v>56750</v>
       </c>
       <c r="Q48" t="s">
         <v>403</v>
@@ -5733,10 +5733,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="B49" s="33">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="Q49" t="s">
         <v>404</v>
@@ -5747,10 +5747,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="B50" s="33">
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="Q50" t="s">
         <v>405</v>
@@ -5761,10 +5761,10 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="B51" s="33">
-        <v>67500</v>
+        <v>58842</v>
       </c>
       <c r="Q51" t="s">
         <v>406</v>
@@ -5775,922 +5775,943 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
+        <v>3200</v>
+      </c>
+      <c r="B52" s="33">
+        <v>62200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4000</v>
+      </c>
+      <c r="B53" s="33">
+        <v>75600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>5000</v>
       </c>
-      <c r="B52" s="33">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="B54" s="33">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>150</v>
-      </c>
-      <c r="B56" s="33">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>250</v>
-      </c>
-      <c r="B57" s="33">
-        <v>1120</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="B58" s="33">
-        <v>1660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="B59" s="33">
-        <v>5387</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="B60" s="33">
-        <v>4650</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
+        <v>600</v>
+      </c>
+      <c r="B61" s="33">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>800</v>
+      </c>
+      <c r="B62" s="33">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>1000</v>
       </c>
-      <c r="B61" s="33">
+      <c r="B63" s="33">
         <v>30000</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B66" s="7" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>75</v>
-      </c>
-      <c r="B65" s="33">
-        <v>2970</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>112.5</v>
-      </c>
-      <c r="B66" s="33">
-        <v>3250</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="B67" s="33">
-        <v>5298</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>175</v>
+        <v>112.5</v>
       </c>
       <c r="B68" s="33">
-        <v>6000</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="B69" s="33">
-        <v>7144</v>
+        <v>5298</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="B70" s="33">
-        <v>10493</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
+        <v>225</v>
+      </c>
+      <c r="B71" s="33">
+        <v>7144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>300</v>
+      </c>
+      <c r="B72" s="33">
+        <v>10493</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>500</v>
       </c>
-      <c r="B71" s="33">
+      <c r="B73" s="33">
         <v>14500</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B76" s="7" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>100</v>
-      </c>
-      <c r="B75" s="33">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>125</v>
-      </c>
-      <c r="B76" s="33">
-        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B77" s="33">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="B78" s="33">
-        <v>550</v>
+        <v>420</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B79" s="33">
-        <v>650</v>
+        <v>480</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="B80" s="33">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="B81" s="33">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B82" s="33">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="B83" s="33">
-        <v>1000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B84" s="33">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="B85" s="33">
-        <v>1800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
+        <v>400</v>
+      </c>
+      <c r="B86" s="33">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>500</v>
+      </c>
+      <c r="B87" s="33">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88">
         <v>600</v>
       </c>
-      <c r="B86" s="33">
+      <c r="B88" s="33">
         <v>2200</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B91" s="7" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>40</v>
-      </c>
-      <c r="B90" s="33">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>50</v>
-      </c>
-      <c r="B91" s="33">
-        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
+        <v>40</v>
+      </c>
+      <c r="B92" s="33">
         <v>60</v>
       </c>
-      <c r="B92" s="33">
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>50</v>
+      </c>
+      <c r="B93" s="33">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>60</v>
+      </c>
+      <c r="B94" s="33">
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>411</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>150</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>225</v>
+        <v>175</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>300</v>
+        <v>225</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>350</v>
+        <v>250</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>1600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>2500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>4000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
         <v>5000</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B136" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C136" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="D136" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="E136" s="7" t="s">
         <v>416</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>417</v>
-      </c>
-      <c r="B134" s="33">
-        <v>0</v>
-      </c>
-      <c r="C134" s="33">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>20</v>
-      </c>
-      <c r="E134">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>418</v>
-      </c>
-      <c r="B135" s="33">
-        <v>0</v>
-      </c>
-      <c r="C135" s="33">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>25</v>
-      </c>
-      <c r="E135">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>419</v>
-      </c>
-      <c r="B136" s="33">
-        <v>0.30329</v>
-      </c>
-      <c r="C136" s="33">
-        <v>0.28</v>
-      </c>
-      <c r="D136">
-        <v>35</v>
-      </c>
-      <c r="E136">
-        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="B137" s="33">
-        <v>0.56613</v>
+        <v>0</v>
       </c>
       <c r="C137" s="33">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E137">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>316</v>
+        <v>418</v>
       </c>
       <c r="B138" s="33">
-        <v>0.87104</v>
+        <v>0</v>
       </c>
       <c r="C138" s="33">
-        <v>0.30636</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E138">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B139" s="33">
-        <v>1.33293</v>
+        <v>0.30329</v>
       </c>
       <c r="C139" s="33">
-        <v>0.37998</v>
+        <v>0.28</v>
       </c>
       <c r="D139">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="E139">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>322</v>
+        <v>380</v>
       </c>
       <c r="B140" s="33">
-        <v>1.68126</v>
+        <v>0.56613</v>
       </c>
       <c r="C140" s="33">
-        <v>0.36681</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E140">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>421</v>
+        <v>316</v>
       </c>
       <c r="B141" s="33">
-        <v>2.1044</v>
+        <v>0.87104</v>
       </c>
       <c r="C141" s="33">
-        <v>0.4821</v>
+        <v>0.30636</v>
       </c>
       <c r="D141">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="E141">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>325</v>
+        <v>420</v>
       </c>
       <c r="B142" s="33">
-        <v>2.39833</v>
+        <v>1.33293</v>
       </c>
       <c r="C142" s="33">
-        <v>0.66733</v>
+        <v>0.37998</v>
       </c>
       <c r="D142">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="E142">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B143" s="33">
-        <v>2.95304</v>
+        <v>1.68126</v>
       </c>
       <c r="C143" s="33">
-        <v>0.75045</v>
+        <v>0.36681</v>
       </c>
       <c r="D143">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E143">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B144" s="33">
-        <v>3.63758</v>
+        <v>2.1044</v>
       </c>
       <c r="C144" s="33">
-        <v>0.88701</v>
+        <v>0.4821</v>
       </c>
       <c r="D144">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="E144">
-        <v>135</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B145" s="33">
-        <v>4.5658</v>
+        <v>2.39833</v>
       </c>
       <c r="C145" s="33">
-        <v>1.09956</v>
+        <v>0.66733</v>
       </c>
       <c r="D145">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="E145">
-        <v>155</v>
+        <v>100</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>58</v>
+        <v>333</v>
       </c>
       <c r="B146" s="33">
-        <v>5.73045</v>
+        <v>2.95304</v>
       </c>
       <c r="C146" s="33">
-        <v>1.2278</v>
+        <v>0.75045</v>
       </c>
       <c r="D146">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="E146">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>367</v>
+        <v>422</v>
       </c>
       <c r="B147" s="33">
-        <v>6.64016</v>
+        <v>3.63758</v>
       </c>
       <c r="C147" s="33">
-        <v>1.49616</v>
+        <v>0.88701</v>
       </c>
       <c r="D147">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="E147">
-        <v>205</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B148" s="33">
-        <v>7.9632</v>
+        <v>4.5658</v>
       </c>
       <c r="C148" s="33">
-        <v>2.06137</v>
+        <v>1.09956</v>
       </c>
       <c r="D148">
-        <v>285</v>
+        <v>200</v>
       </c>
       <c r="E148">
-        <v>230</v>
+        <v>155</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B149" s="33">
-        <v>9.32416</v>
+        <v>5.73045</v>
       </c>
       <c r="C149" s="33">
-        <v>2.10412</v>
+        <v>1.2278</v>
       </c>
       <c r="D149">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="E149">
-        <v>250</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B150" s="33">
-        <v>10.60671</v>
+        <v>6.64016</v>
       </c>
       <c r="C150" s="33">
-        <v>2.45797</v>
+        <v>1.49616</v>
       </c>
       <c r="D150">
-        <v>335</v>
+        <v>255</v>
       </c>
       <c r="E150">
-        <v>270</v>
+        <v>205</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>423</v>
+        <v>351</v>
       </c>
       <c r="B151" s="33">
-        <v>11.334</v>
+        <v>7.9632</v>
       </c>
       <c r="C151" s="33">
-        <v>2.589</v>
+        <v>2.06137</v>
       </c>
       <c r="D151">
-        <v>355</v>
+        <v>285</v>
       </c>
       <c r="E151">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>424</v>
+        <v>60</v>
       </c>
       <c r="B152" s="33">
-        <v>13.30059</v>
+        <v>9.32416</v>
       </c>
       <c r="C152" s="33">
-        <v>2.7204</v>
+        <v>2.10412</v>
       </c>
       <c r="D152">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="E152">
-        <v>310</v>
+        <v>250</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>55</v>
+        <v>359</v>
       </c>
       <c r="B153" s="33">
-        <v>16.57382</v>
+        <v>10.60671</v>
       </c>
       <c r="C153" s="33">
-        <v>3.44354</v>
+        <v>2.45797</v>
       </c>
       <c r="D153">
-        <v>420</v>
+        <v>335</v>
       </c>
       <c r="E153">
-        <v>340</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B154" s="33">
-        <v>0</v>
+        <v>11.334</v>
       </c>
       <c r="C154" s="33">
-        <v>4.809</v>
+        <v>2.589</v>
       </c>
       <c r="D154">
-        <v>460</v>
+        <v>355</v>
       </c>
       <c r="E154">
-        <v>375</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B155" s="33">
-        <v>25.921</v>
+        <v>13.30059</v>
       </c>
       <c r="C155" s="33">
-        <v>4.859</v>
+        <v>2.7204</v>
       </c>
       <c r="D155">
-        <v>475</v>
+        <v>380</v>
       </c>
       <c r="E155">
-        <v>385</v>
+        <v>310</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>427</v>
+        <v>55</v>
       </c>
       <c r="B156" s="33">
-        <v>0</v>
+        <v>16.57382</v>
       </c>
       <c r="C156" s="33">
-        <v>0</v>
+        <v>3.44354</v>
       </c>
       <c r="D156">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="E156">
-        <v>395</v>
+        <v>340</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B157" s="33">
         <v>0</v>
       </c>
       <c r="C157" s="33">
-        <v>7.566</v>
+        <v>4.809</v>
       </c>
       <c r="D157">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="E157">
-        <v>425</v>
+        <v>375</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>426</v>
+      </c>
+      <c r="B158" s="33">
+        <v>25.921</v>
+      </c>
+      <c r="C158" s="33">
+        <v>4.859</v>
+      </c>
+      <c r="D158">
+        <v>475</v>
+      </c>
+      <c r="E158">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>427</v>
+      </c>
+      <c r="B159" s="33">
+        <v>0</v>
+      </c>
+      <c r="C159" s="33">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>490</v>
+      </c>
+      <c r="E159">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>428</v>
+      </c>
+      <c r="B160" s="33">
+        <v>0</v>
+      </c>
+      <c r="C160" s="33">
+        <v>7.566</v>
+      </c>
+      <c r="D160">
+        <v>520</v>
+      </c>
+      <c r="E160">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>429</v>
       </c>
-      <c r="B158" s="33">
+      <c r="B161" s="33">
         <v>34.398</v>
       </c>
-      <c r="C158" s="33">
+      <c r="C161" s="33">
         <v>6.668</v>
       </c>
-      <c r="D158">
+      <c r="D161">
         <v>545</v>
       </c>
-      <c r="E158">
+      <c r="E161">
         <v>445</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
         <v>430</v>
       </c>
     </row>
@@ -8107,10 +8128,10 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="D10:D28">
-      <formula1>RateCard!$A$134:$A$158</formula1>
+      <formula1>RateCard!$A$137:$A$161</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D5:D28">
-      <formula1>RateCard!$A$134:$A$158</formula1>
+      <formula1>RateCard!$A$137:$A$161</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E10:E28">
       <formula1>"Cu,Al"</formula1>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -75,6 +75,7 @@
     <definedName name="PermitPerChg">RateCard!$R$49</definedName>
     <definedName name="UtilAppDcfc">RateCard!$R$50</definedName>
     <definedName name="UtilAppL2">RateCard!$R$51</definedName>
+    <definedName name="ServiceBoxCost">RateCard!$R$52</definedName>
     <definedName name="NTotal">Intake!$B$36</definedName>
     <definedName name="NDcfc">Intake!$B$37</definedName>
     <definedName name="NumL2">Intake!$B$38</definedName>
@@ -123,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="478">
   <si>
     <t>RFC INTAKE — EV Charging Project</t>
   </si>
@@ -638,7 +639,7 @@
     <t>Electrical supply &amp; construction</t>
   </si>
   <si>
-    <t>Wire runs (Takeoff + feeders) + conduit &amp; install allowance + data box</t>
+    <t>Wire runs (Takeoff + feeders) + conduit &amp; install allowance + data box + Christy box</t>
   </si>
   <si>
     <t>Switchgear, panels &amp; transformer (Panel sheet)</t>
@@ -1344,6 +1345,9 @@
   </si>
   <si>
     <t>Utility application $ (L2-only site)</t>
+  </si>
+  <si>
+    <t>Christy box at the point of connection $ (one per site, traffic lid)</t>
   </si>
   <si>
     <t>Sub-panel / distribution 208V</t>
@@ -5773,12 +5777,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3200</v>
       </c>
       <c r="B52" s="33">
         <v>62200</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>407</v>
+      </c>
+      <c r="R52" s="33">
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -5799,7 +5809,7 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -5860,7 +5870,7 @@
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -5929,7 +5939,7 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -6038,7 +6048,7 @@
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -6075,7 +6085,7 @@
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
@@ -6265,7 +6275,7 @@
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -6273,21 +6283,21 @@
         <v>395</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B137" s="33">
         <v>0</v>
@@ -6304,7 +6314,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B138" s="33">
         <v>0</v>
@@ -6321,7 +6331,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B139" s="33">
         <v>0.30329</v>
@@ -6372,7 +6382,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B142" s="33">
         <v>1.33293</v>
@@ -6406,7 +6416,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B144" s="33">
         <v>2.1044</v>
@@ -6457,7 +6467,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B147" s="33">
         <v>3.63758</v>
@@ -6576,7 +6586,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B154" s="33">
         <v>11.334</v>
@@ -6593,7 +6603,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B155" s="33">
         <v>13.30059</v>
@@ -6627,7 +6637,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B157" s="33">
         <v>0</v>
@@ -6644,7 +6654,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B158" s="33">
         <v>25.921</v>
@@ -6661,7 +6671,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B159" s="33">
         <v>0</v>
@@ -6678,7 +6688,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B160" s="33">
         <v>0</v>
@@ -6695,7 +6705,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B161" s="33">
         <v>34.398</v>
@@ -6712,7 +6722,7 @@
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -6731,142 +6741,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="63" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="63" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="63" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="63" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="63" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="63" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="63" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="63" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="63" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="63" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="63" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="63" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="63" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="63" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="63" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="63" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="63" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="63" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="63" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="63" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -6876,22 +6886,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="63" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="63" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="63" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -6901,17 +6911,17 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="63" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="63" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
@@ -6921,57 +6931,57 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="63" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="63" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="63" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="63" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="63" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="63" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="63" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="63" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="63" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="63" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -12804,7 +12814,7 @@
         <v>171</v>
       </c>
       <c r="B7" s="9">
-        <f>WireTotal+SUM(Intake!E23:E34)+IF(NTotal&gt;0,DataBoxCost,0)</f>
+        <f>WireTotal+SUM(Intake!E23:E34)+IF(NTotal&gt;0,DataBoxCost+ServiceBoxCost,0)</f>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -453,7 +453,7 @@
     <t>PANEL SCHEDULE 2 — 208V PANEL (LEVEL 2)</t>
   </si>
   <si>
-    <t>208V bus connected amps</t>
+    <t>208V bus connected amps (line)</t>
   </si>
   <si>
     <t>208V bus demand amps (×125%)</t>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E24" s="9" t="n">
         <f>IFERROR($B24*VLOOKUP($A24,ModelTable,IF(InstallMethod="Trenched",3,16),FALSE),0)</f>
-        <v>1460</v>
+        <v>1435</v>
       </c>
       <c r="F24" s="9" t="n">
         <f>IFERROR($B24*VLOOKUP($A24,ModelTable,2,FALSE),0)</f>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B93" t="str">
         <f>IF(NDcfc&gt;0,SgSuggested&amp;"A switchgear @ 480V","208V service")&amp;IF(TxKvaSuggested&gt;0," + "&amp;TxKvaSuggested&amp;" kVA step-down TX","")</f>
-        <v>2500A switchgear @ 480V + 112.5 kVA step-down TX</v>
+        <v>2500A switchgear @ 480V + 75 kVA step-down TX</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B94" s="14" t="n">
         <f>TotalCost</f>
-        <v>879075.2144818875</v>
+        <v>878408.2432318876</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B95" s="11" t="n">
         <f>CustomerTotal</f>
-        <v>879075.2144818875</v>
+        <v>878408.2432318876</v>
       </c>
     </row>
   </sheetData>
@@ -3833,7 +3833,7 @@
         <v>1402.5</v>
       </c>
       <c r="C4" s="33">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D4" t="s">
         <v>315</v>
@@ -3872,7 +3872,7 @@
         <v>317</v>
       </c>
       <c r="P4" s="33">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -3898,7 +3898,7 @@
         <v>1402.5</v>
       </c>
       <c r="C5" s="33">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
         <v>315</v>
@@ -3937,7 +3937,7 @@
         <v>317</v>
       </c>
       <c r="P5" s="33">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="Q5" t="s">
         <v>319</v>
@@ -3963,7 +3963,7 @@
         <v>1402.5</v>
       </c>
       <c r="C6" s="33">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D6" t="s">
         <v>315</v>
@@ -4002,7 +4002,7 @@
         <v>317</v>
       </c>
       <c r="P6" s="33">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="Q6" t="s">
         <v>320</v>
@@ -4028,7 +4028,7 @@
         <v>1650</v>
       </c>
       <c r="C7" s="33">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="D7" t="s">
         <v>315</v>
@@ -4067,7 +4067,7 @@
         <v>317</v>
       </c>
       <c r="P7" s="33">
-        <v>688</v>
+        <v>657</v>
       </c>
       <c r="Q7" t="s">
         <v>323</v>
@@ -4093,7 +4093,7 @@
         <v>1952.5</v>
       </c>
       <c r="C8" s="33">
-        <v>693</v>
+        <v>657</v>
       </c>
       <c r="D8" t="s">
         <v>315</v>
@@ -4132,7 +4132,7 @@
         <v>317</v>
       </c>
       <c r="P8" s="33">
-        <v>1324</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4143,7 +4143,7 @@
         <v>1952.5</v>
       </c>
       <c r="C9" s="33">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="D9" t="s">
         <v>315</v>
@@ -4182,7 +4182,7 @@
         <v>317</v>
       </c>
       <c r="P9" s="33">
-        <v>842</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -4193,7 +4193,7 @@
         <v>1952.5</v>
       </c>
       <c r="C10" s="33">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="D10" t="s">
         <v>315</v>
@@ -4232,7 +4232,7 @@
         <v>317</v>
       </c>
       <c r="P10" s="33">
-        <v>885</v>
+        <v>854</v>
       </c>
       <c r="Q10" t="s">
         <v>328</v>
@@ -4249,7 +4249,7 @@
         <v>2194.5</v>
       </c>
       <c r="C11" s="33">
-        <v>612</v>
+        <v>579</v>
       </c>
       <c r="D11" t="s">
         <v>315</v>
@@ -4288,7 +4288,7 @@
         <v>317</v>
       </c>
       <c r="P11" s="33">
-        <v>1150</v>
+        <v>1099</v>
       </c>
       <c r="Q11" t="s">
         <v>330</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="33">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="D35" t="s">
         <v>315</v>
@@ -5632,7 +5632,7 @@
         <v>317</v>
       </c>
       <c r="P35" s="33">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="Q35" t="s">
         <v>383</v>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="F18" t="n">
         <f>IF(AND(NDcfc&gt;0,NumL2&gt;0),TxKvaConnected*1000/(480*SQRT(3)),0)</f>
-        <v>86.66666666666667</v>
+        <v>50.03702332976758</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="F19" t="n">
         <f>F17+F18</f>
-        <v>1676.6666666666667</v>
+        <v>1640.0370233297676</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="F20" t="n">
         <f>F19*1.25</f>
-        <v>2095.8333333333335</v>
+        <v>2050.0462791622094</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -9423,8 +9423,8 @@
         <v>109</v>
       </c>
       <c r="F38" t="n">
-        <f>SUM(F26:F37)</f>
-        <v>200</v>
+        <f>SUM(F26:F37)/SQRT(3)</f>
+        <v>115.47005383792516</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="F39" t="n">
         <f>F38*1.25</f>
-        <v>250</v>
+        <v>144.33756729740645</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="F40" t="n">
         <f>IF(NumL2&gt;0,IF(ISNUMBER($D$40),$D$40,INDEX(PnlSizes,MIN(ROWS(PnlSizes),COUNTIF(PnlSizes,"&lt;"&amp;F39)+1))),0)</f>
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="F42" s="9" t="n">
         <f>IF(NumL2&gt;0,IFERROR(VLOOKUP(F40,PnlTable,2,FALSE),0),0)</f>
-        <v>1120</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="F45" t="n">
         <f>IF(AND(NDcfc&gt;0,NumL2&gt;0),F38*208*SQRT(3)/1000,0)</f>
-        <v>72.05331359486529</v>
+        <v>41.60000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="F46" t="n">
         <f>F45*1.25</f>
-        <v>90.06664199358161</v>
+        <v>52.000000000000014</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="F47" t="n">
         <f>IF(F45&gt;0,IF(ISNUMBER($D$47),$D$47,INDEX(TxSizes,MIN(ROWS(TxSizes),COUNTIF(TxSizes,"&lt;"&amp;F46)+1))),0)</f>
-        <v>112.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F48" s="9" t="n">
         <f>IF(F47&gt;0,IFERROR(VLOOKUP(F47,TxTable,2,FALSE),0),0)</f>
-        <v>3250</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="F49" t="n">
         <f>IF(F47&gt;0,F47*1000/(480*SQRT(3)),0)</f>
-        <v>135.31646934131857</v>
+        <v>90.21097956087904</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="F50" t="n">
         <f>IF(F47&gt;0,INDEX(StdBrk,MIN(ROWS(StdBrk),COUNTIF(StdBrk,"&lt;"&amp;F49*1.25)+1)),0)</f>
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="F51" s="9" t="n">
         <f>IF(F50&gt;0,IFERROR(VLOOKUP(F50,BrkTbl480,2,FALSE),0),0)</f>
-        <v>550</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="F66" s="9" t="n">
         <f>SUM(F54:F65)+F51</f>
-        <v>6925</v>
+        <v>6795</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="F68" s="20" t="n">
         <f>F22+F42+F48+F66</f>
-        <v>71295</v>
+        <v>70765</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C17" s="25" t="str">
         <f>IF($AA$23=1,$X$23,"")</f>
-        <v>XFMR 112.5 KVA - EV_SUB (208V)</v>
+        <v>XFMR 75 KVA - EV_SUB (208V)</v>
       </c>
       <c r="D17" s="25" t="n">
         <f>IF($AA$23=1,$Y$23,"")</f>
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="E17" s="25" t="n">
         <f>IF($AA$23=1,3,"")</f>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="F17" s="25" t="n">
         <f>IF($AA$23=1,ROUND($Z$23,0),"")</f>
-        <v>24018</v>
+        <v>13867</v>
       </c>
       <c r="G17" s="25" t="str">
         <f>IF($AA$24=1,ROUND($Z$24,0),"")</f>
@@ -10661,7 +10661,7 @@
       <c r="G18" s="25"/>
       <c r="H18" s="25" t="n">
         <f>IF($AA$23=1,ROUND($Z$23,0),"")</f>
-        <v>24018</v>
+        <v>13867</v>
       </c>
       <c r="I18" s="25" t="str">
         <f>IF($AA$24=1,ROUND($Z$24,0),"")</f>
@@ -10736,7 +10736,7 @@
       <c r="I19" s="25"/>
       <c r="J19" s="25" t="n">
         <f>IF($AA$23=1,ROUND($Z$23,0),"")</f>
-        <v>24018</v>
+        <v>13867</v>
       </c>
       <c r="K19" s="25" t="str">
         <f>IF($AA$24=1,ROUND($Z$24,0),"")</f>
@@ -11091,15 +11091,15 @@
       </c>
       <c r="X23" t="str">
         <f>IF(T23&gt;0,UPPER(V23)&amp;" #"&amp;U23,IF(S23=$S$15+1,IF(TxKvaSuggested&gt;0,"XFMR "&amp;TxKvaSuggested&amp;" KVA - EV_SUB (208V)",""),""))</f>
-        <v>XFMR 112.5 KVA - EV_SUB (208V)</v>
+        <v>XFMR 75 KVA - EV_SUB (208V)</v>
       </c>
       <c r="Y23" t="n">
         <f>IF(T23&gt;0,IFERROR(INDEX(Intake!$J$53:$J$64,T23),0),IF(S23=$S$15+1,IF(TxKvaSuggested&gt;0,Panel!$F$50,0),0))</f>
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="Z23" t="n">
         <f>IF(T23&gt;0,IFERROR(VLOOKUP(V23,ModelTable,11,FALSE),0)*480/SQRT(3),IF(S23=$S$15+1,IF(TxKvaSuggested&gt;0,TxKvaConnected*1000/3,0),0))</f>
-        <v>24017.771198288432</v>
+        <v>13866.66666666667</v>
       </c>
       <c r="AA23" t="n">
         <f>IF(S23&lt;=$S$15,1,IF(S23=$S$15+1,IF(TxKvaSuggested&gt;0,1,0),0))</f>
@@ -11757,17 +11757,17 @@
       </c>
       <c r="F33" s="27" t="n">
         <f>SUM(F8:G31)</f>
-        <v>464652</v>
+        <v>454501</v>
       </c>
       <c r="G33" s="27"/>
       <c r="H33" s="27" t="n">
         <f>SUM(H8:I31)</f>
-        <v>464652</v>
+        <v>454501</v>
       </c>
       <c r="I33" s="27"/>
       <c r="J33" s="27" t="n">
         <f>SUM(J8:K31)</f>
-        <v>464652</v>
+        <v>454501</v>
       </c>
       <c r="K33" s="27"/>
       <c r="L33" s="23" t="s">
@@ -11776,7 +11776,7 @@
       <c r="M33" s="23"/>
       <c r="N33" s="27" t="n">
         <f>F33+H33+J33</f>
-        <v>1393956</v>
+        <v>1363503</v>
       </c>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
@@ -11785,17 +11785,17 @@
       </c>
       <c r="F34" s="27" t="n">
         <f>F33*1.25</f>
-        <v>580815</v>
+        <v>568126.25</v>
       </c>
       <c r="G34" s="27"/>
       <c r="H34" s="27" t="n">
         <f>H33*1.25</f>
-        <v>580815</v>
+        <v>568126.25</v>
       </c>
       <c r="I34" s="27"/>
       <c r="J34" s="27" t="n">
         <f>J33*1.25</f>
-        <v>580815</v>
+        <v>568126.25</v>
       </c>
       <c r="K34" s="27"/>
       <c r="L34" s="23" t="s">
@@ -11804,7 +11804,7 @@
       <c r="M34" s="23"/>
       <c r="N34" s="27" t="n">
         <f>N33*1.25</f>
-        <v>1742445</v>
+        <v>1704378.75</v>
       </c>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
@@ -11813,17 +11813,17 @@
       </c>
       <c r="F35" s="27" t="n">
         <f>MAX($F$34,$H$34,$J$34)</f>
-        <v>580815</v>
+        <v>568126.25</v>
       </c>
       <c r="G35" s="27"/>
       <c r="H35" s="27" t="n">
         <f>MAX($F$34,$H$34,$J$34)</f>
-        <v>580815</v>
+        <v>568126.25</v>
       </c>
       <c r="I35" s="27"/>
       <c r="J35" s="27" t="n">
         <f>MAX($F$34,$H$34,$J$34)</f>
-        <v>580815</v>
+        <v>568126.25</v>
       </c>
       <c r="K35" s="27"/>
       <c r="L35" s="23" t="s">
@@ -11832,7 +11832,7 @@
       <c r="M35" s="23"/>
       <c r="N35" s="28" t="n">
         <f>N34/(480*SQRT(3))</f>
-        <v>2095.8356037460785</v>
+        <v>2050.049021069954</v>
       </c>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
@@ -11841,17 +11841,17 @@
       </c>
       <c r="F36" s="28" t="n">
         <f>F35/(480/SQRT(3))</f>
-        <v>2095.835603746078</v>
+        <v>2050.0490210699536</v>
       </c>
       <c r="G36" s="28"/>
       <c r="H36" s="28" t="n">
         <f>H35/(480/SQRT(3))</f>
-        <v>2095.835603746078</v>
+        <v>2050.0490210699536</v>
       </c>
       <c r="I36" s="28"/>
       <c r="J36" s="28" t="n">
         <f>J35/(480/SQRT(3))</f>
-        <v>2095.835603746078</v>
+        <v>2050.0490210699536</v>
       </c>
       <c r="K36" s="28"/>
       <c r="L36" s="23" t="s">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="N3" t="str">
         <f>Panel!$F$40&amp;" A 3P"</f>
-        <v>250 A 3P</v>
+        <v>150 A 3P</v>
       </c>
       <c r="S3" t="n">
         <f>IF(Intake!$D$23="L2",Intake!$B$23*IFERROR(VLOOKUP(Intake!$A$23,ModelTable,7,FALSE),0),0)</f>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="E4" t="str">
         <f>IF(TxKvaSuggested&gt;0,"EV_MAIN VIA "&amp;TxKvaSuggested&amp;" KVA XFMR","UTILITY")</f>
-        <v>EV_MAIN VIA 112.5 KVA XFMR</v>
+        <v>EV_MAIN VIA 75 KVA XFMR</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>139</v>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="N4" t="str">
         <f>Panel!$F$40&amp;" A"</f>
-        <v>250 A</v>
+        <v>150 A</v>
       </c>
       <c r="S4" t="n">
         <f>IF(Intake!$D$24="L2",Intake!$B$24*IFERROR(VLOOKUP(Intake!$A$24,ModelTable,7,FALSE),0),0)</f>
@@ -13989,7 +13989,7 @@
       <c r="M36" s="23"/>
       <c r="N36" t="n">
         <f>Panel!$F$40</f>
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="S36">
         <v>20</v>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="B7" s="9" t="n">
         <f>WireTotal+SUM(Intake!E23:E34)+IF(NTotal&gt;0,DataBoxCost+ServiceBoxCost,0)</f>
-        <v>39272.599650000004</v>
+        <v>39247.599650000004</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f>GearTotal</f>
-        <v>71295</v>
+        <v>70765</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f>SUM(B7:B18)</f>
-        <v>206847.22965</v>
+        <v>206292.22965</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="B20" s="9" t="n">
         <f>B19*ContingencyPct</f>
-        <v>20684.722965</v>
+        <v>20629.222965</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="B21" s="11" t="n">
         <f>B19+B20</f>
-        <v>227531.952615</v>
+        <v>226921.452615</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="B24" s="9" t="n">
         <f>ConstructionTotal*TaxPct</f>
-        <v>16496.066564587498</v>
+        <v>16451.8053145875</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="B25" s="9" t="n">
         <f>ConstructionTotal+LaborCost</f>
-        <v>339456.952615</v>
+        <v>338846.452615</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="B38" s="9" t="n">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,500+0.02*Valuation,300),0)</f>
-        <v>7289.139052300001</v>
+        <v>7276.929052300001</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B39" s="9" t="n">
         <f>SUM(B35:B38)</f>
-        <v>41377.8890523</v>
+        <v>41365.6790523</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f>ConstructionTotal+LaborCost+B24+B28+B29+B30+B31+B32+B39</f>
-        <v>879075.2144818875</v>
+        <v>878408.2432318876</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="B43" s="32" t="n">
         <f>TotalCost-RebateAmt</f>
-        <v>879075.2144818875</v>
+        <v>878408.2432318876</v>
       </c>
     </row>
   </sheetData>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="D3" s="41" t="n">
         <f>Estimate!B7+Estimate!B10+Estimate!B15</f>
-        <v>40772.599650000004</v>
+        <v>40747.599650000004</v>
       </c>
       <c r="E3" s="42" t="n">
         <f>ContingencyPct</f>
@@ -14962,11 +14962,11 @@
       </c>
       <c r="F3" s="41" t="n">
         <f>(D3*E3)+D3</f>
-        <v>44849.859615</v>
+        <v>44822.359615</v>
       </c>
       <c r="G3" s="43" t="n">
         <f>F3*C3</f>
-        <v>44849.859615</v>
+        <v>44822.359615</v>
       </c>
       <c r="J3" s="44" t="s">
         <v>233</v>
@@ -15013,7 +15013,7 @@
       </c>
       <c r="D5" s="41" t="n">
         <f>Panel!F42+Panel!F48+Panel!F66</f>
-        <v>11295</v>
+        <v>10765</v>
       </c>
       <c r="E5" s="42" t="n">
         <f>ContingencyPct</f>
@@ -15021,11 +15021,11 @@
       </c>
       <c r="F5" s="41" t="n">
         <f>(D5*E5)+D5</f>
-        <v>12424.5</v>
+        <v>11841.5</v>
       </c>
       <c r="G5" s="43" t="n">
         <f>F5*C5</f>
-        <v>12424.5</v>
+        <v>11841.5</v>
       </c>
       <c r="J5" s="46" t="s">
         <v>237</v>
@@ -15272,7 +15272,7 @@
       <c r="F15" s="53"/>
       <c r="G15" s="55" t="n">
         <f>SUM(G3:G13)</f>
-        <v>227531.95261500002</v>
+        <v>226921.45261500002</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15332,7 +15332,7 @@
       <c r="F20" s="57"/>
       <c r="G20" s="58" t="n">
         <f>G15+G19</f>
-        <v>339456.952615</v>
+        <v>338846.452615</v>
       </c>
     </row>
   </sheetData>

--- a/templates/RFC-Template.xlsx
+++ b/templates/RFC-Template.xlsx
@@ -2770,8 +2770,8 @@
         <v>42</v>
       </c>
       <c r="B49" s="5" t="n">
-        <f>IF(NTotal&lt;=0,0,ROUNDUP((8+2.5*NDcfc+1*NumL2+TrenchFt/40)*VLOOKUP(Terrain,TerrainTable,3,FALSE)+IF(InstallMethod="Trenched",0,RouteFt/EmtFtPerDay),0))</f>
-        <v>37</v>
+        <f>IF(NTotal&lt;=0,0,ROUNDUP((8+2.5*NDcfc+1*(SUMPRODUCT(($D$23:$D$34="L2")*$G$23:$G$34)-NumL2)+0.25*(2*NumL2-SUMPRODUCT(($D$23:$D$34="L2")*$G$23:$G$34))+TrenchFt/40)*VLOOKUP(Terrain,TerrainTable,3,FALSE)+IF(InstallMethod="Trenched",0,RouteFt/EmtFtPerDay),0))</f>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B72" s="5" t="n">
         <f>LaborDays</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C72" s="12" t="n">
         <f>LaborDayRate</f>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D72" s="9" t="n">
         <f>$B$72*$C$72</f>
-        <v>101750</v>
+        <v>90750</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D75" s="11" t="n">
         <f>SUM(D72:D74)</f>
-        <v>101750</v>
+        <v>90750</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B94" s="14" t="n">
         <f>TotalCost</f>
-        <v>878408.2432318876</v>
+        <v>862996.6162318876</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B95" s="11" t="n">
         <f>CustomerTotal</f>
-        <v>878408.2432318876</v>
+        <v>862996.6162318876</v>
       </c>
     </row>
   </sheetData>
@@ -3676,11 +3676,11 @@
       </c>
       <c r="B9" t="n">
         <f>LaborDays</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
         <f>LaborDays+7</f>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>290</v>
@@ -4470,7 +4470,7 @@
         <v>339</v>
       </c>
       <c r="B15" s="33">
-        <v>28500</v>
+        <v>31350</v>
       </c>
       <c r="C15" s="33">
         <v>402</v>
@@ -4694,7 +4694,7 @@
         <v>348</v>
       </c>
       <c r="B19" s="33">
-        <v>54000</v>
+        <v>59400</v>
       </c>
       <c r="C19" s="33">
         <v>558</v>
@@ -4806,7 +4806,7 @@
         <v>353</v>
       </c>
       <c r="B21" s="33">
-        <v>57000</v>
+        <v>68200</v>
       </c>
       <c r="C21" s="33">
         <v>753</v>
@@ -5142,7 +5142,7 @@
         <v>364</v>
       </c>
       <c r="B27" s="33">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="C27" s="33">
         <v>1268</v>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="B4" t="n">
         <f>LaborDays</f>
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="B16" s="9" t="n">
         <f>IF(NTotal&lt;=0,0,IF(InstallMethod="Surface EMT",EquipBaseEmt+EquipPerDayEmt*LaborDays,EquipBase+EquipPerDay*LaborDays))</f>
-        <v>13176</v>
+        <v>12132</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f>SUM(B7:B18)</f>
-        <v>206292.22965</v>
+        <v>205248.22965</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="B20" s="9" t="n">
         <f>B19*ContingencyPct</f>
-        <v>20629.222965</v>
+        <v>20524.822965</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="B21" s="11" t="n">
         <f>B19+B20</f>
-        <v>226921.452615</v>
+        <v>225773.052615</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="B23" s="9" t="n">
         <f>LaborBase*(1+ContingencyPct)</f>
-        <v>111925.00000000001</v>
+        <v>99825.00000000001</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="B24" s="9" t="n">
         <f>ConstructionTotal*TaxPct</f>
-        <v>16451.8053145875</v>
+        <v>16368.546314587498</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="B25" s="9" t="n">
         <f>ConstructionTotal+LaborCost</f>
-        <v>338846.452615</v>
+        <v>325598.052615</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="B37" s="9" t="n">
         <f>IF(IncCpm="Yes",LaborCost*CpmPct,0)</f>
-        <v>16788.75</v>
+        <v>14973.750000000002</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="B38" s="9" t="n">
         <f>IF(IncPermits="Yes",IF(NDcfc&gt;0,500+0.02*Valuation,300),0)</f>
-        <v>7276.929052300001</v>
+        <v>7011.9610523</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B39" s="9" t="n">
         <f>SUM(B35:B38)</f>
-        <v>41365.6790523</v>
+        <v>39285.7110523</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f>ConstructionTotal+LaborCost+B24+B28+B29+B30+B31+B32+B39</f>
-        <v>878408.2432318876</v>
+        <v>862996.6162318876</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="B43" s="32" t="n">
         <f>TotalCost-RebateAmt</f>
-        <v>878408.2432318876</v>
+        <v>862996.6162318876</v>
       </c>
     </row>
   </sheetData>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="K5" s="48" t="n">
         <f>LaborDays</f>
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="K6" s="48" t="n">
         <f>K5/30</f>
-        <v>1.2333333333333334</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="K7" s="50" t="n">
         <f>K5*K4</f>
-        <v>101750</v>
+        <v>90750</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="D13" s="41" t="n">
         <f>Estimate!B16</f>
-        <v>13176</v>
+        <v>12132</v>
       </c>
       <c r="E13" s="42" t="n">
         <f>ContingencyPct</f>
@@ -15234,11 +15234,11 @@
       </c>
       <c r="F13" s="41" t="n">
         <f>(D13*E13)+D13</f>
-        <v>14493.6</v>
+        <v>13345.2</v>
       </c>
       <c r="G13" s="43" t="n">
         <f>F13*C13</f>
-        <v>14493.6</v>
+        <v>13345.2</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -15250,18 +15250,18 @@
       </c>
       <c r="D14" s="41" t="n">
         <f>Estimate!B35+Estimate!B36+Estimate!B37</f>
-        <v>34088.75</v>
+        <v>32273.75</v>
       </c>
       <c r="E14" s="42">
         <v>0</v>
       </c>
       <c r="F14" s="41" t="n">
         <f>(D14*E14)+D14</f>
-        <v>34088.75</v>
+        <v>32273.75</v>
       </c>
       <c r="G14" s="43" t="n">
         <f>F14*C14</f>
-        <v>34088.75</v>
+        <v>32273.75</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -15272,7 +15272,7 @@
       <c r="F15" s="53"/>
       <c r="G15" s="55" t="n">
         <f>SUM(G3:G13)</f>
-        <v>226921.45261500002</v>
+        <v>225773.05261500002</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="C18" s="40" t="n">
         <f>K5</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D18" s="41" t="n">
         <f>K4</f>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="G18" s="43" t="n">
         <f>F18*C18</f>
-        <v>111925</v>
+        <v>99825</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -15319,7 +15319,7 @@
       <c r="F19" s="53"/>
       <c r="G19" s="55" t="n">
         <f>SUM(G18)</f>
-        <v>111925</v>
+        <v>99825</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -15332,7 +15332,7 @@
       <c r="F20" s="57"/>
       <c r="G20" s="58" t="n">
         <f>G15+G19</f>
-        <v>338846.452615</v>
+        <v>325598.05261500005</v>
       </c>
     </row>
   </sheetData>
